--- a/Data/National Accounts/PSA-09MAQ_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-09MAQ_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6FFD6E-2FDD-4A82-806B-0A9FBE941D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC0F0EF-7785-46E5-BF97-EFA74BD3F87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="MAQ" sheetId="9" r:id="rId1"/>
@@ -698,13 +698,13 @@
     <t>Table 10.7 Gross Value Added in Mining and Quarrying, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -746,10 +746,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -861,9 +863,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -871,9 +870,6 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -886,6 +882,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{0662CF8E-D90D-4FC2-9E33-010BFB9B5552}"/>
@@ -895,28 +897,7 @@
     <cellStyle name="Normal 2 2" xfId="4" xr:uid="{97D21D1F-4EF8-4188-9D7F-BCC1E953CA47}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{B9946DC9-451A-4989-BE67-D129290ED45C}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -1279,7 +1260,7 @@
     </row>
     <row r="3" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -1290,7 +1271,7 @@
     </row>
     <row r="6" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1301,162 +1282,162 @@
     <row r="8" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
-      <c r="B9" s="22">
+      <c r="B9" s="30">
         <v>2000</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22">
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30">
         <v>2001</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22">
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30">
         <v>2002</v>
       </c>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22">
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30">
         <v>2003</v>
       </c>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22">
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30">
         <v>2004</v>
       </c>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22">
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30">
         <v>2005</v>
       </c>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22">
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30">
         <v>2006</v>
       </c>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22">
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30">
         <v>2007</v>
       </c>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="22"/>
-      <c r="AH9" s="22">
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30">
         <v>2008</v>
       </c>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="22"/>
-      <c r="AK9" s="22"/>
-      <c r="AL9" s="22">
+      <c r="AI9" s="30"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="30">
         <v>2009</v>
       </c>
-      <c r="AM9" s="22"/>
-      <c r="AN9" s="22"/>
-      <c r="AO9" s="22"/>
-      <c r="AP9" s="22">
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="30"/>
+      <c r="AP9" s="30">
         <v>2010</v>
       </c>
-      <c r="AQ9" s="22"/>
-      <c r="AR9" s="22"/>
-      <c r="AS9" s="22"/>
-      <c r="AT9" s="22">
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="30"/>
+      <c r="AS9" s="30"/>
+      <c r="AT9" s="30">
         <v>2011</v>
       </c>
-      <c r="AU9" s="22"/>
-      <c r="AV9" s="22"/>
-      <c r="AW9" s="22"/>
-      <c r="AX9" s="22">
+      <c r="AU9" s="30"/>
+      <c r="AV9" s="30"/>
+      <c r="AW9" s="30"/>
+      <c r="AX9" s="30">
         <v>2012</v>
       </c>
-      <c r="AY9" s="22"/>
-      <c r="AZ9" s="22"/>
-      <c r="BA9" s="22"/>
-      <c r="BB9" s="22">
+      <c r="AY9" s="30"/>
+      <c r="AZ9" s="30"/>
+      <c r="BA9" s="30"/>
+      <c r="BB9" s="30">
         <v>2013</v>
       </c>
-      <c r="BC9" s="22"/>
-      <c r="BD9" s="22"/>
-      <c r="BE9" s="22"/>
-      <c r="BF9" s="22">
+      <c r="BC9" s="30"/>
+      <c r="BD9" s="30"/>
+      <c r="BE9" s="30"/>
+      <c r="BF9" s="30">
         <v>2014</v>
       </c>
-      <c r="BG9" s="22"/>
-      <c r="BH9" s="22"/>
-      <c r="BI9" s="22"/>
-      <c r="BJ9" s="22">
+      <c r="BG9" s="30"/>
+      <c r="BH9" s="30"/>
+      <c r="BI9" s="30"/>
+      <c r="BJ9" s="30">
         <v>2015</v>
       </c>
-      <c r="BK9" s="22"/>
-      <c r="BL9" s="22"/>
-      <c r="BM9" s="22"/>
-      <c r="BN9" s="22">
+      <c r="BK9" s="30"/>
+      <c r="BL9" s="30"/>
+      <c r="BM9" s="30"/>
+      <c r="BN9" s="30">
         <v>2016</v>
       </c>
-      <c r="BO9" s="22"/>
-      <c r="BP9" s="22"/>
-      <c r="BQ9" s="22"/>
-      <c r="BR9" s="22">
+      <c r="BO9" s="30"/>
+      <c r="BP9" s="30"/>
+      <c r="BQ9" s="30"/>
+      <c r="BR9" s="30">
         <v>2017</v>
       </c>
-      <c r="BS9" s="22"/>
-      <c r="BT9" s="22"/>
-      <c r="BU9" s="22"/>
-      <c r="BV9" s="22">
+      <c r="BS9" s="30"/>
+      <c r="BT9" s="30"/>
+      <c r="BU9" s="30"/>
+      <c r="BV9" s="30">
         <v>2018</v>
       </c>
-      <c r="BW9" s="22"/>
-      <c r="BX9" s="22"/>
-      <c r="BY9" s="22"/>
-      <c r="BZ9" s="22">
+      <c r="BW9" s="30"/>
+      <c r="BX9" s="30"/>
+      <c r="BY9" s="30"/>
+      <c r="BZ9" s="30">
         <v>2019</v>
       </c>
-      <c r="CA9" s="22"/>
-      <c r="CB9" s="22"/>
-      <c r="CC9" s="22"/>
-      <c r="CD9" s="22">
+      <c r="CA9" s="30"/>
+      <c r="CB9" s="30"/>
+      <c r="CC9" s="30"/>
+      <c r="CD9" s="30">
         <v>2020</v>
       </c>
-      <c r="CE9" s="22"/>
-      <c r="CF9" s="22"/>
-      <c r="CG9" s="22"/>
-      <c r="CH9" s="23">
+      <c r="CE9" s="30"/>
+      <c r="CF9" s="30"/>
+      <c r="CG9" s="30"/>
+      <c r="CH9" s="22">
         <v>2021</v>
       </c>
-      <c r="CI9" s="23"/>
-      <c r="CJ9" s="23"/>
-      <c r="CK9" s="23"/>
-      <c r="CL9" s="24">
+      <c r="CI9" s="22"/>
+      <c r="CJ9" s="22"/>
+      <c r="CK9" s="22"/>
+      <c r="CL9" s="23">
         <v>2022</v>
       </c>
-      <c r="CM9" s="24"/>
-      <c r="CN9" s="24"/>
-      <c r="CO9" s="24"/>
-      <c r="CP9" s="28">
+      <c r="CM9" s="23"/>
+      <c r="CN9" s="23"/>
+      <c r="CO9" s="23"/>
+      <c r="CP9" s="26">
         <v>2023</v>
       </c>
-      <c r="CQ9" s="28"/>
-      <c r="CR9" s="28"/>
-      <c r="CS9" s="28"/>
-      <c r="CT9" s="28">
+      <c r="CQ9" s="26"/>
+      <c r="CR9" s="26"/>
+      <c r="CS9" s="26"/>
+      <c r="CT9" s="26">
         <v>2024</v>
       </c>
-      <c r="CU9" s="28"/>
-      <c r="CV9" s="28"/>
-      <c r="CW9" s="28"/>
-      <c r="CX9" s="28">
+      <c r="CU9" s="26"/>
+      <c r="CV9" s="26"/>
+      <c r="CW9" s="26"/>
+      <c r="CX9" s="26">
         <v>2025</v>
       </c>
-      <c r="CY9" s="28"/>
-      <c r="CZ9" s="28"/>
-      <c r="DA9" s="28"/>
+      <c r="CY9" s="26"/>
+      <c r="CZ9" s="26"/>
+      <c r="DA9" s="26"/>
     </row>
     <row r="10" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1782,244 +1763,244 @@
       <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="24">
         <v>794.11637299999984</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="24">
         <v>766.37296099999992</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="24">
         <v>763.95932300000004</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="24">
         <v>348.28399964466195</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="24">
         <v>631.34958799999993</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="24">
         <v>410.60773999999992</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="24">
         <v>365.91663400000004</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="24">
         <v>389.18186088251889</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="24">
         <v>694.67960899999991</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="24">
         <v>848.34231999999997</v>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="24">
         <v>651.23409500000002</v>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="24">
         <v>421.92036805226996</v>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="24">
         <v>580.96508699999993</v>
       </c>
-      <c r="O12" s="25">
+      <c r="O12" s="24">
         <v>1089.3449450000001</v>
       </c>
-      <c r="P12" s="25">
+      <c r="P12" s="24">
         <v>640.79916200000014</v>
       </c>
-      <c r="Q12" s="25">
+      <c r="Q12" s="24">
         <v>339.59760586871391</v>
       </c>
-      <c r="R12" s="25">
+      <c r="R12" s="24">
         <v>769.220235</v>
       </c>
-      <c r="S12" s="25">
+      <c r="S12" s="24">
         <v>772.05173700000012</v>
       </c>
-      <c r="T12" s="25">
+      <c r="T12" s="24">
         <v>1403.2788910000004</v>
       </c>
-      <c r="U12" s="25">
+      <c r="U12" s="24">
         <v>627.61970396246409</v>
       </c>
-      <c r="V12" s="25">
+      <c r="V12" s="24">
         <v>932.38082899999984</v>
       </c>
-      <c r="W12" s="25">
+      <c r="W12" s="24">
         <v>1110.5233030000002</v>
       </c>
-      <c r="X12" s="25">
+      <c r="X12" s="24">
         <v>1038.9867820000002</v>
       </c>
-      <c r="Y12" s="25">
+      <c r="Y12" s="24">
         <v>986.79690944181357</v>
       </c>
-      <c r="Z12" s="25">
+      <c r="Z12" s="24">
         <v>982.5352509999999</v>
       </c>
-      <c r="AA12" s="25">
+      <c r="AA12" s="24">
         <v>1211.5135009999999</v>
       </c>
-      <c r="AB12" s="25">
+      <c r="AB12" s="24">
         <v>909.4671020000003</v>
       </c>
-      <c r="AC12" s="25">
+      <c r="AC12" s="24">
         <v>459.58533244774253</v>
       </c>
-      <c r="AD12" s="25">
+      <c r="AD12" s="24">
         <v>894.50756400000012</v>
       </c>
-      <c r="AE12" s="25">
+      <c r="AE12" s="24">
         <v>1828.9211080000002</v>
       </c>
-      <c r="AF12" s="25">
+      <c r="AF12" s="24">
         <v>1033.0278969999999</v>
       </c>
-      <c r="AG12" s="25">
+      <c r="AG12" s="24">
         <v>554.52032968122523</v>
       </c>
-      <c r="AH12" s="25">
+      <c r="AH12" s="24">
         <v>1122.5006939999998</v>
       </c>
-      <c r="AI12" s="25">
+      <c r="AI12" s="24">
         <v>1711.116297</v>
       </c>
-      <c r="AJ12" s="25">
+      <c r="AJ12" s="24">
         <v>1289.9871459999999</v>
       </c>
-      <c r="AK12" s="25">
+      <c r="AK12" s="24">
         <v>696.00466682713807</v>
       </c>
-      <c r="AL12" s="25">
+      <c r="AL12" s="24">
         <v>1752.2324210000002</v>
       </c>
-      <c r="AM12" s="25">
+      <c r="AM12" s="24">
         <v>1621.7328300000001</v>
       </c>
-      <c r="AN12" s="25">
+      <c r="AN12" s="24">
         <v>1326.2240400000001</v>
       </c>
-      <c r="AO12" s="25">
+      <c r="AO12" s="24">
         <v>749.05839007851512</v>
       </c>
-      <c r="AP12" s="25">
+      <c r="AP12" s="24">
         <v>1571.6359380000001</v>
       </c>
-      <c r="AQ12" s="25">
+      <c r="AQ12" s="24">
         <v>2421.8341029999997</v>
       </c>
-      <c r="AR12" s="25">
+      <c r="AR12" s="24">
         <v>1937.2848779999999</v>
       </c>
-      <c r="AS12" s="25">
+      <c r="AS12" s="24">
         <v>1096.7253942893938</v>
       </c>
-      <c r="AT12" s="25">
+      <c r="AT12" s="24">
         <v>2951.259415</v>
       </c>
-      <c r="AU12" s="25">
+      <c r="AU12" s="24">
         <v>3380.6936529999994</v>
       </c>
-      <c r="AV12" s="25">
+      <c r="AV12" s="24">
         <v>2583.4269829999998</v>
       </c>
-      <c r="AW12" s="25">
+      <c r="AW12" s="24">
         <v>1207.889672806675</v>
       </c>
-      <c r="AX12" s="25">
+      <c r="AX12" s="24">
         <v>2343.2286470000004</v>
       </c>
-      <c r="AY12" s="25">
+      <c r="AY12" s="24">
         <v>3547.7680569999989</v>
       </c>
-      <c r="AZ12" s="25">
+      <c r="AZ12" s="24">
         <v>1398.2198580000002</v>
       </c>
-      <c r="BA12" s="25">
+      <c r="BA12" s="24">
         <v>1032.8610535868686</v>
       </c>
-      <c r="BB12" s="25">
+      <c r="BB12" s="24">
         <v>816.01222799999994</v>
       </c>
-      <c r="BC12" s="25">
+      <c r="BC12" s="24">
         <v>3292.7609749999992</v>
       </c>
-      <c r="BD12" s="25">
+      <c r="BD12" s="24">
         <v>2163.4480800000001</v>
       </c>
-      <c r="BE12" s="25">
+      <c r="BE12" s="24">
         <v>1553.8501129372041</v>
       </c>
-      <c r="BF12" s="25">
+      <c r="BF12" s="24">
         <v>2785.4239000000002</v>
       </c>
-      <c r="BG12" s="25">
+      <c r="BG12" s="24">
         <v>3672.4838589999999</v>
       </c>
-      <c r="BH12" s="25">
+      <c r="BH12" s="24">
         <v>2236.7316469999996</v>
       </c>
-      <c r="BI12" s="25">
+      <c r="BI12" s="24">
         <v>574.19896131024075</v>
       </c>
-      <c r="BJ12" s="25">
+      <c r="BJ12" s="24">
         <v>2463.4389259999998</v>
       </c>
-      <c r="BK12" s="25">
+      <c r="BK12" s="24">
         <v>2457.4550610000001</v>
       </c>
-      <c r="BL12" s="25">
+      <c r="BL12" s="24">
         <v>1881.7013319999996</v>
       </c>
-      <c r="BM12" s="25">
+      <c r="BM12" s="24">
         <v>1590.3231410533162</v>
       </c>
-      <c r="BN12" s="25">
+      <c r="BN12" s="24">
         <v>2689.7720600000002</v>
       </c>
-      <c r="BO12" s="25">
+      <c r="BO12" s="24">
         <v>2264.8916189999995</v>
       </c>
-      <c r="BP12" s="25">
+      <c r="BP12" s="24">
         <v>5760.6983933536139</v>
       </c>
-      <c r="BQ12" s="25">
+      <c r="BQ12" s="24">
         <v>2476.7291178096762</v>
       </c>
-      <c r="BR12" s="25">
+      <c r="BR12" s="24">
         <v>3784.2503890000003</v>
       </c>
-      <c r="BS12" s="25">
+      <c r="BS12" s="24">
         <v>5405.6188920000004</v>
       </c>
-      <c r="BT12" s="25">
+      <c r="BT12" s="24">
         <v>7639.2714569999998</v>
       </c>
-      <c r="BU12" s="25">
+      <c r="BU12" s="24">
         <v>2500.9508066344069</v>
       </c>
-      <c r="BV12" s="25">
+      <c r="BV12" s="24">
         <v>5148.7369070000013</v>
       </c>
-      <c r="BW12" s="25">
+      <c r="BW12" s="24">
         <v>6629.7409140000009</v>
       </c>
-      <c r="BX12" s="25">
+      <c r="BX12" s="24">
         <v>5872.0242509999998</v>
       </c>
-      <c r="BY12" s="25">
+      <c r="BY12" s="24">
         <v>3413.9979416093834</v>
       </c>
-      <c r="BZ12" s="25">
+      <c r="BZ12" s="24">
         <v>4454.9919389999995</v>
       </c>
-      <c r="CA12" s="25">
+      <c r="CA12" s="24">
         <v>6211.0675205265252</v>
       </c>
-      <c r="CB12" s="25">
+      <c r="CB12" s="24">
         <v>4305.5234738111703</v>
       </c>
-      <c r="CC12" s="25">
+      <c r="CC12" s="24">
         <v>1959.7943747016132</v>
       </c>
       <c r="CD12" s="12">
@@ -2074,10 +2055,10 @@
         <v>8398.6294149756122</v>
       </c>
       <c r="CU12" s="12">
-        <v>11366.040301691532</v>
+        <v>11378.012194237403</v>
       </c>
       <c r="CV12" s="12">
-        <v>10123.026406044421</v>
+        <v>10121.242425129351</v>
       </c>
       <c r="CW12" s="12">
         <v>4482.2920522770482</v>
@@ -2086,13 +2067,13 @@
         <v>8784.2374003370114</v>
       </c>
       <c r="CY12" s="12">
-        <v>9847.6283377393138</v>
+        <v>9902.0958737915953</v>
       </c>
       <c r="CZ12" s="12">
-        <v>10696.161632139258</v>
+        <v>10762.470603082478</v>
       </c>
       <c r="DA12" s="12">
-        <v>5839.6278714273049</v>
+        <v>5988.9179232925389</v>
       </c>
       <c r="DB12" s="14"/>
       <c r="DC12" s="14"/>
@@ -2173,244 +2154,244 @@
       <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="24">
         <v>6.1152049999999987</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>14.186243999999999</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <v>64.811802999999998</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="24">
         <v>259.27359019895266</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <v>447.341881</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <v>543.15554999999995</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <v>245.11173199999999</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <v>169.71614333069826</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="24">
         <v>8334.0966169999974</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="24">
         <v>3767.3421960000001</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="24">
         <v>1625.23017</v>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="24">
         <v>999.15481074904392</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="24">
         <v>3676.1525009999987</v>
       </c>
-      <c r="O13" s="25">
+      <c r="O13" s="24">
         <v>4907.7908159999997</v>
       </c>
-      <c r="P13" s="25">
+      <c r="P13" s="24">
         <v>6073.3916480000016</v>
       </c>
-      <c r="Q13" s="25">
+      <c r="Q13" s="24">
         <v>6813.5686867867807</v>
       </c>
-      <c r="R13" s="25">
+      <c r="R13" s="24">
         <v>5991.9242140000006</v>
       </c>
-      <c r="S13" s="25">
+      <c r="S13" s="24">
         <v>6208.9220800000003</v>
       </c>
-      <c r="T13" s="25">
+      <c r="T13" s="24">
         <v>5259.2892730000012</v>
       </c>
-      <c r="U13" s="25">
+      <c r="U13" s="24">
         <v>4780.2787532499615</v>
       </c>
-      <c r="V13" s="25">
+      <c r="V13" s="24">
         <v>6520.9175959999993</v>
       </c>
-      <c r="W13" s="25">
+      <c r="W13" s="24">
         <v>8534.2982219999994</v>
       </c>
-      <c r="X13" s="25">
+      <c r="X13" s="24">
         <v>9378.4040140000034</v>
       </c>
-      <c r="Y13" s="25">
+      <c r="Y13" s="24">
         <v>8818.249419640757</v>
       </c>
-      <c r="Z13" s="25">
+      <c r="Z13" s="24">
         <v>7766.9502659999998</v>
       </c>
-      <c r="AA13" s="25">
+      <c r="AA13" s="24">
         <v>9284.6452769999996</v>
       </c>
-      <c r="AB13" s="25">
+      <c r="AB13" s="24">
         <v>10271.798977000002</v>
       </c>
-      <c r="AC13" s="25">
+      <c r="AC13" s="24">
         <v>6216.0874833499083</v>
       </c>
-      <c r="AD13" s="25">
+      <c r="AD13" s="24">
         <v>8822.9695159999992</v>
       </c>
-      <c r="AE13" s="25">
+      <c r="AE13" s="24">
         <v>9614.0692050000016</v>
       </c>
-      <c r="AF13" s="25">
+      <c r="AF13" s="24">
         <v>8766.2836830000015</v>
       </c>
-      <c r="AG13" s="25">
+      <c r="AG13" s="24">
         <v>7470.125701667368</v>
       </c>
-      <c r="AH13" s="25">
+      <c r="AH13" s="24">
         <v>8759.5875609999985</v>
       </c>
-      <c r="AI13" s="25">
+      <c r="AI13" s="24">
         <v>11219.219043999999</v>
       </c>
-      <c r="AJ13" s="25">
+      <c r="AJ13" s="24">
         <v>12416.667626</v>
       </c>
-      <c r="AK13" s="25">
+      <c r="AK13" s="24">
         <v>10506.187462661739</v>
       </c>
-      <c r="AL13" s="25">
+      <c r="AL13" s="24">
         <v>7970.9733259999994</v>
       </c>
-      <c r="AM13" s="25">
+      <c r="AM13" s="24">
         <v>10610.951773000001</v>
       </c>
-      <c r="AN13" s="25">
+      <c r="AN13" s="24">
         <v>11073.366724</v>
       </c>
-      <c r="AO13" s="25">
+      <c r="AO13" s="24">
         <v>12135.039845021141</v>
       </c>
-      <c r="AP13" s="25">
+      <c r="AP13" s="24">
         <v>7961.3209000000006</v>
       </c>
-      <c r="AQ13" s="25">
+      <c r="AQ13" s="24">
         <v>11275.626972</v>
       </c>
-      <c r="AR13" s="25">
+      <c r="AR13" s="24">
         <v>11276.166713000001</v>
       </c>
-      <c r="AS13" s="25">
+      <c r="AS13" s="24">
         <v>11249.185139886411</v>
       </c>
-      <c r="AT13" s="25">
+      <c r="AT13" s="24">
         <v>10804.553634</v>
       </c>
-      <c r="AU13" s="25">
+      <c r="AU13" s="24">
         <v>13132.898034999998</v>
       </c>
-      <c r="AV13" s="25">
+      <c r="AV13" s="24">
         <v>12800.319378</v>
       </c>
-      <c r="AW13" s="25">
+      <c r="AW13" s="24">
         <v>10826.924280947678</v>
       </c>
-      <c r="AX13" s="25">
+      <c r="AX13" s="24">
         <v>10274.968441000001</v>
       </c>
-      <c r="AY13" s="25">
+      <c r="AY13" s="24">
         <v>11705.614650999996</v>
       </c>
-      <c r="AZ13" s="25">
+      <c r="AZ13" s="24">
         <v>10015.323321</v>
       </c>
-      <c r="BA13" s="25">
+      <c r="BA13" s="24">
         <v>11181.056198897077</v>
       </c>
-      <c r="BB13" s="25">
+      <c r="BB13" s="24">
         <v>10304.407727</v>
       </c>
-      <c r="BC13" s="25">
+      <c r="BC13" s="24">
         <v>9871.3222419999984</v>
       </c>
-      <c r="BD13" s="25">
+      <c r="BD13" s="24">
         <v>10115.840367000003</v>
       </c>
-      <c r="BE13" s="25">
+      <c r="BE13" s="24">
         <v>8428.2098279051152</v>
       </c>
-      <c r="BF13" s="25">
+      <c r="BF13" s="24">
         <v>11524.367569</v>
       </c>
-      <c r="BG13" s="25">
+      <c r="BG13" s="24">
         <v>11351.914746999999</v>
       </c>
-      <c r="BH13" s="25">
+      <c r="BH13" s="24">
         <v>7524.4473009999992</v>
       </c>
-      <c r="BI13" s="25">
+      <c r="BI13" s="24">
         <v>9998.1124232565544</v>
       </c>
-      <c r="BJ13" s="25">
+      <c r="BJ13" s="24">
         <v>6259.6821729999992</v>
       </c>
-      <c r="BK13" s="25">
+      <c r="BK13" s="24">
         <v>6847.8412559999979</v>
       </c>
-      <c r="BL13" s="25">
+      <c r="BL13" s="24">
         <v>6320.3402110000006</v>
       </c>
-      <c r="BM13" s="25">
+      <c r="BM13" s="24">
         <v>8353.5606420055683</v>
       </c>
-      <c r="BN13" s="25">
+      <c r="BN13" s="24">
         <v>7516.3221610000001</v>
       </c>
-      <c r="BO13" s="25">
+      <c r="BO13" s="24">
         <v>7347.2584639999986</v>
       </c>
-      <c r="BP13" s="25">
+      <c r="BP13" s="24">
         <v>5349.6780903283825</v>
       </c>
-      <c r="BQ13" s="25">
+      <c r="BQ13" s="24">
         <v>7409.3794904590404</v>
       </c>
-      <c r="BR13" s="25">
+      <c r="BR13" s="24">
         <v>6676.5368849999995</v>
       </c>
-      <c r="BS13" s="25">
+      <c r="BS13" s="24">
         <v>8527.7948029999989</v>
       </c>
-      <c r="BT13" s="25">
+      <c r="BT13" s="24">
         <v>7444.7381609999993</v>
       </c>
-      <c r="BU13" s="25">
+      <c r="BU13" s="24">
         <v>9734.2008230002648</v>
       </c>
-      <c r="BV13" s="25">
+      <c r="BV13" s="24">
         <v>9643.4504070000003</v>
       </c>
-      <c r="BW13" s="25">
+      <c r="BW13" s="24">
         <v>9979.3267780000006</v>
       </c>
-      <c r="BX13" s="25">
+      <c r="BX13" s="24">
         <v>8313.1704460000001</v>
       </c>
-      <c r="BY13" s="25">
+      <c r="BY13" s="24">
         <v>10779.991704759663</v>
       </c>
-      <c r="BZ13" s="25">
+      <c r="BZ13" s="24">
         <v>10100.199167357752</v>
       </c>
-      <c r="CA13" s="25">
+      <c r="CA13" s="24">
         <v>10822.803328</v>
       </c>
-      <c r="CB13" s="25">
+      <c r="CB13" s="24">
         <v>7010.0687939999998</v>
       </c>
-      <c r="CC13" s="25">
+      <c r="CC13" s="24">
         <v>9369.7032996939015</v>
       </c>
       <c r="CD13" s="12">
@@ -2465,25 +2446,25 @@
         <v>5872.9859319981824</v>
       </c>
       <c r="CU13" s="12">
-        <v>5020.844745825927</v>
+        <v>5020.8447458259261</v>
       </c>
       <c r="CV13" s="12">
         <v>4005.2673242145211</v>
       </c>
       <c r="CW13" s="12">
-        <v>5537.7171624746334</v>
+        <v>5537.7171624746343</v>
       </c>
       <c r="CX13" s="12">
         <v>8133.1848955953719</v>
       </c>
       <c r="CY13" s="12">
-        <v>4583.1737825361661</v>
+        <v>4583.1018009958789</v>
       </c>
       <c r="CZ13" s="12">
         <v>3874.8193174640592</v>
       </c>
       <c r="DA13" s="12">
-        <v>4681.8551857766379</v>
+        <v>4767.6377268554515</v>
       </c>
       <c r="DB13" s="14"/>
       <c r="DC13" s="14"/>
@@ -2564,244 +2545,244 @@
       <c r="A14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="24">
         <v>2472.1585949999994</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>2221.3938330000001</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <v>2643.092404</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="24">
         <v>3346.3300032795146</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <v>2364.1159229999994</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="24">
         <v>3081.0323440000002</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="24">
         <v>2872.6053010000001</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="24">
         <v>2830.2676447826884</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="24">
         <v>3164.9585479999996</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="24">
         <v>3317.0662480000005</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="24">
         <v>3784.6104580000006</v>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="24">
         <v>3595.127310199362</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="24">
         <v>3917.1234329999997</v>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="24">
         <v>3953.5024219999996</v>
       </c>
-      <c r="P14" s="25">
+      <c r="P14" s="24">
         <v>4719.5461170000017</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="24">
         <v>5206.8633749987785</v>
       </c>
-      <c r="R14" s="25">
+      <c r="R14" s="24">
         <v>4716.6752470000001</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S14" s="24">
         <v>3496.8587779999998</v>
       </c>
-      <c r="T14" s="25">
+      <c r="T14" s="24">
         <v>4855.6519220000009</v>
       </c>
-      <c r="U14" s="25">
+      <c r="U14" s="24">
         <v>5436.105945720974</v>
       </c>
-      <c r="V14" s="25">
+      <c r="V14" s="24">
         <v>4243.4147899999998</v>
       </c>
-      <c r="W14" s="25">
+      <c r="W14" s="24">
         <v>4882.7799309999991</v>
       </c>
-      <c r="X14" s="25">
+      <c r="X14" s="24">
         <v>5833.9763160000011</v>
       </c>
-      <c r="Y14" s="25">
+      <c r="Y14" s="24">
         <v>5198.9883020283378</v>
       </c>
-      <c r="Z14" s="25">
+      <c r="Z14" s="24">
         <v>5658.9230669999997</v>
       </c>
-      <c r="AA14" s="25">
+      <c r="AA14" s="24">
         <v>6311.1515969999991</v>
       </c>
-      <c r="AB14" s="25">
+      <c r="AB14" s="24">
         <v>5377.3986839999998</v>
       </c>
-      <c r="AC14" s="25">
+      <c r="AC14" s="24">
         <v>5553.7963162615897</v>
       </c>
-      <c r="AD14" s="25">
+      <c r="AD14" s="24">
         <v>7606.5203539999993</v>
       </c>
-      <c r="AE14" s="25">
+      <c r="AE14" s="24">
         <v>5986.6790940000001</v>
       </c>
-      <c r="AF14" s="25">
+      <c r="AF14" s="24">
         <v>8007.2203079999999</v>
       </c>
-      <c r="AG14" s="25">
+      <c r="AG14" s="24">
         <v>6916.588477867158</v>
       </c>
-      <c r="AH14" s="25">
+      <c r="AH14" s="24">
         <v>9092.5096489999996</v>
       </c>
-      <c r="AI14" s="25">
+      <c r="AI14" s="24">
         <v>6655.0939280000002</v>
       </c>
-      <c r="AJ14" s="25">
+      <c r="AJ14" s="24">
         <v>7945.4944570000007</v>
       </c>
-      <c r="AK14" s="25">
+      <c r="AK14" s="24">
         <v>6676.7133023864017</v>
       </c>
-      <c r="AL14" s="25">
+      <c r="AL14" s="24">
         <v>8822.7483759999996</v>
       </c>
-      <c r="AM14" s="25">
+      <c r="AM14" s="24">
         <v>6326.3121550000005</v>
       </c>
-      <c r="AN14" s="25">
+      <c r="AN14" s="24">
         <v>11278.466806000002</v>
       </c>
-      <c r="AO14" s="25">
+      <c r="AO14" s="24">
         <v>11631.942114353393</v>
       </c>
-      <c r="AP14" s="25">
+      <c r="AP14" s="24">
         <v>9347.7049719999995</v>
       </c>
-      <c r="AQ14" s="25">
+      <c r="AQ14" s="24">
         <v>12784.327214000001</v>
       </c>
-      <c r="AR14" s="25">
+      <c r="AR14" s="24">
         <v>13081.704052000001</v>
       </c>
-      <c r="AS14" s="25">
+      <c r="AS14" s="24">
         <v>15403.026206994937</v>
       </c>
-      <c r="AT14" s="25">
+      <c r="AT14" s="24">
         <v>15917.287211999999</v>
       </c>
-      <c r="AU14" s="25">
+      <c r="AU14" s="24">
         <v>16945.996634999996</v>
       </c>
-      <c r="AV14" s="25">
+      <c r="AV14" s="24">
         <v>6984.2519130000001</v>
       </c>
-      <c r="AW14" s="25">
+      <c r="AW14" s="24">
         <v>6783.0390080284897</v>
       </c>
-      <c r="AX14" s="25">
+      <c r="AX14" s="24">
         <v>6149.4442819999995</v>
       </c>
-      <c r="AY14" s="25">
+      <c r="AY14" s="24">
         <v>6059.2979299999988</v>
       </c>
-      <c r="AZ14" s="25">
+      <c r="AZ14" s="24">
         <v>5815.5105640000002</v>
       </c>
-      <c r="BA14" s="25">
+      <c r="BA14" s="24">
         <v>5628.9253107862332</v>
       </c>
-      <c r="BB14" s="25">
+      <c r="BB14" s="24">
         <v>4608.5971800000007</v>
       </c>
-      <c r="BC14" s="25">
+      <c r="BC14" s="24">
         <v>5085.8326929999985</v>
       </c>
-      <c r="BD14" s="25">
+      <c r="BD14" s="24">
         <v>5319.282173999999</v>
       </c>
-      <c r="BE14" s="25">
+      <c r="BE14" s="24">
         <v>5333.5981552810099</v>
       </c>
-      <c r="BF14" s="25">
+      <c r="BF14" s="24">
         <v>5294.9738849999994</v>
       </c>
-      <c r="BG14" s="25">
+      <c r="BG14" s="24">
         <v>4203.8220870000005</v>
       </c>
-      <c r="BH14" s="25">
+      <c r="BH14" s="24">
         <v>5182.5061870000009</v>
       </c>
-      <c r="BI14" s="25">
+      <c r="BI14" s="24">
         <v>5611.0765443829887</v>
       </c>
-      <c r="BJ14" s="25">
+      <c r="BJ14" s="24">
         <v>5648.0153899999987</v>
       </c>
-      <c r="BK14" s="25">
+      <c r="BK14" s="24">
         <v>5290.383491999999</v>
       </c>
-      <c r="BL14" s="25">
+      <c r="BL14" s="24">
         <v>5084.5241409999999</v>
       </c>
-      <c r="BM14" s="25">
+      <c r="BM14" s="24">
         <v>4985.0904614530518</v>
       </c>
-      <c r="BN14" s="25">
+      <c r="BN14" s="24">
         <v>6244.1831939999993</v>
       </c>
-      <c r="BO14" s="25">
+      <c r="BO14" s="24">
         <v>7147.5893989999995</v>
       </c>
-      <c r="BP14" s="25">
+      <c r="BP14" s="24">
         <v>6232.2943023825619</v>
       </c>
-      <c r="BQ14" s="25">
+      <c r="BQ14" s="24">
         <v>5391.8740098834287</v>
       </c>
-      <c r="BR14" s="25">
+      <c r="BR14" s="24">
         <v>7292.098935</v>
       </c>
-      <c r="BS14" s="25">
+      <c r="BS14" s="24">
         <v>6476.9207859999997</v>
       </c>
-      <c r="BT14" s="25">
+      <c r="BT14" s="24">
         <v>6180.2356609999988</v>
       </c>
-      <c r="BU14" s="25">
+      <c r="BU14" s="24">
         <v>6364.4162413124795</v>
       </c>
-      <c r="BV14" s="25">
+      <c r="BV14" s="24">
         <v>6481.492326999999</v>
       </c>
-      <c r="BW14" s="25">
+      <c r="BW14" s="24">
         <v>6826.2817220000006</v>
       </c>
-      <c r="BX14" s="25">
+      <c r="BX14" s="24">
         <v>6247.1424500000003</v>
       </c>
-      <c r="BY14" s="25">
+      <c r="BY14" s="24">
         <v>5516.228135017107</v>
       </c>
-      <c r="BZ14" s="25">
+      <c r="BZ14" s="24">
         <v>7161.2744120017987</v>
       </c>
-      <c r="CA14" s="25">
+      <c r="CA14" s="24">
         <v>7245.9516219999996</v>
       </c>
-      <c r="CB14" s="25">
+      <c r="CB14" s="24">
         <v>6865.5985869999995</v>
       </c>
-      <c r="CC14" s="25">
+      <c r="CC14" s="24">
         <v>5597.2428047479962</v>
       </c>
       <c r="CD14" s="12">
@@ -2862,19 +2843,19 @@
         <v>18424.068537477629</v>
       </c>
       <c r="CW14" s="12">
-        <v>16718.091355148263</v>
+        <v>16729.578722883864</v>
       </c>
       <c r="CX14" s="12">
-        <v>19398.67565617774</v>
+        <v>19454.20354583126</v>
       </c>
       <c r="CY14" s="12">
-        <v>23828.795182788159</v>
+        <v>23839.824484290759</v>
       </c>
       <c r="CZ14" s="12">
-        <v>24092.78682097917</v>
+        <v>24123.374429885138</v>
       </c>
       <c r="DA14" s="12">
-        <v>24123.152530294748</v>
+        <v>24121.33716112205</v>
       </c>
       <c r="DB14" s="14"/>
       <c r="DC14" s="14"/>
@@ -2955,244 +2936,244 @@
       <c r="A15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="24">
         <v>133.97860999999997</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>587.69638800000007</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <v>143.07809399999999</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="24">
         <v>19.397534672673771</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <v>140.44997799999996</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <v>731.24290299999996</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <v>263.01665700000001</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="24">
         <v>34.647333540565327</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="24">
         <v>174.78893899999994</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="24">
         <v>550.80377999999996</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="24">
         <v>237.36181099999999</v>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="24">
         <v>44.445233909360084</v>
       </c>
-      <c r="N15" s="25">
+      <c r="N15" s="24">
         <v>221.70970299999996</v>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="24">
         <v>519.03891999999996</v>
       </c>
-      <c r="P15" s="25">
+      <c r="P15" s="24">
         <v>252.97114700000006</v>
       </c>
-      <c r="Q15" s="25">
+      <c r="Q15" s="24">
         <v>49.108734440052608</v>
       </c>
-      <c r="R15" s="25">
+      <c r="R15" s="24">
         <v>81.832414</v>
       </c>
-      <c r="S15" s="25">
+      <c r="S15" s="24">
         <v>519.75309799999991</v>
       </c>
-      <c r="T15" s="25">
+      <c r="T15" s="24">
         <v>416.344221</v>
       </c>
-      <c r="U15" s="25">
+      <c r="U15" s="24">
         <v>44.992612625552127</v>
       </c>
-      <c r="V15" s="25">
+      <c r="V15" s="24">
         <v>337.4652529999999</v>
       </c>
-      <c r="W15" s="25">
+      <c r="W15" s="24">
         <v>1342.4401949999999</v>
       </c>
-      <c r="X15" s="25">
+      <c r="X15" s="24">
         <v>572.69519600000012</v>
       </c>
-      <c r="Y15" s="25">
+      <c r="Y15" s="24">
         <v>81.656131743459781</v>
       </c>
-      <c r="Z15" s="25">
+      <c r="Z15" s="24">
         <v>465.80742900000007</v>
       </c>
-      <c r="AA15" s="25">
+      <c r="AA15" s="24">
         <v>1996.7474259999999</v>
       </c>
-      <c r="AB15" s="25">
+      <c r="AB15" s="24">
         <v>1907.5440160000003</v>
       </c>
-      <c r="AC15" s="25">
+      <c r="AC15" s="24">
         <v>1429.8710195173235</v>
       </c>
-      <c r="AD15" s="25">
+      <c r="AD15" s="24">
         <v>2728.3951840000004</v>
       </c>
-      <c r="AE15" s="25">
+      <c r="AE15" s="24">
         <v>9672.742040000001</v>
       </c>
-      <c r="AF15" s="25">
+      <c r="AF15" s="24">
         <v>1577.8663099999999</v>
       </c>
-      <c r="AG15" s="25">
+      <c r="AG15" s="24">
         <v>860.31744361711492</v>
       </c>
-      <c r="AH15" s="25">
+      <c r="AH15" s="24">
         <v>619.69209000000001</v>
       </c>
-      <c r="AI15" s="25">
+      <c r="AI15" s="24">
         <v>3061.749264</v>
       </c>
-      <c r="AJ15" s="25">
+      <c r="AJ15" s="24">
         <v>1276.9027370000001</v>
       </c>
-      <c r="AK15" s="25">
+      <c r="AK15" s="24">
         <v>1017.5551653121819</v>
       </c>
-      <c r="AL15" s="25">
+      <c r="AL15" s="24">
         <v>403.01586800000001</v>
       </c>
-      <c r="AM15" s="25">
+      <c r="AM15" s="24">
         <v>1792.1292300000002</v>
       </c>
-      <c r="AN15" s="25">
+      <c r="AN15" s="24">
         <v>2018.9285329999998</v>
       </c>
-      <c r="AO15" s="25">
+      <c r="AO15" s="24">
         <v>1382.9574725555033</v>
       </c>
-      <c r="AP15" s="25">
+      <c r="AP15" s="24">
         <v>1610.5972710000001</v>
       </c>
-      <c r="AQ15" s="25">
+      <c r="AQ15" s="24">
         <v>4782.3414599999996</v>
       </c>
-      <c r="AR15" s="25">
+      <c r="AR15" s="24">
         <v>2140.8419000000004</v>
       </c>
-      <c r="AS15" s="25">
+      <c r="AS15" s="24">
         <v>2067.5879424376503</v>
       </c>
-      <c r="AT15" s="25">
+      <c r="AT15" s="24">
         <v>2501.2381249999999</v>
       </c>
-      <c r="AU15" s="25">
+      <c r="AU15" s="24">
         <v>6291.4223709999997</v>
       </c>
-      <c r="AV15" s="25">
+      <c r="AV15" s="24">
         <v>5014.3367069999995</v>
       </c>
-      <c r="AW15" s="25">
+      <c r="AW15" s="24">
         <v>2642.9533391865903</v>
       </c>
-      <c r="AX15" s="25">
+      <c r="AX15" s="24">
         <v>6021.4529040000007</v>
       </c>
-      <c r="AY15" s="25">
+      <c r="AY15" s="24">
         <v>13219.466725</v>
       </c>
-      <c r="AZ15" s="25">
+      <c r="AZ15" s="24">
         <v>5790.2356</v>
       </c>
-      <c r="BA15" s="25">
+      <c r="BA15" s="24">
         <v>1794.2154933203312</v>
       </c>
-      <c r="BB15" s="25">
+      <c r="BB15" s="24">
         <v>6375.5607170000003</v>
       </c>
-      <c r="BC15" s="25">
+      <c r="BC15" s="24">
         <v>10637.199186999997</v>
       </c>
-      <c r="BD15" s="25">
+      <c r="BD15" s="24">
         <v>4909.5558240000018</v>
       </c>
-      <c r="BE15" s="25">
+      <c r="BE15" s="24">
         <v>1448.4127153335778</v>
       </c>
-      <c r="BF15" s="25">
+      <c r="BF15" s="24">
         <v>6365.6553459999996</v>
       </c>
-      <c r="BG15" s="25">
+      <c r="BG15" s="24">
         <v>17449.942985999998</v>
       </c>
-      <c r="BH15" s="25">
+      <c r="BH15" s="24">
         <v>9713.292773000001</v>
       </c>
-      <c r="BI15" s="25">
+      <c r="BI15" s="24">
         <v>1988.5650584584457</v>
       </c>
-      <c r="BJ15" s="25">
+      <c r="BJ15" s="24">
         <v>6380.8247760000004</v>
       </c>
-      <c r="BK15" s="25">
+      <c r="BK15" s="24">
         <v>10919.492179999997</v>
       </c>
-      <c r="BL15" s="25">
+      <c r="BL15" s="24">
         <v>5853.276773999999</v>
       </c>
-      <c r="BM15" s="25">
+      <c r="BM15" s="24">
         <v>1159.9314659342913</v>
       </c>
-      <c r="BN15" s="25">
+      <c r="BN15" s="24">
         <v>5207.5954979999997</v>
       </c>
-      <c r="BO15" s="25">
+      <c r="BO15" s="24">
         <v>6343.5395209999988</v>
       </c>
-      <c r="BP15" s="25">
+      <c r="BP15" s="24">
         <v>3682.8855812260699</v>
       </c>
-      <c r="BQ15" s="25">
+      <c r="BQ15" s="24">
         <v>1293.4189071308401</v>
       </c>
-      <c r="BR15" s="25">
+      <c r="BR15" s="24">
         <v>3316.6052649999997</v>
       </c>
-      <c r="BS15" s="25">
+      <c r="BS15" s="24">
         <v>7678.0405419999988</v>
       </c>
-      <c r="BT15" s="25">
+      <c r="BT15" s="24">
         <v>3968.9810390000002</v>
       </c>
-      <c r="BU15" s="25">
+      <c r="BU15" s="24">
         <v>1260.6743611827308</v>
       </c>
-      <c r="BV15" s="25">
+      <c r="BV15" s="24">
         <v>3927.0776790000004</v>
       </c>
-      <c r="BW15" s="25">
+      <c r="BW15" s="24">
         <v>7130.4487939999999</v>
       </c>
-      <c r="BX15" s="25">
+      <c r="BX15" s="24">
         <v>5720.3326679999991</v>
       </c>
-      <c r="BY15" s="25">
+      <c r="BY15" s="24">
         <v>961.94272805159767</v>
       </c>
-      <c r="BZ15" s="25">
+      <c r="BZ15" s="24">
         <v>4384.275826527648</v>
       </c>
-      <c r="CA15" s="25">
+      <c r="CA15" s="24">
         <v>7976.4271108528137</v>
       </c>
-      <c r="CB15" s="25">
+      <c r="CB15" s="24">
         <v>6082.0581140000013</v>
       </c>
-      <c r="CC15" s="25">
+      <c r="CC15" s="24">
         <v>1596.8662211683732</v>
       </c>
       <c r="CD15" s="12">
@@ -3244,28 +3225,28 @@
         <v>3328.4627221109013</v>
       </c>
       <c r="CT15" s="12">
-        <v>11256.175072299757</v>
+        <v>11346.063755608031</v>
       </c>
       <c r="CU15" s="12">
-        <v>11913.897940696526</v>
+        <v>11971.811444470812</v>
       </c>
       <c r="CV15" s="12">
-        <v>8325.6231516599782</v>
+        <v>8409.3617065857143</v>
       </c>
       <c r="CW15" s="12">
-        <v>3216.7699023826717</v>
+        <v>3252.6211914047799</v>
       </c>
       <c r="CX15" s="12">
-        <v>10129.29746302537</v>
+        <v>10162.255110584607</v>
       </c>
       <c r="CY15" s="12">
-        <v>12355.738298433882</v>
+        <v>12360.372635244859</v>
       </c>
       <c r="CZ15" s="12">
-        <v>9042.0465988018714</v>
+        <v>9147.9077566122178</v>
       </c>
       <c r="DA15" s="12">
-        <v>3599.0929937348351</v>
+        <v>3722.8026198904531</v>
       </c>
       <c r="DB15" s="14"/>
       <c r="DC15" s="14"/>
@@ -3346,244 +3327,244 @@
       <c r="A16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="24">
         <v>355.66394099999997</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>329.57169100000004</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <v>425.68140100000011</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="24">
         <v>375.8972222528904</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <v>388.20773299999996</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <v>236.95257600000005</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="24">
         <v>177.94313800000003</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="24">
         <v>135.08643981715099</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="24">
         <v>531.03502999999989</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="24">
         <v>104.36611600000003</v>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="24">
         <v>109.910827</v>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="24">
         <v>145.83038965628054</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="24">
         <v>534.40676199999996</v>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="24">
         <v>168.109791</v>
       </c>
-      <c r="P16" s="25">
+      <c r="P16" s="24">
         <v>206.81622100000004</v>
       </c>
-      <c r="Q16" s="25">
+      <c r="Q16" s="24">
         <v>250.93124621457304</v>
       </c>
-      <c r="R16" s="25">
+      <c r="R16" s="24">
         <v>306.97141599999998</v>
       </c>
-      <c r="S16" s="25">
+      <c r="S16" s="24">
         <v>298.34876499999996</v>
       </c>
-      <c r="T16" s="25">
+      <c r="T16" s="24">
         <v>321.51381000000003</v>
       </c>
-      <c r="U16" s="25">
+      <c r="U16" s="24">
         <v>379.38416473451218</v>
       </c>
-      <c r="V16" s="25">
+      <c r="V16" s="24">
         <v>428.70955499999997</v>
       </c>
-      <c r="W16" s="25">
+      <c r="W16" s="24">
         <v>443.95820200000003</v>
       </c>
-      <c r="X16" s="25">
+      <c r="X16" s="24">
         <v>517.98817200000019</v>
       </c>
-      <c r="Y16" s="25">
+      <c r="Y16" s="24">
         <v>546.57110656438499</v>
       </c>
-      <c r="Z16" s="25">
+      <c r="Z16" s="24">
         <v>564.08071199999995</v>
       </c>
-      <c r="AA16" s="25">
+      <c r="AA16" s="24">
         <v>857.19552299999998</v>
       </c>
-      <c r="AB16" s="25">
+      <c r="AB16" s="24">
         <v>1000.468417</v>
       </c>
-      <c r="AC16" s="25">
+      <c r="AC16" s="24">
         <v>1079.805923537147</v>
       </c>
-      <c r="AD16" s="25">
+      <c r="AD16" s="24">
         <v>1000.4441180000001</v>
       </c>
-      <c r="AE16" s="25">
+      <c r="AE16" s="24">
         <v>1208.3690280000001</v>
       </c>
-      <c r="AF16" s="25">
+      <c r="AF16" s="24">
         <v>1207.2059690000001</v>
       </c>
-      <c r="AG16" s="25">
+      <c r="AG16" s="24">
         <v>1100.0068304992078</v>
       </c>
-      <c r="AH16" s="25">
+      <c r="AH16" s="24">
         <v>1063.632607</v>
       </c>
-      <c r="AI16" s="25">
+      <c r="AI16" s="24">
         <v>930.91614299999992</v>
       </c>
-      <c r="AJ16" s="25">
+      <c r="AJ16" s="24">
         <v>949.98829400000011</v>
       </c>
-      <c r="AK16" s="25">
+      <c r="AK16" s="24">
         <v>667.057617899506</v>
       </c>
-      <c r="AL16" s="25">
+      <c r="AL16" s="24">
         <v>1230.3391549999997</v>
       </c>
-      <c r="AM16" s="25">
+      <c r="AM16" s="24">
         <v>1388.3224070000001</v>
       </c>
-      <c r="AN16" s="25">
+      <c r="AN16" s="24">
         <v>1783.88355</v>
       </c>
-      <c r="AO16" s="25">
+      <c r="AO16" s="24">
         <v>2086.1723651016091</v>
       </c>
-      <c r="AP16" s="25">
+      <c r="AP16" s="24">
         <v>2287.8972400000002</v>
       </c>
-      <c r="AQ16" s="25">
+      <c r="AQ16" s="24">
         <v>1948.945099</v>
       </c>
-      <c r="AR16" s="25">
+      <c r="AR16" s="24">
         <v>2287.2717400000001</v>
       </c>
-      <c r="AS16" s="25">
+      <c r="AS16" s="24">
         <v>2877.6598655038215</v>
       </c>
-      <c r="AT16" s="25">
+      <c r="AT16" s="24">
         <v>2560.4841000000001</v>
       </c>
-      <c r="AU16" s="25">
+      <c r="AU16" s="24">
         <v>2689.8055169999993</v>
       </c>
-      <c r="AV16" s="25">
+      <c r="AV16" s="24">
         <v>2746.4078430000004</v>
       </c>
-      <c r="AW16" s="25">
+      <c r="AW16" s="24">
         <v>3266.9195589944784</v>
       </c>
-      <c r="AX16" s="25">
+      <c r="AX16" s="24">
         <v>2601.1592699999997</v>
       </c>
-      <c r="AY16" s="25">
+      <c r="AY16" s="24">
         <v>2498.6383019999998</v>
       </c>
-      <c r="AZ16" s="25">
+      <c r="AZ16" s="24">
         <v>1916.911239</v>
       </c>
-      <c r="BA16" s="25">
+      <c r="BA16" s="24">
         <v>1977.3809541582223</v>
       </c>
-      <c r="BB16" s="25">
+      <c r="BB16" s="24">
         <v>2247.7762479999997</v>
       </c>
-      <c r="BC16" s="25">
+      <c r="BC16" s="24">
         <v>3254.5135589999986</v>
       </c>
-      <c r="BD16" s="25">
+      <c r="BD16" s="24">
         <v>3285.8607220000004</v>
       </c>
-      <c r="BE16" s="25">
+      <c r="BE16" s="24">
         <v>4093.0487664476477</v>
       </c>
-      <c r="BF16" s="25">
+      <c r="BF16" s="24">
         <v>2927.4336219999996</v>
       </c>
-      <c r="BG16" s="25">
+      <c r="BG16" s="24">
         <v>2617.1329829999995</v>
       </c>
-      <c r="BH16" s="25">
+      <c r="BH16" s="24">
         <v>3189.3263070000003</v>
       </c>
-      <c r="BI16" s="25">
+      <c r="BI16" s="24">
         <v>3379.9172012434951</v>
       </c>
-      <c r="BJ16" s="25">
+      <c r="BJ16" s="24">
         <v>2288.457257</v>
       </c>
-      <c r="BK16" s="25">
+      <c r="BK16" s="24">
         <v>2550.0199079999988</v>
       </c>
-      <c r="BL16" s="25">
+      <c r="BL16" s="24">
         <v>2446.2752240000004</v>
       </c>
-      <c r="BM16" s="25">
+      <c r="BM16" s="24">
         <v>2938.3224269492907</v>
       </c>
-      <c r="BN16" s="25">
+      <c r="BN16" s="24">
         <v>2456.8594929999999</v>
       </c>
-      <c r="BO16" s="25">
+      <c r="BO16" s="24">
         <v>2311.2717679999996</v>
       </c>
-      <c r="BP16" s="25">
+      <c r="BP16" s="24">
         <v>2220.4267131362985</v>
       </c>
-      <c r="BQ16" s="25">
+      <c r="BQ16" s="24">
         <v>2751.6701215838198</v>
       </c>
-      <c r="BR16" s="25">
+      <c r="BR16" s="24">
         <v>2586.4193160000004</v>
       </c>
-      <c r="BS16" s="25">
+      <c r="BS16" s="24">
         <v>2254.9734820000003</v>
       </c>
-      <c r="BT16" s="25">
+      <c r="BT16" s="24">
         <v>2662.4741249999997</v>
       </c>
-      <c r="BU16" s="25">
+      <c r="BU16" s="24">
         <v>3298.5396399468509</v>
       </c>
-      <c r="BV16" s="25">
+      <c r="BV16" s="24">
         <v>2731.2978669999998</v>
       </c>
-      <c r="BW16" s="25">
+      <c r="BW16" s="24">
         <v>2678.5819220000003</v>
       </c>
-      <c r="BX16" s="25">
+      <c r="BX16" s="24">
         <v>2632.0223319999991</v>
       </c>
-      <c r="BY16" s="25">
+      <c r="BY16" s="24">
         <v>3066.1471604327398</v>
       </c>
-      <c r="BZ16" s="25">
+      <c r="BZ16" s="24">
         <v>2669.9058449999984</v>
       </c>
-      <c r="CA16" s="25">
+      <c r="CA16" s="24">
         <v>2571.8843919999995</v>
       </c>
-      <c r="CB16" s="25">
+      <c r="CB16" s="24">
         <v>2366.3566069999997</v>
       </c>
-      <c r="CC16" s="25">
+      <c r="CC16" s="24">
         <v>2620.1412887200363</v>
       </c>
       <c r="CD16" s="12">
@@ -3644,10 +3625,10 @@
         <v>3277.2071135840024</v>
       </c>
       <c r="CW16" s="12">
-        <v>6010.8616200915176</v>
+        <v>6010.8616200915167</v>
       </c>
       <c r="CX16" s="12">
-        <v>2443.5939492841512</v>
+        <v>2443.5939492841508</v>
       </c>
       <c r="CY16" s="12">
         <v>3475.8307269041043</v>
@@ -3656,7 +3637,7 @@
         <v>3848.1964303738814</v>
       </c>
       <c r="DA16" s="12">
-        <v>6184.7406244976028</v>
+        <v>5996.5149948437911</v>
       </c>
       <c r="DB16" s="14"/>
       <c r="DC16" s="14"/>
@@ -3737,244 +3718,244 @@
       <c r="A17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="24">
         <v>2011.3008409999995</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>1567.2925349999998</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="24">
         <v>1552.275873</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="24">
         <v>1709.3034109886482</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>1441.4327229999994</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>1610.8290659999998</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>1455.7912089999998</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>1814.0175065111305</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="24">
         <v>1211.1781150000002</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="24">
         <v>2019.6987619999995</v>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="24">
         <v>2439.3909469999999</v>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="24">
         <v>2564.5763193565099</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="24">
         <v>2709.6015669999997</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="24">
         <v>1641.4176990000001</v>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="24">
         <v>2023.4872810000004</v>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="24">
         <v>1889.6532626515616</v>
       </c>
-      <c r="R17" s="25">
+      <c r="R17" s="24">
         <v>2593.5764139999997</v>
       </c>
-      <c r="S17" s="25">
+      <c r="S17" s="24">
         <v>1351.2928339999999</v>
       </c>
-      <c r="T17" s="25">
+      <c r="T17" s="24">
         <v>2560.8054030000003</v>
       </c>
-      <c r="U17" s="25">
+      <c r="U17" s="24">
         <v>2281.9056976399888</v>
       </c>
-      <c r="V17" s="25">
+      <c r="V17" s="24">
         <v>3260.8266309999995</v>
       </c>
-      <c r="W17" s="25">
+      <c r="W17" s="24">
         <v>1899.7200309999998</v>
       </c>
-      <c r="X17" s="25">
+      <c r="X17" s="24">
         <v>2031.4196240000003</v>
       </c>
-      <c r="Y17" s="25">
+      <c r="Y17" s="24">
         <v>2514.5029997362717</v>
       </c>
-      <c r="Z17" s="25">
+      <c r="Z17" s="24">
         <v>3225.4220610000002</v>
       </c>
-      <c r="AA17" s="25">
+      <c r="AA17" s="24">
         <v>2139.6695719999998</v>
       </c>
-      <c r="AB17" s="25">
+      <c r="AB17" s="24">
         <v>2384.0025540000006</v>
       </c>
-      <c r="AC17" s="25">
+      <c r="AC17" s="24">
         <v>2425.8135691996317</v>
       </c>
-      <c r="AD17" s="25">
+      <c r="AD17" s="24">
         <v>3472.0688239999995</v>
       </c>
-      <c r="AE17" s="25">
+      <c r="AE17" s="24">
         <v>3249.020853</v>
       </c>
-      <c r="AF17" s="25">
+      <c r="AF17" s="24">
         <v>2434.5301720000002</v>
       </c>
-      <c r="AG17" s="25">
+      <c r="AG17" s="24">
         <v>2197.7727506456022</v>
       </c>
-      <c r="AH17" s="25">
+      <c r="AH17" s="24">
         <v>3032.4703719999998</v>
       </c>
-      <c r="AI17" s="25">
+      <c r="AI17" s="24">
         <v>2496.1001579999997</v>
       </c>
-      <c r="AJ17" s="25">
+      <c r="AJ17" s="24">
         <v>2549.7402340000003</v>
       </c>
-      <c r="AK17" s="25">
+      <c r="AK17" s="24">
         <v>2811.0398431222343</v>
       </c>
-      <c r="AL17" s="25">
+      <c r="AL17" s="24">
         <v>3948.0381430000002</v>
       </c>
-      <c r="AM17" s="25">
+      <c r="AM17" s="24">
         <v>2539.123083</v>
       </c>
-      <c r="AN17" s="25">
+      <c r="AN17" s="24">
         <v>2945.9663430000001</v>
       </c>
-      <c r="AO17" s="25">
+      <c r="AO17" s="24">
         <v>3857.7920777605855</v>
       </c>
-      <c r="AP17" s="25">
+      <c r="AP17" s="24">
         <v>4622.4037019999996</v>
       </c>
-      <c r="AQ17" s="25">
+      <c r="AQ17" s="24">
         <v>3770.1119490000001</v>
       </c>
-      <c r="AR17" s="25">
+      <c r="AR17" s="24">
         <v>3817.749546</v>
       </c>
-      <c r="AS17" s="25">
+      <c r="AS17" s="24">
         <v>3781.7964734972911</v>
       </c>
-      <c r="AT17" s="25">
+      <c r="AT17" s="24">
         <v>5974.9491709999993</v>
       </c>
-      <c r="AU17" s="25">
+      <c r="AU17" s="24">
         <v>4434.0165219999981</v>
       </c>
-      <c r="AV17" s="25">
+      <c r="AV17" s="24">
         <v>4614.9894709999999</v>
       </c>
-      <c r="AW17" s="25">
+      <c r="AW17" s="24">
         <v>4431.3425234837978</v>
       </c>
-      <c r="AX17" s="25">
+      <c r="AX17" s="24">
         <v>6061.174438</v>
       </c>
-      <c r="AY17" s="25">
+      <c r="AY17" s="24">
         <v>5133.7653329999994</v>
       </c>
-      <c r="AZ17" s="25">
+      <c r="AZ17" s="24">
         <v>4291.5703220000005</v>
       </c>
-      <c r="BA17" s="25">
+      <c r="BA17" s="24">
         <v>5308.3378715187637</v>
       </c>
-      <c r="BB17" s="25">
+      <c r="BB17" s="24">
         <v>6321.3897860000006</v>
       </c>
-      <c r="BC17" s="25">
+      <c r="BC17" s="24">
         <v>5171.5687899999984</v>
       </c>
-      <c r="BD17" s="25">
+      <c r="BD17" s="24">
         <v>5333.9299990000009</v>
       </c>
-      <c r="BE17" s="25">
+      <c r="BE17" s="24">
         <v>6481.5112175248069</v>
       </c>
-      <c r="BF17" s="25">
+      <c r="BF17" s="24">
         <v>8249.625188</v>
       </c>
-      <c r="BG17" s="25">
+      <c r="BG17" s="24">
         <v>5458.3164689999994</v>
       </c>
-      <c r="BH17" s="25">
+      <c r="BH17" s="24">
         <v>5700.885816</v>
       </c>
-      <c r="BI17" s="25">
+      <c r="BI17" s="24">
         <v>6880.3007680411647</v>
       </c>
-      <c r="BJ17" s="25">
+      <c r="BJ17" s="24">
         <v>8943.444738000002</v>
       </c>
-      <c r="BK17" s="25">
+      <c r="BK17" s="24">
         <v>5023.0832829999999</v>
       </c>
-      <c r="BL17" s="25">
+      <c r="BL17" s="24">
         <v>5948.4860659999995</v>
       </c>
-      <c r="BM17" s="25">
+      <c r="BM17" s="24">
         <v>7992.4991672757697</v>
       </c>
-      <c r="BN17" s="25">
+      <c r="BN17" s="24">
         <v>8748.0670569999984</v>
       </c>
-      <c r="BO17" s="25">
+      <c r="BO17" s="24">
         <v>5242.8996239999997</v>
       </c>
-      <c r="BP17" s="25">
+      <c r="BP17" s="24">
         <v>9337.8091495731915</v>
       </c>
-      <c r="BQ17" s="25">
+      <c r="BQ17" s="24">
         <v>10470.412216133216</v>
       </c>
-      <c r="BR17" s="25">
+      <c r="BR17" s="24">
         <v>10812.320698000001</v>
       </c>
-      <c r="BS17" s="25">
+      <c r="BS17" s="24">
         <v>8546.7906860000021</v>
       </c>
-      <c r="BT17" s="25">
+      <c r="BT17" s="24">
         <v>11574.691098999998</v>
       </c>
-      <c r="BU17" s="25">
+      <c r="BU17" s="24">
         <v>12106.338431482591</v>
       </c>
-      <c r="BV17" s="25">
+      <c r="BV17" s="24">
         <v>13011.850413999999</v>
       </c>
-      <c r="BW17" s="25">
+      <c r="BW17" s="24">
         <v>10294.746047999999</v>
       </c>
-      <c r="BX17" s="25">
+      <c r="BX17" s="24">
         <v>11525.100973999999</v>
       </c>
-      <c r="BY17" s="25">
+      <c r="BY17" s="24">
         <v>14791.356016425587</v>
       </c>
-      <c r="BZ17" s="25">
+      <c r="BZ17" s="24">
         <v>13916.247992411645</v>
       </c>
-      <c r="CA17" s="25">
+      <c r="CA17" s="24">
         <v>10358.729522924432</v>
       </c>
-      <c r="CB17" s="25">
+      <c r="CB17" s="24">
         <v>10559.020823663737</v>
       </c>
-      <c r="CC17" s="25">
+      <c r="CC17" s="24">
         <v>15450.240006454096</v>
       </c>
       <c r="CD17" s="12">
@@ -4026,28 +4007,28 @@
         <v>17050.765566466631</v>
       </c>
       <c r="CT17" s="12">
-        <v>18067.942898231897</v>
+        <v>18021.781226574501</v>
       </c>
       <c r="CU17" s="12">
-        <v>11130.027873605897</v>
+        <v>11064.979807847347</v>
       </c>
       <c r="CV17" s="12">
-        <v>16120.376113920405</v>
+        <v>16209.180837280417</v>
       </c>
       <c r="CW17" s="12">
-        <v>18144.851477763797</v>
+        <v>18172.088896201632</v>
       </c>
       <c r="CX17" s="12">
-        <v>18921.61444114129</v>
+        <v>18956.706693845685</v>
       </c>
       <c r="CY17" s="12">
-        <v>11472.440448460797</v>
+        <v>11379.180195871428</v>
       </c>
       <c r="CZ17" s="12">
-        <v>16950.09633192989</v>
+        <v>16918.356943797295</v>
       </c>
       <c r="DA17" s="12">
-        <v>18581.134060741329</v>
+        <v>18335.832749210262</v>
       </c>
       <c r="DB17" s="14"/>
       <c r="DC17" s="14"/>
@@ -4308,244 +4289,244 @@
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="25">
         <v>5773.333564999999</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="25">
         <v>5486.5136519999996</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="25">
         <v>5592.8988980000004</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="25">
         <v>6058.4857610373419</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="25">
         <v>5412.8978259999985</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="25">
         <v>6613.8201790000003</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="25">
         <v>5380.3846709999998</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="25">
         <v>5372.9169288647527</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="25">
         <v>14110.736857999997</v>
       </c>
-      <c r="K19" s="26">
+      <c r="K19" s="25">
         <v>10607.619422</v>
       </c>
-      <c r="L19" s="26">
+      <c r="L19" s="25">
         <v>8847.738308</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="25">
         <v>7771.0544319228266</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="25">
         <v>11639.959052999999</v>
       </c>
-      <c r="O19" s="26">
+      <c r="O19" s="25">
         <v>12279.204592999999</v>
       </c>
-      <c r="P19" s="26">
+      <c r="P19" s="25">
         <v>13917.011576000003</v>
       </c>
-      <c r="Q19" s="26">
+      <c r="Q19" s="25">
         <v>14549.722910960461</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="25">
         <v>14460.19994</v>
       </c>
-      <c r="S19" s="26">
+      <c r="S19" s="25">
         <v>12647.227292</v>
       </c>
-      <c r="T19" s="26">
+      <c r="T19" s="25">
         <v>14816.883520000003</v>
       </c>
-      <c r="U19" s="26">
+      <c r="U19" s="25">
         <v>13550.286877933453</v>
       </c>
-      <c r="V19" s="26">
+      <c r="V19" s="25">
         <v>15723.714653999999</v>
       </c>
-      <c r="W19" s="26">
+      <c r="W19" s="25">
         <v>18213.719883999998</v>
       </c>
-      <c r="X19" s="26">
+      <c r="X19" s="25">
         <v>19373.470104000007</v>
       </c>
-      <c r="Y19" s="26">
+      <c r="Y19" s="25">
         <v>18146.764869155024</v>
       </c>
-      <c r="Z19" s="26">
+      <c r="Z19" s="25">
         <v>18663.718786000001</v>
       </c>
-      <c r="AA19" s="26">
+      <c r="AA19" s="25">
         <v>21800.922895999993</v>
       </c>
-      <c r="AB19" s="26">
+      <c r="AB19" s="25">
         <v>21850.679750000003</v>
       </c>
-      <c r="AC19" s="26">
+      <c r="AC19" s="25">
         <v>17164.959644313341</v>
       </c>
-      <c r="AD19" s="26">
+      <c r="AD19" s="25">
         <v>24524.905559999996</v>
       </c>
-      <c r="AE19" s="26">
+      <c r="AE19" s="25">
         <v>31559.801328000001</v>
       </c>
-      <c r="AF19" s="26">
+      <c r="AF19" s="25">
         <v>23026.134339</v>
       </c>
-      <c r="AG19" s="26">
+      <c r="AG19" s="25">
         <v>19099.331533977678</v>
       </c>
-      <c r="AH19" s="26">
+      <c r="AH19" s="25">
         <v>23690.392972999998</v>
       </c>
-      <c r="AI19" s="26">
+      <c r="AI19" s="25">
         <v>26074.194833999998</v>
       </c>
-      <c r="AJ19" s="26">
+      <c r="AJ19" s="25">
         <v>26428.780494000002</v>
       </c>
-      <c r="AK19" s="26">
+      <c r="AK19" s="25">
         <v>22374.558058209201</v>
       </c>
-      <c r="AL19" s="26">
+      <c r="AL19" s="25">
         <v>24127.347289000001</v>
       </c>
-      <c r="AM19" s="26">
+      <c r="AM19" s="25">
         <v>24278.571477999998</v>
       </c>
-      <c r="AN19" s="26">
+      <c r="AN19" s="25">
         <v>30426.835996000002</v>
       </c>
-      <c r="AO19" s="26">
+      <c r="AO19" s="25">
         <v>31842.962264870748</v>
       </c>
-      <c r="AP19" s="26">
+      <c r="AP19" s="25">
         <v>27401.560022999995</v>
       </c>
-      <c r="AQ19" s="26">
+      <c r="AQ19" s="25">
         <v>36983.186796999995</v>
       </c>
-      <c r="AR19" s="26">
+      <c r="AR19" s="25">
         <v>34541.018829000001</v>
       </c>
-      <c r="AS19" s="26">
+      <c r="AS19" s="25">
         <v>36475.981022609507</v>
       </c>
-      <c r="AT19" s="26">
+      <c r="AT19" s="25">
         <v>40709.771656999998</v>
       </c>
-      <c r="AU19" s="26">
+      <c r="AU19" s="25">
         <v>46874.832732999988</v>
       </c>
-      <c r="AV19" s="26">
+      <c r="AV19" s="25">
         <v>34743.732294999994</v>
       </c>
-      <c r="AW19" s="26">
+      <c r="AW19" s="25">
         <v>29159.068383447709</v>
       </c>
-      <c r="AX19" s="26">
+      <c r="AX19" s="25">
         <v>33451.427982000001</v>
       </c>
-      <c r="AY19" s="26">
+      <c r="AY19" s="25">
         <v>42164.550997999992</v>
       </c>
-      <c r="AZ19" s="26">
+      <c r="AZ19" s="25">
         <v>29227.770904000001</v>
       </c>
-      <c r="BA19" s="26">
+      <c r="BA19" s="25">
         <v>26922.776882267495</v>
       </c>
-      <c r="BB19" s="26">
+      <c r="BB19" s="25">
         <v>30673.743886</v>
       </c>
-      <c r="BC19" s="26">
+      <c r="BC19" s="25">
         <v>37313.197445999991</v>
       </c>
-      <c r="BD19" s="26">
+      <c r="BD19" s="25">
         <v>31127.917166000007</v>
       </c>
-      <c r="BE19" s="26">
+      <c r="BE19" s="25">
         <v>27338.630795429359</v>
       </c>
-      <c r="BF19" s="26">
+      <c r="BF19" s="25">
         <v>37147.479509999997</v>
       </c>
-      <c r="BG19" s="26">
+      <c r="BG19" s="25">
         <v>44753.613130999991</v>
       </c>
-      <c r="BH19" s="26">
+      <c r="BH19" s="25">
         <v>33547.190030999998</v>
       </c>
-      <c r="BI19" s="26">
+      <c r="BI19" s="25">
         <v>28432.170956692891</v>
       </c>
-      <c r="BJ19" s="26">
+      <c r="BJ19" s="25">
         <v>31983.863260000002</v>
       </c>
-      <c r="BK19" s="26">
+      <c r="BK19" s="25">
         <v>33088.275179999997</v>
       </c>
-      <c r="BL19" s="26">
+      <c r="BL19" s="25">
         <v>27534.603748000001</v>
       </c>
-      <c r="BM19" s="26">
+      <c r="BM19" s="25">
         <v>27019.727304671287</v>
       </c>
-      <c r="BN19" s="26">
+      <c r="BN19" s="25">
         <v>32862.799462999996</v>
       </c>
-      <c r="BO19" s="26">
+      <c r="BO19" s="25">
         <v>30657.450394999993</v>
       </c>
-      <c r="BP19" s="26">
+      <c r="BP19" s="25">
         <v>32583.792230000116</v>
       </c>
-      <c r="BQ19" s="26">
+      <c r="BQ19" s="25">
         <v>29793.483863000019</v>
       </c>
-      <c r="BR19" s="26">
+      <c r="BR19" s="25">
         <v>34468.231487999998</v>
       </c>
-      <c r="BS19" s="26">
+      <c r="BS19" s="25">
         <v>38890.139191000002</v>
       </c>
-      <c r="BT19" s="26">
+      <c r="BT19" s="25">
         <v>39470.391541999998</v>
       </c>
-      <c r="BU19" s="26">
+      <c r="BU19" s="25">
         <v>35265.120303559321</v>
       </c>
-      <c r="BV19" s="26">
+      <c r="BV19" s="25">
         <v>40943.905601000006</v>
       </c>
-      <c r="BW19" s="26">
+      <c r="BW19" s="25">
         <v>43539.126177999999</v>
       </c>
-      <c r="BX19" s="26">
+      <c r="BX19" s="25">
         <v>40309.793120999995</v>
       </c>
-      <c r="BY19" s="26">
+      <c r="BY19" s="25">
         <v>38529.663686296073</v>
       </c>
-      <c r="BZ19" s="26">
+      <c r="BZ19" s="25">
         <v>42686.895182298838</v>
       </c>
-      <c r="CA19" s="26">
+      <c r="CA19" s="25">
         <v>45186.863496303769</v>
       </c>
-      <c r="CB19" s="26">
+      <c r="CB19" s="25">
         <v>37188.626399474917</v>
       </c>
-      <c r="CC19" s="26">
+      <c r="CC19" s="25">
         <v>36593.987995486015</v>
       </c>
       <c r="CD19" s="16">
@@ -4597,28 +4578,28 @@
         <v>52411.950986839634</v>
       </c>
       <c r="CT19" s="16">
-        <v>58472.661681303143</v>
+        <v>58516.388692954024</v>
       </c>
       <c r="CU19" s="16">
-        <v>61013.799783498129</v>
+        <v>61018.63711405974</v>
       </c>
       <c r="CV19" s="16">
-        <v>60275.56864690096</v>
+        <v>60446.32794427163</v>
       </c>
       <c r="CW19" s="16">
-        <v>54110.583570137933</v>
+        <v>54185.159645333479</v>
       </c>
       <c r="CX19" s="16">
-        <v>67810.603805560939</v>
+        <v>67934.18159547809</v>
       </c>
       <c r="CY19" s="16">
-        <v>65563.60677686242</v>
+        <v>65540.40571709862</v>
       </c>
       <c r="CZ19" s="16">
-        <v>68504.107131688128</v>
+        <v>68675.125481215058</v>
       </c>
       <c r="DA19" s="16">
-        <v>63009.603266472455</v>
+        <v>62933.043175214545</v>
       </c>
       <c r="DB19" s="14"/>
       <c r="DC19" s="14"/>
@@ -5179,7 +5160,7 @@
     </row>
     <row r="26" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -5190,7 +5171,7 @@
     </row>
     <row r="29" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -5201,162 +5182,162 @@
     <row r="31" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="32" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="22">
+      <c r="B32" s="30">
         <v>2000</v>
       </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22">
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30">
         <v>2001</v>
       </c>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22">
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30">
         <v>2002</v>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22">
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30">
         <v>2003</v>
       </c>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22">
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30">
         <v>2004</v>
       </c>
-      <c r="S32" s="22"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22">
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30">
         <v>2005</v>
       </c>
-      <c r="W32" s="22"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="22">
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30">
         <v>2006</v>
       </c>
-      <c r="AA32" s="22"/>
-      <c r="AB32" s="22"/>
-      <c r="AC32" s="22"/>
-      <c r="AD32" s="22">
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30">
         <v>2007</v>
       </c>
-      <c r="AE32" s="22"/>
-      <c r="AF32" s="22"/>
-      <c r="AG32" s="22"/>
-      <c r="AH32" s="22">
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30">
         <v>2008</v>
       </c>
-      <c r="AI32" s="22"/>
-      <c r="AJ32" s="22"/>
-      <c r="AK32" s="22"/>
-      <c r="AL32" s="22">
+      <c r="AI32" s="30"/>
+      <c r="AJ32" s="30"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="30">
         <v>2009</v>
       </c>
-      <c r="AM32" s="22"/>
-      <c r="AN32" s="22"/>
-      <c r="AO32" s="22"/>
-      <c r="AP32" s="22">
+      <c r="AM32" s="30"/>
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="30"/>
+      <c r="AP32" s="30">
         <v>2010</v>
       </c>
-      <c r="AQ32" s="22"/>
-      <c r="AR32" s="22"/>
-      <c r="AS32" s="22"/>
-      <c r="AT32" s="22">
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="30"/>
+      <c r="AS32" s="30"/>
+      <c r="AT32" s="30">
         <v>2011</v>
       </c>
-      <c r="AU32" s="22"/>
-      <c r="AV32" s="22"/>
-      <c r="AW32" s="22"/>
-      <c r="AX32" s="22">
+      <c r="AU32" s="30"/>
+      <c r="AV32" s="30"/>
+      <c r="AW32" s="30"/>
+      <c r="AX32" s="30">
         <v>2012</v>
       </c>
-      <c r="AY32" s="22"/>
-      <c r="AZ32" s="22"/>
-      <c r="BA32" s="22"/>
-      <c r="BB32" s="22">
+      <c r="AY32" s="30"/>
+      <c r="AZ32" s="30"/>
+      <c r="BA32" s="30"/>
+      <c r="BB32" s="30">
         <v>2013</v>
       </c>
-      <c r="BC32" s="22"/>
-      <c r="BD32" s="22"/>
-      <c r="BE32" s="22"/>
-      <c r="BF32" s="22">
+      <c r="BC32" s="30"/>
+      <c r="BD32" s="30"/>
+      <c r="BE32" s="30"/>
+      <c r="BF32" s="30">
         <v>2014</v>
       </c>
-      <c r="BG32" s="22"/>
-      <c r="BH32" s="22"/>
-      <c r="BI32" s="22"/>
-      <c r="BJ32" s="22">
+      <c r="BG32" s="30"/>
+      <c r="BH32" s="30"/>
+      <c r="BI32" s="30"/>
+      <c r="BJ32" s="30">
         <v>2015</v>
       </c>
-      <c r="BK32" s="22"/>
-      <c r="BL32" s="22"/>
-      <c r="BM32" s="22"/>
-      <c r="BN32" s="22">
+      <c r="BK32" s="30"/>
+      <c r="BL32" s="30"/>
+      <c r="BM32" s="30"/>
+      <c r="BN32" s="30">
         <v>2016</v>
       </c>
-      <c r="BO32" s="22"/>
-      <c r="BP32" s="22"/>
-      <c r="BQ32" s="22"/>
-      <c r="BR32" s="22">
+      <c r="BO32" s="30"/>
+      <c r="BP32" s="30"/>
+      <c r="BQ32" s="30"/>
+      <c r="BR32" s="30">
         <v>2017</v>
       </c>
-      <c r="BS32" s="22"/>
-      <c r="BT32" s="22"/>
-      <c r="BU32" s="22"/>
-      <c r="BV32" s="22">
+      <c r="BS32" s="30"/>
+      <c r="BT32" s="30"/>
+      <c r="BU32" s="30"/>
+      <c r="BV32" s="30">
         <v>2018</v>
       </c>
-      <c r="BW32" s="22"/>
-      <c r="BX32" s="22"/>
-      <c r="BY32" s="22"/>
-      <c r="BZ32" s="22">
+      <c r="BW32" s="30"/>
+      <c r="BX32" s="30"/>
+      <c r="BY32" s="30"/>
+      <c r="BZ32" s="30">
         <v>2019</v>
       </c>
-      <c r="CA32" s="22"/>
-      <c r="CB32" s="22"/>
-      <c r="CC32" s="22"/>
-      <c r="CD32" s="22">
+      <c r="CA32" s="30"/>
+      <c r="CB32" s="30"/>
+      <c r="CC32" s="30"/>
+      <c r="CD32" s="30">
         <v>2020</v>
       </c>
-      <c r="CE32" s="22"/>
-      <c r="CF32" s="22"/>
-      <c r="CG32" s="22"/>
-      <c r="CH32" s="23">
+      <c r="CE32" s="30"/>
+      <c r="CF32" s="30"/>
+      <c r="CG32" s="30"/>
+      <c r="CH32" s="22">
         <v>2021</v>
       </c>
-      <c r="CI32" s="23"/>
-      <c r="CJ32" s="23"/>
-      <c r="CK32" s="23"/>
-      <c r="CL32" s="24">
+      <c r="CI32" s="22"/>
+      <c r="CJ32" s="22"/>
+      <c r="CK32" s="22"/>
+      <c r="CL32" s="23">
         <v>2022</v>
       </c>
-      <c r="CM32" s="24"/>
-      <c r="CN32" s="24"/>
-      <c r="CO32" s="24"/>
-      <c r="CP32" s="28">
+      <c r="CM32" s="23"/>
+      <c r="CN32" s="23"/>
+      <c r="CO32" s="23"/>
+      <c r="CP32" s="26">
         <v>2023</v>
       </c>
-      <c r="CQ32" s="28"/>
-      <c r="CR32" s="28"/>
-      <c r="CS32" s="28"/>
-      <c r="CT32" s="28">
+      <c r="CQ32" s="26"/>
+      <c r="CR32" s="26"/>
+      <c r="CS32" s="26"/>
+      <c r="CT32" s="26">
         <v>2024</v>
       </c>
-      <c r="CU32" s="28"/>
-      <c r="CV32" s="28"/>
-      <c r="CW32" s="28"/>
-      <c r="CX32" s="28">
+      <c r="CU32" s="26"/>
+      <c r="CV32" s="26"/>
+      <c r="CW32" s="26"/>
+      <c r="CX32" s="26">
         <v>2025</v>
       </c>
-      <c r="CY32" s="28"/>
-      <c r="CZ32" s="28"/>
-      <c r="DA32" s="28"/>
+      <c r="CY32" s="26"/>
+      <c r="CZ32" s="26"/>
+      <c r="DA32" s="26"/>
     </row>
     <row r="33" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
@@ -5682,244 +5663,244 @@
       <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="24">
         <v>1325.9619250487733</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="24">
         <v>1658.0341501061268</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="24">
         <v>1050.9577630715739</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="24">
         <v>914.04669559063882</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="24">
         <v>942.41825928849175</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="24">
         <v>863.75426766652174</v>
       </c>
-      <c r="H35" s="25">
+      <c r="H35" s="24">
         <v>448.37719122319299</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="24">
         <v>686.98890038135789</v>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="24">
         <v>1139.710822262962</v>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="24">
         <v>1792.6933665836214</v>
       </c>
-      <c r="L35" s="25">
+      <c r="L35" s="24">
         <v>767.42055330258324</v>
       </c>
-      <c r="M35" s="25">
+      <c r="M35" s="24">
         <v>963.68433356325465</v>
       </c>
-      <c r="N35" s="25">
+      <c r="N35" s="24">
         <v>1339.5176533176998</v>
       </c>
-      <c r="O35" s="25">
+      <c r="O35" s="24">
         <v>2234.0836859832448</v>
       </c>
-      <c r="P35" s="25">
+      <c r="P35" s="24">
         <v>726.03244444183031</v>
       </c>
-      <c r="Q35" s="25">
+      <c r="Q35" s="24">
         <v>660.23324338752502</v>
       </c>
-      <c r="R35" s="25">
+      <c r="R35" s="24">
         <v>1788.8343246503291</v>
       </c>
-      <c r="S35" s="25">
+      <c r="S35" s="24">
         <v>1942.2542604892128</v>
       </c>
-      <c r="T35" s="25">
+      <c r="T35" s="24">
         <v>927.52388682244793</v>
       </c>
-      <c r="U35" s="25">
+      <c r="U35" s="24">
         <v>1092.0630052151578</v>
       </c>
-      <c r="V35" s="25">
+      <c r="V35" s="24">
         <v>1612.9188639139998</v>
       </c>
-      <c r="W35" s="25">
+      <c r="W35" s="24">
         <v>1793.0577473407379</v>
       </c>
-      <c r="X35" s="25">
+      <c r="X35" s="24">
         <v>702.03238729853013</v>
       </c>
-      <c r="Y35" s="25">
+      <c r="Y35" s="24">
         <v>2002.5139135474938</v>
       </c>
-      <c r="Z35" s="25">
+      <c r="Z35" s="24">
         <v>1581.2370032847064</v>
       </c>
-      <c r="AA35" s="25">
+      <c r="AA35" s="24">
         <v>2126.8122087441229</v>
       </c>
-      <c r="AB35" s="25">
+      <c r="AB35" s="24">
         <v>696.02987728288986</v>
       </c>
-      <c r="AC35" s="25">
+      <c r="AC35" s="24">
         <v>925.10811869975407</v>
       </c>
-      <c r="AD35" s="25">
+      <c r="AD35" s="24">
         <v>1500.8823347492284</v>
       </c>
-      <c r="AE35" s="25">
+      <c r="AE35" s="24">
         <v>3070.6030015028332</v>
       </c>
-      <c r="AF35" s="25">
+      <c r="AF35" s="24">
         <v>875.63774368576753</v>
       </c>
-      <c r="AG35" s="25">
+      <c r="AG35" s="24">
         <v>1339.8603811406119</v>
       </c>
-      <c r="AH35" s="25">
+      <c r="AH35" s="24">
         <v>2056.6017158445957</v>
       </c>
-      <c r="AI35" s="25">
+      <c r="AI35" s="24">
         <v>2412.0644820925445</v>
       </c>
-      <c r="AJ35" s="25">
+      <c r="AJ35" s="24">
         <v>949.26863986100102</v>
       </c>
-      <c r="AK35" s="25">
+      <c r="AK35" s="24">
         <v>1552.0401288211719</v>
       </c>
-      <c r="AL35" s="25">
+      <c r="AL35" s="24">
         <v>2786.3312343309381</v>
       </c>
-      <c r="AM35" s="25">
+      <c r="AM35" s="24">
         <v>2740.106705233422</v>
       </c>
-      <c r="AN35" s="25">
+      <c r="AN35" s="24">
         <v>1257.4240465171088</v>
       </c>
-      <c r="AO35" s="25">
+      <c r="AO35" s="24">
         <v>2051.8223350858734</v>
       </c>
-      <c r="AP35" s="25">
+      <c r="AP35" s="24">
         <v>3118.2034237564235</v>
       </c>
-      <c r="AQ35" s="25">
+      <c r="AQ35" s="24">
         <v>4259.5315223440066</v>
       </c>
-      <c r="AR35" s="25">
+      <c r="AR35" s="24">
         <v>1452.4508120362559</v>
       </c>
-      <c r="AS35" s="25">
+      <c r="AS35" s="24">
         <v>2161.8496109704884</v>
       </c>
-      <c r="AT35" s="25">
+      <c r="AT35" s="24">
         <v>3869.329370145957</v>
       </c>
-      <c r="AU35" s="25">
+      <c r="AU35" s="24">
         <v>4425.0000738543422</v>
       </c>
-      <c r="AV35" s="25">
+      <c r="AV35" s="24">
         <v>1595.6876371526723</v>
       </c>
-      <c r="AW35" s="25">
+      <c r="AW35" s="24">
         <v>2364.9993404793449</v>
       </c>
-      <c r="AX35" s="25">
+      <c r="AX35" s="24">
         <v>3492.8192590703625</v>
       </c>
-      <c r="AY35" s="25">
+      <c r="AY35" s="24">
         <v>5081.9151609990304</v>
       </c>
-      <c r="AZ35" s="25">
+      <c r="AZ35" s="24">
         <v>1598.3849495874022</v>
       </c>
-      <c r="BA35" s="25">
+      <c r="BA35" s="24">
         <v>2581.9429091572356</v>
       </c>
-      <c r="BB35" s="25">
+      <c r="BB35" s="24">
         <v>1471.5032540181724</v>
       </c>
-      <c r="BC35" s="25">
+      <c r="BC35" s="24">
         <v>5186.1593571306694</v>
       </c>
-      <c r="BD35" s="25">
+      <c r="BD35" s="24">
         <v>1832.6763764411805</v>
       </c>
-      <c r="BE35" s="25">
+      <c r="BE35" s="24">
         <v>2990.1029019854395</v>
       </c>
-      <c r="BF35" s="25">
+      <c r="BF35" s="24">
         <v>4195.1689508908921</v>
       </c>
-      <c r="BG35" s="25">
+      <c r="BG35" s="24">
         <v>6001.3245246101096</v>
       </c>
-      <c r="BH35" s="25">
+      <c r="BH35" s="24">
         <v>2260.8354604991787</v>
       </c>
-      <c r="BI35" s="25">
+      <c r="BI35" s="24">
         <v>1316.7894271042371</v>
       </c>
-      <c r="BJ35" s="25">
+      <c r="BJ35" s="24">
         <v>4185.1858339657701</v>
       </c>
-      <c r="BK35" s="25">
+      <c r="BK35" s="24">
         <v>4548.3225616918935</v>
       </c>
-      <c r="BL35" s="25">
+      <c r="BL35" s="24">
         <v>1836.8804647799552</v>
       </c>
-      <c r="BM35" s="25">
+      <c r="BM35" s="24">
         <v>3403.0730005435803</v>
       </c>
-      <c r="BN35" s="25">
+      <c r="BN35" s="24">
         <v>5739.3717399345633</v>
       </c>
-      <c r="BO35" s="25">
+      <c r="BO35" s="24">
         <v>3866.9295415848055</v>
       </c>
-      <c r="BP35" s="25">
+      <c r="BP35" s="24">
         <v>4208.6180046626587</v>
       </c>
-      <c r="BQ35" s="25">
+      <c r="BQ35" s="24">
         <v>4753.7374939794181</v>
       </c>
-      <c r="BR35" s="25">
+      <c r="BR35" s="24">
         <v>5988.8585918428253</v>
       </c>
-      <c r="BS35" s="25">
+      <c r="BS35" s="24">
         <v>6719.9255013449501</v>
       </c>
-      <c r="BT35" s="25">
+      <c r="BT35" s="24">
         <v>4199.8906435571735</v>
       </c>
-      <c r="BU35" s="25">
+      <c r="BU35" s="24">
         <v>4649.9114896652563</v>
       </c>
-      <c r="BV35" s="25">
+      <c r="BV35" s="24">
         <v>6738.6257852508325</v>
       </c>
-      <c r="BW35" s="25">
+      <c r="BW35" s="24">
         <v>5867.4910648546538</v>
       </c>
-      <c r="BX35" s="25">
+      <c r="BX35" s="24">
         <v>2503.8926202042612</v>
       </c>
-      <c r="BY35" s="25">
+      <c r="BY35" s="24">
         <v>5954.4905432996366</v>
       </c>
-      <c r="BZ35" s="25">
+      <c r="BZ35" s="24">
         <v>6625.6376656000239</v>
       </c>
-      <c r="CA35" s="25">
+      <c r="CA35" s="24">
         <v>8198.4844587195075</v>
       </c>
-      <c r="CB35" s="25">
+      <c r="CB35" s="24">
         <v>3389.4773479978817</v>
       </c>
-      <c r="CC35" s="25">
+      <c r="CC35" s="24">
         <v>5256.8028553051563</v>
       </c>
       <c r="CD35" s="12">
@@ -5974,25 +5955,25 @@
         <v>8622.8568957456064</v>
       </c>
       <c r="CU35" s="12">
-        <v>10286.551445226913</v>
+        <v>10297.386308143201</v>
       </c>
       <c r="CV35" s="12">
-        <v>3412.0620506736282</v>
+        <v>3411.4607429880325</v>
       </c>
       <c r="CW35" s="12">
         <v>4079.7479540459672</v>
       </c>
       <c r="CX35" s="12">
-        <v>9616.3386955633359</v>
+        <v>9616.3386955633378</v>
       </c>
       <c r="CY35" s="12">
-        <v>10889.847518595509</v>
+        <v>10950.079601080774</v>
       </c>
       <c r="CZ35" s="12">
-        <v>4370.1128421913127</v>
+        <v>4397.2045873834159</v>
       </c>
       <c r="DA35" s="12">
-        <v>6515.3363360740532</v>
+        <v>6681.9008708265374</v>
       </c>
       <c r="DB35" s="14"/>
       <c r="DC35" s="14"/>
@@ -6073,244 +6054,244 @@
       <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="24">
         <v>3.1867291917811693</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="24">
         <v>28.5124105707695</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="24">
         <v>157.71016833953834</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="24">
         <v>446.54227954705624</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="24">
         <v>630.80378134560613</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="24">
         <v>945.75779599417888</v>
       </c>
-      <c r="H36" s="25">
+      <c r="H36" s="24">
         <v>436.21701702134783</v>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="24">
         <v>321.0146725354806</v>
       </c>
-      <c r="J36" s="25">
+      <c r="J36" s="24">
         <v>13019.652939464169</v>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="24">
         <v>6220.7648290138832</v>
       </c>
-      <c r="L36" s="25">
+      <c r="L36" s="24">
         <v>2255.7572267724299</v>
       </c>
-      <c r="M36" s="25">
+      <c r="M36" s="24">
         <v>1241.5301712913672</v>
       </c>
-      <c r="N36" s="25">
+      <c r="N36" s="24">
         <v>3728.6824316505158</v>
       </c>
-      <c r="O36" s="25">
+      <c r="O36" s="24">
         <v>8398.7710734014781</v>
       </c>
-      <c r="P36" s="25">
+      <c r="P36" s="24">
         <v>9155.0699223050196</v>
       </c>
-      <c r="Q36" s="25">
+      <c r="Q36" s="24">
         <v>8399.5539149569067</v>
       </c>
-      <c r="R36" s="25">
+      <c r="R36" s="24">
         <v>6615.8968150543897</v>
       </c>
-      <c r="S36" s="25">
+      <c r="S36" s="24">
         <v>10905.431405203955</v>
       </c>
-      <c r="T36" s="25">
+      <c r="T36" s="24">
         <v>4572.130072677227</v>
       </c>
-      <c r="U36" s="25">
+      <c r="U36" s="24">
         <v>4875.7254943996131</v>
       </c>
-      <c r="V36" s="25">
+      <c r="V36" s="24">
         <v>7393.4825995894616</v>
       </c>
-      <c r="W36" s="25">
+      <c r="W36" s="24">
         <v>13441.775082619846</v>
       </c>
-      <c r="X36" s="25">
+      <c r="X36" s="24">
         <v>6548.4144763414097</v>
       </c>
-      <c r="Y36" s="25">
+      <c r="Y36" s="24">
         <v>7684.878017594292</v>
       </c>
-      <c r="Z36" s="25">
+      <c r="Z36" s="24">
         <v>7071.4562267657484</v>
       </c>
-      <c r="AA36" s="25">
+      <c r="AA36" s="24">
         <v>12789.228114431749</v>
       </c>
-      <c r="AB36" s="25">
+      <c r="AB36" s="24">
         <v>7038.0296483988768</v>
       </c>
-      <c r="AC36" s="25">
+      <c r="AC36" s="24">
         <v>5549.7312615916489</v>
       </c>
-      <c r="AD36" s="25">
+      <c r="AD36" s="24">
         <v>8926.5459091342382</v>
       </c>
-      <c r="AE36" s="25">
+      <c r="AE36" s="24">
         <v>15093.639154732184</v>
       </c>
-      <c r="AF36" s="25">
+      <c r="AF36" s="24">
         <v>7028.8910209462983</v>
       </c>
-      <c r="AG36" s="25">
+      <c r="AG36" s="24">
         <v>6842.5716386938448</v>
       </c>
-      <c r="AH36" s="25">
+      <c r="AH36" s="24">
         <v>8620.6073379901754</v>
       </c>
-      <c r="AI36" s="25">
+      <c r="AI36" s="24">
         <v>14340.724578200041</v>
       </c>
-      <c r="AJ36" s="25">
+      <c r="AJ36" s="24">
         <v>7600.6471715045454</v>
       </c>
-      <c r="AK36" s="25">
+      <c r="AK36" s="24">
         <v>9625.5415022047346</v>
       </c>
-      <c r="AL36" s="25">
+      <c r="AL36" s="24">
         <v>7517.7691889304915</v>
       </c>
-      <c r="AM36" s="25">
+      <c r="AM36" s="24">
         <v>19147.239860046491</v>
       </c>
-      <c r="AN36" s="25">
+      <c r="AN36" s="24">
         <v>6938.787574282791</v>
       </c>
-      <c r="AO36" s="25">
+      <c r="AO36" s="24">
         <v>9150.3254625590289</v>
       </c>
-      <c r="AP36" s="25">
+      <c r="AP36" s="24">
         <v>5405.8956293426236</v>
       </c>
-      <c r="AQ36" s="25">
+      <c r="AQ36" s="24">
         <v>18459.094449442731</v>
       </c>
-      <c r="AR36" s="25">
+      <c r="AR36" s="24">
         <v>7428.8187837317446</v>
       </c>
-      <c r="AS36" s="25">
+      <c r="AS36" s="24">
         <v>8636.4409103570706</v>
       </c>
-      <c r="AT36" s="25">
+      <c r="AT36" s="24">
         <v>7132.2609296712144</v>
       </c>
-      <c r="AU36" s="25">
+      <c r="AU36" s="24">
         <v>18234.61550477608</v>
       </c>
-      <c r="AV36" s="25">
+      <c r="AV36" s="24">
         <v>7825.6523015706616</v>
       </c>
-      <c r="AW36" s="25">
+      <c r="AW36" s="24">
         <v>8598.3791378471215</v>
       </c>
-      <c r="AX36" s="25">
+      <c r="AX36" s="24">
         <v>7684.0122235167482</v>
       </c>
-      <c r="AY36" s="25">
+      <c r="AY36" s="24">
         <v>18719.586333781415</v>
       </c>
-      <c r="AZ36" s="25">
+      <c r="AZ36" s="24">
         <v>6224.1914462280583</v>
       </c>
-      <c r="BA36" s="25">
+      <c r="BA36" s="24">
         <v>8142.0206904253891</v>
       </c>
-      <c r="BB36" s="25">
+      <c r="BB36" s="24">
         <v>7595.7857259473485</v>
       </c>
-      <c r="BC36" s="25">
+      <c r="BC36" s="24">
         <v>17211.421216426344</v>
       </c>
-      <c r="BD36" s="25">
+      <c r="BD36" s="24">
         <v>6315.9684641818858</v>
       </c>
-      <c r="BE36" s="25">
+      <c r="BE36" s="24">
         <v>5524.6730209085927</v>
       </c>
-      <c r="BF36" s="25">
+      <c r="BF36" s="24">
         <v>7387.4504176913579</v>
       </c>
-      <c r="BG36" s="25">
+      <c r="BG36" s="24">
         <v>17537.286438749423</v>
       </c>
-      <c r="BH36" s="25">
+      <c r="BH36" s="24">
         <v>4861.1488147120053</v>
       </c>
-      <c r="BI36" s="25">
+      <c r="BI36" s="24">
         <v>8188.683376655782</v>
       </c>
-      <c r="BJ36" s="25">
+      <c r="BJ36" s="24">
         <v>5925.5734520992864</v>
       </c>
-      <c r="BK36" s="25">
+      <c r="BK36" s="24">
         <v>16684.50195293807</v>
       </c>
-      <c r="BL36" s="25">
+      <c r="BL36" s="24">
         <v>5080.3473889834577</v>
       </c>
-      <c r="BM36" s="25">
+      <c r="BM36" s="24">
         <v>8243.5733736772381</v>
       </c>
-      <c r="BN36" s="25">
+      <c r="BN36" s="24">
         <v>7788.6344842029457</v>
       </c>
-      <c r="BO36" s="25">
+      <c r="BO36" s="24">
         <v>18635.905823589572</v>
       </c>
-      <c r="BP36" s="25">
+      <c r="BP36" s="24">
         <v>4834.1525973864946</v>
       </c>
-      <c r="BQ36" s="25">
+      <c r="BQ36" s="24">
         <v>7433.7050827961493</v>
       </c>
-      <c r="BR36" s="25">
+      <c r="BR36" s="24">
         <v>5497.2062148778323</v>
       </c>
-      <c r="BS36" s="25">
+      <c r="BS36" s="24">
         <v>17797.341728554671</v>
       </c>
-      <c r="BT36" s="25">
+      <c r="BT36" s="24">
         <v>5491.6265026490219</v>
       </c>
-      <c r="BU36" s="25">
+      <c r="BU36" s="24">
         <v>7909.7003599946465</v>
       </c>
-      <c r="BV36" s="25">
+      <c r="BV36" s="24">
         <v>7459.2799484336674</v>
       </c>
-      <c r="BW36" s="25">
+      <c r="BW36" s="24">
         <v>18006.576315989703</v>
       </c>
-      <c r="BX36" s="25">
+      <c r="BX36" s="24">
         <v>5166.2212481271745</v>
       </c>
-      <c r="BY36" s="25">
+      <c r="BY36" s="24">
         <v>8083.8618232091194</v>
       </c>
-      <c r="BZ36" s="25">
+      <c r="BZ36" s="24">
         <v>7772.7515855259871</v>
       </c>
-      <c r="CA36" s="25">
+      <c r="CA36" s="24">
         <v>20076.000130750595</v>
       </c>
-      <c r="CB36" s="25">
+      <c r="CB36" s="24">
         <v>4817.6391890854165</v>
       </c>
-      <c r="CC36" s="25">
+      <c r="CC36" s="24">
         <v>7587.4100950403681</v>
       </c>
       <c r="CD36" s="12">
@@ -6365,7 +6346,7 @@
         <v>4028.8949373389642</v>
       </c>
       <c r="CU36" s="12">
-        <v>8410.6507946779657</v>
+        <v>8410.6507946779639</v>
       </c>
       <c r="CV36" s="12">
         <v>2452.5537263063347</v>
@@ -6377,13 +6358,13 @@
         <v>3427.8754539324013</v>
       </c>
       <c r="CY36" s="12">
-        <v>6839.5342754944531</v>
+        <v>6839.4268564360973</v>
       </c>
       <c r="CZ36" s="12">
         <v>2379.2364750780257</v>
       </c>
       <c r="DA36" s="12">
-        <v>2682.824939658582</v>
+        <v>2731.9805695235727</v>
       </c>
       <c r="DB36" s="14"/>
       <c r="DC36" s="14"/>
@@ -6464,244 +6445,244 @@
       <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="24">
         <v>9942.1248366084674</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="24">
         <v>7935.519664370855</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="24">
         <v>9637.4625717962663</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="24">
         <v>11718.97662792066</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="24">
         <v>8570.0907428792689</v>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="24">
         <v>10756.082216377537</v>
       </c>
-      <c r="H37" s="25">
+      <c r="H37" s="24">
         <v>9375.5728427072609</v>
       </c>
-      <c r="I37" s="25">
+      <c r="I37" s="24">
         <v>9681.2070548964821</v>
       </c>
-      <c r="J37" s="25">
+      <c r="J37" s="24">
         <v>10399.178059967877</v>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="24">
         <v>10301.322737221661</v>
       </c>
-      <c r="L37" s="25">
+      <c r="L37" s="24">
         <v>10667.980227006274</v>
       </c>
-      <c r="M37" s="25">
+      <c r="M37" s="24">
         <v>10201.23608648628</v>
       </c>
-      <c r="N37" s="25">
+      <c r="N37" s="24">
         <v>9886.4702697768225</v>
       </c>
-      <c r="O37" s="25">
+      <c r="O37" s="24">
         <v>10290.752584708027</v>
       </c>
-      <c r="P37" s="25">
+      <c r="P37" s="24">
         <v>12473.084745652626</v>
       </c>
-      <c r="Q37" s="25">
+      <c r="Q37" s="24">
         <v>11919.699543353305</v>
       </c>
-      <c r="R37" s="25">
+      <c r="R37" s="24">
         <v>10517.514220224239</v>
       </c>
-      <c r="S37" s="25">
+      <c r="S37" s="24">
         <v>8633.7716235434073</v>
       </c>
-      <c r="T37" s="25">
+      <c r="T37" s="24">
         <v>10807.100314489278</v>
       </c>
-      <c r="U37" s="25">
+      <c r="U37" s="24">
         <v>11913.80350490096</v>
       </c>
-      <c r="V37" s="25">
+      <c r="V37" s="24">
         <v>10169.504347290509</v>
       </c>
-      <c r="W37" s="25">
+      <c r="W37" s="24">
         <v>11334.323286173056</v>
       </c>
-      <c r="X37" s="25">
+      <c r="X37" s="24">
         <v>11863.335776804981</v>
       </c>
-      <c r="Y37" s="25">
+      <c r="Y37" s="24">
         <v>11404.051075066471</v>
       </c>
-      <c r="Z37" s="25">
+      <c r="Z37" s="24">
         <v>11653.336283542727</v>
       </c>
-      <c r="AA37" s="25">
+      <c r="AA37" s="24">
         <v>11013.272947113635</v>
       </c>
-      <c r="AB37" s="25">
+      <c r="AB37" s="24">
         <v>9016.5872871694501</v>
       </c>
-      <c r="AC37" s="25">
+      <c r="AC37" s="24">
         <v>10560.686171098645</v>
       </c>
-      <c r="AD37" s="25">
+      <c r="AD37" s="24">
         <v>12055.141988069767</v>
       </c>
-      <c r="AE37" s="25">
+      <c r="AE37" s="24">
         <v>9690.0129115656764</v>
       </c>
-      <c r="AF37" s="25">
+      <c r="AF37" s="24">
         <v>12357.031216134228</v>
       </c>
-      <c r="AG37" s="25">
+      <c r="AG37" s="24">
         <v>10699.212722349259</v>
       </c>
-      <c r="AH37" s="25">
+      <c r="AH37" s="24">
         <v>12777.47216341843</v>
       </c>
-      <c r="AI37" s="25">
+      <c r="AI37" s="24">
         <v>9243.9158399523531</v>
       </c>
-      <c r="AJ37" s="25">
+      <c r="AJ37" s="24">
         <v>9948.0422107465401</v>
       </c>
-      <c r="AK37" s="25">
+      <c r="AK37" s="24">
         <v>8940.5481925045624</v>
       </c>
-      <c r="AL37" s="25">
+      <c r="AL37" s="24">
         <v>11484.957196018111</v>
       </c>
-      <c r="AM37" s="25">
+      <c r="AM37" s="24">
         <v>7655.9831369018839</v>
       </c>
-      <c r="AN37" s="25">
+      <c r="AN37" s="24">
         <v>11409.396096016853</v>
       </c>
-      <c r="AO37" s="25">
+      <c r="AO37" s="24">
         <v>11670.507170602052</v>
       </c>
-      <c r="AP37" s="25">
+      <c r="AP37" s="24">
         <v>9814.9488166659594</v>
       </c>
-      <c r="AQ37" s="25">
+      <c r="AQ37" s="24">
         <v>12146.475586166891</v>
       </c>
-      <c r="AR37" s="25">
+      <c r="AR37" s="24">
         <v>10847.829087733562</v>
       </c>
-      <c r="AS37" s="25">
+      <c r="AS37" s="24">
         <v>12868.699734952137</v>
       </c>
-      <c r="AT37" s="25">
+      <c r="AT37" s="24">
         <v>12529.587934806083</v>
       </c>
-      <c r="AU37" s="25">
+      <c r="AU37" s="24">
         <v>13093.501488656328</v>
       </c>
-      <c r="AV37" s="25">
+      <c r="AV37" s="24">
         <v>4670.9593611091741</v>
       </c>
-      <c r="AW37" s="25">
+      <c r="AW37" s="24">
         <v>5612.388003795837</v>
       </c>
-      <c r="AX37" s="25">
+      <c r="AX37" s="24">
         <v>4825.4450649167493</v>
       </c>
-      <c r="AY37" s="25">
+      <c r="AY37" s="24">
         <v>4956.0358040474975</v>
       </c>
-      <c r="AZ37" s="25">
+      <c r="AZ37" s="24">
         <v>4312.8027705177237</v>
       </c>
-      <c r="BA37" s="25">
+      <c r="BA37" s="24">
         <v>4558.0161273942758</v>
       </c>
-      <c r="BB37" s="25">
+      <c r="BB37" s="24">
         <v>3879.6381101962033</v>
       </c>
-      <c r="BC37" s="25">
+      <c r="BC37" s="24">
         <v>5205.4283704461704</v>
       </c>
-      <c r="BD37" s="25">
+      <c r="BD37" s="24">
         <v>4858.829800942106</v>
       </c>
-      <c r="BE37" s="25">
+      <c r="BE37" s="24">
         <v>5518.6196803267576</v>
       </c>
-      <c r="BF37" s="25">
+      <c r="BF37" s="24">
         <v>5297.7077283357039</v>
       </c>
-      <c r="BG37" s="25">
+      <c r="BG37" s="24">
         <v>4446.3712791867756</v>
       </c>
-      <c r="BH37" s="25">
+      <c r="BH37" s="24">
         <v>5055.5647593208914</v>
       </c>
-      <c r="BI37" s="25">
+      <c r="BI37" s="24">
         <v>6305.5366040556819</v>
       </c>
-      <c r="BJ37" s="25">
+      <c r="BJ37" s="24">
         <v>6132.976339217731</v>
       </c>
-      <c r="BK37" s="25">
+      <c r="BK37" s="24">
         <v>6020.9325755252703</v>
       </c>
-      <c r="BL37" s="25">
+      <c r="BL37" s="24">
         <v>5423.7739959758683</v>
       </c>
-      <c r="BM37" s="25">
+      <c r="BM37" s="24">
         <v>5823.0127821029428</v>
       </c>
-      <c r="BN37" s="25">
+      <c r="BN37" s="24">
         <v>6890.8477762607426</v>
       </c>
-      <c r="BO37" s="25">
+      <c r="BO37" s="24">
         <v>7371.2221450666402</v>
       </c>
-      <c r="BP37" s="25">
+      <c r="BP37" s="24">
         <v>5357.8863221845504</v>
       </c>
-      <c r="BQ37" s="25">
+      <c r="BQ37" s="24">
         <v>5671.8614120250268</v>
       </c>
-      <c r="BR37" s="25">
+      <c r="BR37" s="24">
         <v>7585.5062014967498</v>
       </c>
-      <c r="BS37" s="25">
+      <c r="BS37" s="24">
         <v>6474.3392523085804</v>
       </c>
-      <c r="BT37" s="25">
+      <c r="BT37" s="24">
         <v>5419.1611790010847</v>
       </c>
-      <c r="BU37" s="25">
+      <c r="BU37" s="24">
         <v>6391.5180787741247</v>
       </c>
-      <c r="BV37" s="25">
+      <c r="BV37" s="24">
         <v>6338.1666337580355</v>
       </c>
-      <c r="BW37" s="25">
+      <c r="BW37" s="24">
         <v>6824.1010908392527</v>
       </c>
-      <c r="BX37" s="25">
+      <c r="BX37" s="24">
         <v>5991.869109995796</v>
       </c>
-      <c r="BY37" s="25">
+      <c r="BY37" s="24">
         <v>5917.0077994240255</v>
       </c>
-      <c r="BZ37" s="25">
+      <c r="BZ37" s="24">
         <v>7145.8169889028268</v>
       </c>
-      <c r="CA37" s="25">
+      <c r="CA37" s="24">
         <v>7135.2219951940588</v>
       </c>
-      <c r="CB37" s="25">
+      <c r="CB37" s="24">
         <v>5317.7924717972573</v>
       </c>
-      <c r="CC37" s="25">
+      <c r="CC37" s="24">
         <v>4875.2259184043169</v>
       </c>
       <c r="CD37" s="12">
@@ -6762,19 +6743,19 @@
         <v>7343.9731725169113</v>
       </c>
       <c r="CW37" s="12">
-        <v>7257.0701787109283</v>
+        <v>7262.0566710116909</v>
       </c>
       <c r="CX37" s="12">
-        <v>6763.0229030930705</v>
+        <v>6782.4094442816604</v>
       </c>
       <c r="CY37" s="12">
-        <v>7806.7156608634068</v>
+        <v>7810.3290462699388</v>
       </c>
       <c r="CZ37" s="12">
-        <v>6911.4354538447733</v>
+        <v>6920.2100421151908</v>
       </c>
       <c r="DA37" s="12">
-        <v>6717.0419053421938</v>
+        <v>6716.536419552498</v>
       </c>
       <c r="DB37" s="14"/>
       <c r="DC37" s="14"/>
@@ -6855,244 +6836,244 @@
       <c r="A38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="24">
         <v>63.730313174419287</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="24">
         <v>390.8939765873198</v>
       </c>
-      <c r="D38" s="25">
+      <c r="D38" s="24">
         <v>128.24794446692633</v>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="24">
         <v>10.740325855691813</v>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="24">
         <v>75.816368479435411</v>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="24">
         <v>425.30897577135096</v>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="24">
         <v>248.33255543805498</v>
       </c>
-      <c r="I38" s="25">
+      <c r="I38" s="24">
         <v>26.014280944220708</v>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="24">
         <v>103.90076461400335</v>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="24">
         <v>382.9922910007345</v>
       </c>
-      <c r="L38" s="25">
+      <c r="L38" s="24">
         <v>222.88800006187481</v>
       </c>
-      <c r="M38" s="25">
+      <c r="M38" s="24">
         <v>26.162622844051949</v>
       </c>
-      <c r="N38" s="25">
+      <c r="N38" s="24">
         <v>110.17413968489252</v>
       </c>
-      <c r="O38" s="25">
+      <c r="O38" s="24">
         <v>295.98478909516723</v>
       </c>
-      <c r="P38" s="25">
+      <c r="P38" s="24">
         <v>174.42338742043836</v>
       </c>
-      <c r="Q38" s="25">
+      <c r="Q38" s="24">
         <v>19.534977157828134</v>
       </c>
-      <c r="R38" s="25">
+      <c r="R38" s="24">
         <v>27.72996059528954</v>
       </c>
-      <c r="S38" s="25">
+      <c r="S38" s="24">
         <v>282.94351674545811</v>
       </c>
-      <c r="T38" s="25">
+      <c r="T38" s="24">
         <v>218.19109933580486</v>
       </c>
-      <c r="U38" s="25">
+      <c r="U38" s="24">
         <v>14.498973252788749</v>
       </c>
-      <c r="V38" s="25">
+      <c r="V38" s="24">
         <v>88.805066314120893</v>
       </c>
-      <c r="W38" s="25">
+      <c r="W38" s="24">
         <v>357.45261426676041</v>
       </c>
-      <c r="X38" s="25">
+      <c r="X38" s="24">
         <v>210.05483949140429</v>
       </c>
-      <c r="Y38" s="25">
+      <c r="Y38" s="24">
         <v>30.947948405593017</v>
       </c>
-      <c r="Z38" s="25">
+      <c r="Z38" s="24">
         <v>178.77760970055738</v>
       </c>
-      <c r="AA38" s="25">
+      <c r="AA38" s="24">
         <v>936.16482946719066</v>
       </c>
-      <c r="AB38" s="25">
+      <c r="AB38" s="24">
         <v>862.96290681281732</v>
       </c>
-      <c r="AC38" s="25">
+      <c r="AC38" s="24">
         <v>449.60941478174408</v>
       </c>
-      <c r="AD38" s="25">
+      <c r="AD38" s="24">
         <v>651.96688614846096</v>
       </c>
-      <c r="AE38" s="25">
+      <c r="AE38" s="24">
         <v>2549.0017489522938</v>
       </c>
-      <c r="AF38" s="25">
+      <c r="AF38" s="24">
         <v>767.54542370501679</v>
       </c>
-      <c r="AG38" s="25">
+      <c r="AG38" s="24">
         <v>309.26240584102339</v>
       </c>
-      <c r="AH38" s="25">
+      <c r="AH38" s="24">
         <v>217.5570594625737</v>
       </c>
-      <c r="AI38" s="25">
+      <c r="AI38" s="24">
         <v>1332.1249866142857</v>
       </c>
-      <c r="AJ38" s="25">
+      <c r="AJ38" s="24">
         <v>971.88413091396262</v>
       </c>
-      <c r="AK38" s="25">
+      <c r="AK38" s="24">
         <v>1018.893948821237</v>
       </c>
-      <c r="AL38" s="25">
+      <c r="AL38" s="24">
         <v>432.12183914154969</v>
       </c>
-      <c r="AM38" s="25">
+      <c r="AM38" s="24">
         <v>1909.9566961871951</v>
       </c>
-      <c r="AN38" s="25">
+      <c r="AN38" s="24">
         <v>2054.4011371974279</v>
       </c>
-      <c r="AO38" s="25">
+      <c r="AO38" s="24">
         <v>1098.9585768839152</v>
       </c>
-      <c r="AP38" s="25">
+      <c r="AP38" s="24">
         <v>1153.0371305907145</v>
       </c>
-      <c r="AQ38" s="25">
+      <c r="AQ38" s="24">
         <v>3768.687792623899</v>
       </c>
-      <c r="AR38" s="25">
+      <c r="AR38" s="24">
         <v>2421.5624356619865</v>
       </c>
-      <c r="AS38" s="25">
+      <c r="AS38" s="24">
         <v>1546.9287408613779</v>
       </c>
-      <c r="AT38" s="25">
+      <c r="AT38" s="24">
         <v>1854.5943492761673</v>
       </c>
-      <c r="AU38" s="25">
+      <c r="AU38" s="24">
         <v>4896.3762109616846</v>
       </c>
-      <c r="AV38" s="25">
+      <c r="AV38" s="24">
         <v>4514.494216662014</v>
       </c>
-      <c r="AW38" s="25">
+      <c r="AW38" s="24">
         <v>1899.1394642406035</v>
       </c>
-      <c r="AX38" s="25">
+      <c r="AX38" s="24">
         <v>4273.5703268520847</v>
       </c>
-      <c r="AY38" s="25">
+      <c r="AY38" s="24">
         <v>8351.38943702291</v>
       </c>
-      <c r="AZ38" s="25">
+      <c r="AZ38" s="24">
         <v>4843.6230576290463</v>
       </c>
-      <c r="BA38" s="25">
+      <c r="BA38" s="24">
         <v>1107.5159939220921</v>
       </c>
-      <c r="BB38" s="25">
+      <c r="BB38" s="24">
         <v>5885.6450739478878</v>
       </c>
-      <c r="BC38" s="25">
+      <c r="BC38" s="24">
         <v>8710.8219556188142</v>
       </c>
-      <c r="BD38" s="25">
+      <c r="BD38" s="24">
         <v>4796.2538489975841</v>
       </c>
-      <c r="BE38" s="25">
+      <c r="BE38" s="24">
         <v>1125.3435784057287</v>
       </c>
-      <c r="BF38" s="25">
+      <c r="BF38" s="24">
         <v>6550.6567088186575</v>
       </c>
-      <c r="BG38" s="25">
+      <c r="BG38" s="24">
         <v>12077.949940686849</v>
       </c>
-      <c r="BH38" s="25">
+      <c r="BH38" s="24">
         <v>7342.9662257321379</v>
       </c>
-      <c r="BI38" s="25">
+      <c r="BI38" s="24">
         <v>1348.6168557817693</v>
       </c>
-      <c r="BJ38" s="25">
+      <c r="BJ38" s="24">
         <v>6523.9341606723365</v>
       </c>
-      <c r="BK38" s="25">
+      <c r="BK38" s="24">
         <v>10456.957703947051</v>
       </c>
-      <c r="BL38" s="25">
+      <c r="BL38" s="24">
         <v>7248.4306350962743</v>
       </c>
-      <c r="BM38" s="25">
+      <c r="BM38" s="24">
         <v>1313.0720786821305</v>
       </c>
-      <c r="BN38" s="25">
+      <c r="BN38" s="24">
         <v>6320.2155252105276</v>
       </c>
-      <c r="BO38" s="25">
+      <c r="BO38" s="24">
         <v>8253.0988963924938</v>
       </c>
-      <c r="BP38" s="25">
+      <c r="BP38" s="24">
         <v>4728.1740617320629</v>
       </c>
-      <c r="BQ38" s="25">
+      <c r="BQ38" s="24">
         <v>1272.367406209296</v>
       </c>
-      <c r="BR38" s="25">
+      <c r="BR38" s="24">
         <v>3255.8796044494488</v>
       </c>
-      <c r="BS38" s="25">
+      <c r="BS38" s="24">
         <v>9260.6352702670083</v>
       </c>
-      <c r="BT38" s="25">
+      <c r="BT38" s="24">
         <v>4854.2379375358869</v>
       </c>
-      <c r="BU38" s="25">
+      <c r="BU38" s="24">
         <v>1147.1756582059002</v>
       </c>
-      <c r="BV38" s="25">
+      <c r="BV38" s="24">
         <v>3022.6183592213588</v>
       </c>
-      <c r="BW38" s="25">
+      <c r="BW38" s="24">
         <v>7998.4290423303391</v>
       </c>
-      <c r="BX38" s="25">
+      <c r="BX38" s="24">
         <v>5791.188906170667</v>
       </c>
-      <c r="BY38" s="25">
+      <c r="BY38" s="24">
         <v>927.56556132923674</v>
       </c>
-      <c r="BZ38" s="25">
+      <c r="BZ38" s="24">
         <v>3795.5978408386472</v>
       </c>
-      <c r="CA38" s="25">
+      <c r="CA38" s="24">
         <v>9585.5898127993405</v>
       </c>
-      <c r="CB38" s="25">
+      <c r="CB38" s="24">
         <v>5433.7460649143777</v>
       </c>
-      <c r="CC38" s="25">
+      <c r="CC38" s="24">
         <v>1183.5453050465471</v>
       </c>
       <c r="CD38" s="12">
@@ -7144,28 +7125,28 @@
         <v>1715.0336096520994</v>
       </c>
       <c r="CT38" s="12">
-        <v>5412.0328815743278</v>
+        <v>5455.251870850976</v>
       </c>
       <c r="CU38" s="12">
-        <v>8112.4809662885255</v>
+        <v>8151.9157675096376</v>
       </c>
       <c r="CV38" s="12">
-        <v>6180.0563760946561</v>
+        <v>6242.2149654118475</v>
       </c>
       <c r="CW38" s="12">
-        <v>1725.5135156052097</v>
+        <v>1744.7445721112085</v>
       </c>
       <c r="CX38" s="12">
-        <v>5014.8897359471166</v>
+        <v>5031.2066591166722</v>
       </c>
       <c r="CY38" s="12">
-        <v>8471.6085786286112</v>
+        <v>8474.7860728855994</v>
       </c>
       <c r="CZ38" s="12">
-        <v>6752.5325841918548</v>
+        <v>6831.5889028807378</v>
       </c>
       <c r="DA38" s="12">
-        <v>1900.8974510105122</v>
+        <v>1966.2359441903313</v>
       </c>
       <c r="DB38" s="14"/>
       <c r="DC38" s="14"/>
@@ -7246,244 +7227,244 @@
       <c r="A39" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="24">
         <v>909.19254082141038</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="24">
         <v>1078.9379589473506</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="24">
         <v>1088.8514094824968</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="24">
         <v>692.01331123642444</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="24">
         <v>833.64649214458882</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="24">
         <v>813.84109527573105</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="24">
         <v>693.2167275001525</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="24">
         <v>449.86190992042657</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="24">
         <v>1349.8061782049006</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="24">
         <v>267.55558533007672</v>
       </c>
-      <c r="L39" s="25">
+      <c r="L39" s="24">
         <v>359.98919539304836</v>
       </c>
-      <c r="M39" s="25">
+      <c r="M39" s="24">
         <v>335.60998695610641</v>
       </c>
-      <c r="N39" s="25">
+      <c r="N39" s="24">
         <v>1384.9932695208497</v>
       </c>
-      <c r="O39" s="25">
+      <c r="O39" s="24">
         <v>293.10021318985605</v>
       </c>
-      <c r="P39" s="25">
+      <c r="P39" s="24">
         <v>389.01443753824742</v>
       </c>
-      <c r="Q39" s="25">
+      <c r="Q39" s="24">
         <v>315.89837864547991</v>
       </c>
-      <c r="R39" s="25">
+      <c r="R39" s="24">
         <v>1186.0745194498024</v>
       </c>
-      <c r="S39" s="25">
+      <c r="S39" s="24">
         <v>254.3566066530264</v>
       </c>
-      <c r="T39" s="25">
+      <c r="T39" s="24">
         <v>350.58637447454754</v>
       </c>
-      <c r="U39" s="25">
+      <c r="U39" s="24">
         <v>314.84555760517151</v>
       </c>
-      <c r="V39" s="25">
+      <c r="V39" s="24">
         <v>1312.8710674881358</v>
       </c>
-      <c r="W39" s="25">
+      <c r="W39" s="24">
         <v>289.11435386939735</v>
       </c>
-      <c r="X39" s="25">
+      <c r="X39" s="24">
         <v>372.00168929014569</v>
       </c>
-      <c r="Y39" s="25">
+      <c r="Y39" s="24">
         <v>313.67098836688291</v>
       </c>
-      <c r="Z39" s="25">
+      <c r="Z39" s="24">
         <v>1219.9748465123862</v>
       </c>
-      <c r="AA39" s="25">
+      <c r="AA39" s="24">
         <v>286.61096689076464</v>
       </c>
-      <c r="AB39" s="25">
+      <c r="AB39" s="24">
         <v>371.19822171711792</v>
       </c>
-      <c r="AC39" s="25">
+      <c r="AC39" s="24">
         <v>350.43494189833336</v>
       </c>
-      <c r="AD39" s="25">
+      <c r="AD39" s="24">
         <v>1520.8969333931236</v>
       </c>
-      <c r="AE39" s="25">
+      <c r="AE39" s="24">
         <v>382.65517004739991</v>
       </c>
-      <c r="AF39" s="25">
+      <c r="AF39" s="24">
         <v>493.88587358709788</v>
       </c>
-      <c r="AG39" s="25">
+      <c r="AG39" s="24">
         <v>390.30915241421883</v>
       </c>
-      <c r="AH39" s="25">
+      <c r="AH39" s="24">
         <v>1721.7353852621418</v>
       </c>
-      <c r="AI39" s="25">
+      <c r="AI39" s="24">
         <v>367.50684014086812</v>
       </c>
-      <c r="AJ39" s="25">
+      <c r="AJ39" s="24">
         <v>451.84808084382348</v>
       </c>
-      <c r="AK39" s="25">
+      <c r="AK39" s="24">
         <v>454.28682784106445</v>
       </c>
-      <c r="AL39" s="25">
+      <c r="AL39" s="24">
         <v>3263.7617108949808</v>
       </c>
-      <c r="AM39" s="25">
+      <c r="AM39" s="24">
         <v>904.11373300807782</v>
       </c>
-      <c r="AN39" s="25">
+      <c r="AN39" s="24">
         <v>1384.7293686830428</v>
       </c>
-      <c r="AO39" s="25">
+      <c r="AO39" s="24">
         <v>1140.6264551150666</v>
       </c>
-      <c r="AP39" s="25">
+      <c r="AP39" s="24">
         <v>4499.1836362924096</v>
       </c>
-      <c r="AQ39" s="25">
+      <c r="AQ39" s="24">
         <v>920.86537188300099</v>
       </c>
-      <c r="AR39" s="25">
+      <c r="AR39" s="24">
         <v>1364.0571410055943</v>
       </c>
-      <c r="AS39" s="25">
+      <c r="AS39" s="24">
         <v>1157.3712974559201</v>
       </c>
-      <c r="AT39" s="25">
+      <c r="AT39" s="24">
         <v>4543.577662198838</v>
       </c>
-      <c r="AU39" s="25">
+      <c r="AU39" s="24">
         <v>1094.8254045461242</v>
       </c>
-      <c r="AV39" s="25">
+      <c r="AV39" s="24">
         <v>1548.6730702830469</v>
       </c>
-      <c r="AW39" s="25">
+      <c r="AW39" s="24">
         <v>1474.4037741777843</v>
       </c>
-      <c r="AX39" s="25">
+      <c r="AX39" s="24">
         <v>5571.2748784379673</v>
       </c>
-      <c r="AY39" s="25">
+      <c r="AY39" s="24">
         <v>1323.247643726258</v>
       </c>
-      <c r="AZ39" s="25">
+      <c r="AZ39" s="24">
         <v>1508.3091841341507</v>
       </c>
-      <c r="BA39" s="25">
+      <c r="BA39" s="24">
         <v>1117.5049101056038</v>
       </c>
-      <c r="BB39" s="25">
+      <c r="BB39" s="24">
         <v>5707.0725913566457</v>
       </c>
-      <c r="BC39" s="25">
+      <c r="BC39" s="24">
         <v>1882.1346975377119</v>
       </c>
-      <c r="BD39" s="25">
+      <c r="BD39" s="24">
         <v>2516.0139926959905</v>
       </c>
-      <c r="BE39" s="25">
+      <c r="BE39" s="24">
         <v>1881.5462754303558</v>
       </c>
-      <c r="BF39" s="25">
+      <c r="BF39" s="24">
         <v>7405.999409573149</v>
       </c>
-      <c r="BG39" s="25">
+      <c r="BG39" s="24">
         <v>1681.5505878539075</v>
       </c>
-      <c r="BH39" s="25">
+      <c r="BH39" s="24">
         <v>2369.9406169678941</v>
       </c>
-      <c r="BI39" s="25">
+      <c r="BI39" s="24">
         <v>1746.2907614986398</v>
       </c>
-      <c r="BJ39" s="25">
+      <c r="BJ39" s="24">
         <v>7162.9229358572975</v>
       </c>
-      <c r="BK39" s="25">
+      <c r="BK39" s="24">
         <v>1674.4444979683794</v>
       </c>
-      <c r="BL39" s="25">
+      <c r="BL39" s="24">
         <v>2170.8130480376999</v>
       </c>
-      <c r="BM39" s="25">
+      <c r="BM39" s="24">
         <v>1787.0012591271861</v>
       </c>
-      <c r="BN39" s="25">
+      <c r="BN39" s="24">
         <v>8169.0086836700502</v>
       </c>
-      <c r="BO39" s="25">
+      <c r="BO39" s="24">
         <v>1698.2432355423698</v>
       </c>
-      <c r="BP39" s="25">
+      <c r="BP39" s="24">
         <v>2037.9354378198523</v>
       </c>
-      <c r="BQ39" s="25">
+      <c r="BQ39" s="24">
         <v>1568.0260048498199</v>
       </c>
-      <c r="BR39" s="25">
+      <c r="BR39" s="24">
         <v>6880.8366075131562</v>
       </c>
-      <c r="BS39" s="25">
+      <c r="BS39" s="24">
         <v>1352.1438361973744</v>
       </c>
-      <c r="BT39" s="25">
+      <c r="BT39" s="24">
         <v>1830.3254796790252</v>
       </c>
-      <c r="BU39" s="25">
+      <c r="BU39" s="24">
         <v>1466.096041045575</v>
       </c>
-      <c r="BV39" s="25">
+      <c r="BV39" s="24">
         <v>6305.1415620306871</v>
       </c>
-      <c r="BW39" s="25">
+      <c r="BW39" s="24">
         <v>1374.7239420104672</v>
       </c>
-      <c r="BX39" s="25">
+      <c r="BX39" s="24">
         <v>1926.9423640840787</v>
       </c>
-      <c r="BY39" s="25">
+      <c r="BY39" s="24">
         <v>1501.2414133075058</v>
       </c>
-      <c r="BZ39" s="25">
+      <c r="BZ39" s="24">
         <v>6495.9397345199759</v>
       </c>
-      <c r="CA39" s="25">
+      <c r="CA39" s="24">
         <v>1372.7121359653493</v>
       </c>
-      <c r="CB39" s="25">
+      <c r="CB39" s="24">
         <v>1680.9651162300061</v>
       </c>
-      <c r="CC39" s="25">
+      <c r="CC39" s="24">
         <v>1251.1146890163657</v>
       </c>
       <c r="CD39" s="12">
@@ -7547,7 +7528,7 @@
         <v>1532.3317486045294</v>
       </c>
       <c r="CX39" s="12">
-        <v>4085.4092974782961</v>
+        <v>4085.4092974782943</v>
       </c>
       <c r="CY39" s="12">
         <v>1159.7277677220832</v>
@@ -7556,7 +7537,7 @@
         <v>1526.2896571705473</v>
       </c>
       <c r="DA39" s="12">
-        <v>1396.5719637325756</v>
+        <v>1354.0688656739121</v>
       </c>
       <c r="DB39" s="14"/>
       <c r="DC39" s="14"/>
@@ -7637,244 +7618,244 @@
       <c r="A40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="24">
         <v>2445.0413469541058</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="24">
         <v>1688.2089363328116</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="24">
         <v>1415.2439680134432</v>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="24">
         <v>1721.7155228961497</v>
       </c>
-      <c r="F40" s="25">
+      <c r="F40" s="24">
         <v>1810.7206670688729</v>
       </c>
-      <c r="G40" s="25">
+      <c r="G40" s="24">
         <v>1940.4626120705152</v>
       </c>
-      <c r="H40" s="25">
+      <c r="H40" s="24">
         <v>1591.3990474475575</v>
       </c>
-      <c r="I40" s="25">
+      <c r="I40" s="24">
         <v>1853.8967204341143</v>
       </c>
-      <c r="J40" s="25">
+      <c r="J40" s="24">
         <v>1867.498427536505</v>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="24">
         <v>2227.9582287811222</v>
       </c>
-      <c r="L40" s="25">
+      <c r="L40" s="24">
         <v>2345.8813258443224</v>
       </c>
-      <c r="M40" s="25">
+      <c r="M40" s="24">
         <v>2663.8441780377816</v>
       </c>
-      <c r="N40" s="25">
+      <c r="N40" s="24">
         <v>3188.2592276764262</v>
       </c>
-      <c r="O40" s="25">
+      <c r="O40" s="24">
         <v>1929.0125290828973</v>
       </c>
-      <c r="P40" s="25">
+      <c r="P40" s="24">
         <v>2149.1608888922938</v>
       </c>
-      <c r="Q40" s="25">
+      <c r="Q40" s="24">
         <v>2217.5024132055692</v>
       </c>
-      <c r="R40" s="25">
+      <c r="R40" s="24">
         <v>3242.8480540062942</v>
       </c>
-      <c r="S40" s="25">
+      <c r="S40" s="24">
         <v>1805.7131619169281</v>
       </c>
-      <c r="T40" s="25">
+      <c r="T40" s="24">
         <v>2020.0912311844927</v>
       </c>
-      <c r="U40" s="25">
+      <c r="U40" s="24">
         <v>2622.797647206467</v>
       </c>
-      <c r="V40" s="25">
+      <c r="V40" s="24">
         <v>3952.7189920775872</v>
       </c>
-      <c r="W40" s="25">
+      <c r="W40" s="24">
         <v>2020.7223962547087</v>
       </c>
-      <c r="X40" s="25">
+      <c r="X40" s="24">
         <v>1572.5331670379467</v>
       </c>
-      <c r="Y40" s="25">
+      <c r="Y40" s="24">
         <v>2872.1160261576915</v>
       </c>
-      <c r="Z40" s="25">
+      <c r="Z40" s="24">
         <v>3493.374649560843</v>
       </c>
-      <c r="AA40" s="25">
+      <c r="AA40" s="24">
         <v>2408.2736340954921</v>
       </c>
-      <c r="AB40" s="25">
+      <c r="AB40" s="24">
         <v>2114.4715684186876</v>
       </c>
-      <c r="AC40" s="25">
+      <c r="AC40" s="24">
         <v>2849.6325229434337</v>
       </c>
-      <c r="AD40" s="25">
+      <c r="AD40" s="24">
         <v>3877.5671603223436</v>
       </c>
-      <c r="AE40" s="25">
+      <c r="AE40" s="24">
         <v>3236.9041449059309</v>
       </c>
-      <c r="AF40" s="25">
+      <c r="AF40" s="24">
         <v>2331.7770553355149</v>
       </c>
-      <c r="AG40" s="25">
+      <c r="AG40" s="24">
         <v>3054.2194486804219</v>
       </c>
-      <c r="AH40" s="25">
+      <c r="AH40" s="24">
         <v>3862.0131545888353</v>
       </c>
-      <c r="AI40" s="25">
+      <c r="AI40" s="24">
         <v>2893.9019000892117</v>
       </c>
-      <c r="AJ40" s="25">
+      <c r="AJ40" s="24">
         <v>2464.7093991270094</v>
       </c>
-      <c r="AK40" s="25">
+      <c r="AK40" s="24">
         <v>3460.1474050835759</v>
       </c>
-      <c r="AL40" s="25">
+      <c r="AL40" s="24">
         <v>4909.2361583347702</v>
       </c>
-      <c r="AM40" s="25">
+      <c r="AM40" s="24">
         <v>3237.7385416208449</v>
       </c>
-      <c r="AN40" s="25">
+      <c r="AN40" s="24">
         <v>3246.4814064784614</v>
       </c>
-      <c r="AO40" s="25">
+      <c r="AO40" s="24">
         <v>4728.2630050331045</v>
       </c>
-      <c r="AP40" s="25">
+      <c r="AP40" s="24">
         <v>6037.0591719909808</v>
       </c>
-      <c r="AQ40" s="25">
+      <c r="AQ40" s="24">
         <v>4780.0626114995821</v>
       </c>
-      <c r="AR40" s="25">
+      <c r="AR40" s="24">
         <v>3773.7981728503164</v>
       </c>
-      <c r="AS40" s="25">
+      <c r="AS40" s="24">
         <v>5376.2593124508576</v>
       </c>
-      <c r="AT40" s="25">
+      <c r="AT40" s="24">
         <v>6212.8067754750773</v>
       </c>
-      <c r="AU40" s="25">
+      <c r="AU40" s="24">
         <v>4547.9928031971185</v>
       </c>
-      <c r="AV40" s="25">
+      <c r="AV40" s="24">
         <v>4027.0494617998829</v>
       </c>
-      <c r="AW40" s="25">
+      <c r="AW40" s="24">
         <v>6821.7575593737902</v>
       </c>
-      <c r="AX40" s="25">
+      <c r="AX40" s="24">
         <v>7831.6460798922199</v>
       </c>
-      <c r="AY40" s="25">
+      <c r="AY40" s="24">
         <v>6272.7478115034792</v>
       </c>
-      <c r="AZ40" s="25">
+      <c r="AZ40" s="24">
         <v>5172.2582102040615</v>
       </c>
-      <c r="BA40" s="25">
+      <c r="BA40" s="24">
         <v>8460.3112912386314</v>
       </c>
-      <c r="BB40" s="25">
+      <c r="BB40" s="24">
         <v>8356.9936821612246</v>
       </c>
-      <c r="BC40" s="25">
+      <c r="BC40" s="24">
         <v>6925.3862077748763</v>
       </c>
-      <c r="BD40" s="25">
+      <c r="BD40" s="24">
         <v>5722.082253385136</v>
       </c>
-      <c r="BE40" s="25">
+      <c r="BE40" s="24">
         <v>9810.3814787067568</v>
       </c>
-      <c r="BF40" s="25">
+      <c r="BF40" s="24">
         <v>10990.427676673271</v>
       </c>
-      <c r="BG40" s="25">
+      <c r="BG40" s="24">
         <v>7768.2845564159215</v>
       </c>
-      <c r="BH40" s="25">
+      <c r="BH40" s="24">
         <v>6689.6046241708555</v>
       </c>
-      <c r="BI40" s="25">
+      <c r="BI40" s="24">
         <v>10684.413929718796</v>
       </c>
-      <c r="BJ40" s="25">
+      <c r="BJ40" s="24">
         <v>11833.99404093639</v>
       </c>
-      <c r="BK40" s="25">
+      <c r="BK40" s="24">
         <v>7092.5360176268732</v>
       </c>
-      <c r="BL40" s="25">
+      <c r="BL40" s="24">
         <v>6526.9488568015022</v>
       </c>
-      <c r="BM40" s="25">
+      <c r="BM40" s="24">
         <v>11489.498188907182</v>
       </c>
-      <c r="BN40" s="25">
+      <c r="BN40" s="24">
         <v>11475.095109187092</v>
       </c>
-      <c r="BO40" s="25">
+      <c r="BO40" s="24">
         <v>6718.4741937854515</v>
       </c>
-      <c r="BP40" s="25">
+      <c r="BP40" s="24">
         <v>8156.0062664576653</v>
       </c>
-      <c r="BQ40" s="25">
+      <c r="BQ40" s="24">
         <v>13857.018617652358</v>
       </c>
-      <c r="BR40" s="25">
+      <c r="BR40" s="24">
         <v>12413.206985609755</v>
       </c>
-      <c r="BS40" s="25">
+      <c r="BS40" s="24">
         <v>9407.5591931590334</v>
       </c>
-      <c r="BT40" s="25">
+      <c r="BT40" s="24">
         <v>8645.0547792649413</v>
       </c>
-      <c r="BU40" s="25">
+      <c r="BU40" s="24">
         <v>15427.349080199012</v>
       </c>
-      <c r="BV40" s="25">
+      <c r="BV40" s="24">
         <v>14049.640873360902</v>
       </c>
-      <c r="BW40" s="25">
+      <c r="BW40" s="24">
         <v>9692.7364637730825</v>
       </c>
-      <c r="BX40" s="25">
+      <c r="BX40" s="24">
         <v>8583.4435398080459</v>
       </c>
-      <c r="BY40" s="25">
+      <c r="BY40" s="24">
         <v>17297.232575483555</v>
       </c>
-      <c r="BZ40" s="25">
+      <c r="BZ40" s="24">
         <v>13754.375296152757</v>
       </c>
-      <c r="CA40" s="25">
+      <c r="CA40" s="24">
         <v>10495.448797252127</v>
       </c>
-      <c r="CB40" s="25">
+      <c r="CB40" s="24">
         <v>8394.1811227511062</v>
       </c>
-      <c r="CC40" s="25">
+      <c r="CC40" s="24">
         <v>17215.538980340767</v>
       </c>
       <c r="CD40" s="12">
@@ -7926,28 +7907,28 @@
         <v>18462.48696299435</v>
       </c>
       <c r="CT40" s="12">
-        <v>14702.563719908845</v>
+        <v>14665.000233972274</v>
       </c>
       <c r="CU40" s="12">
-        <v>8882.7514773896473</v>
+        <v>8830.8373394575792</v>
       </c>
       <c r="CV40" s="12">
-        <v>10786.909162940477</v>
+        <v>10846.332620393028</v>
       </c>
       <c r="CW40" s="12">
-        <v>19716.338060137292</v>
+        <v>19745.934452836555</v>
       </c>
       <c r="CX40" s="12">
-        <v>15374.638485718653</v>
+        <v>15403.152474345658</v>
       </c>
       <c r="CY40" s="12">
-        <v>9096.5379348827064</v>
+        <v>9022.5915562279588</v>
       </c>
       <c r="CZ40" s="12">
-        <v>11216.341255561916</v>
+        <v>11195.338436370434</v>
       </c>
       <c r="DA40" s="12">
-        <v>20056.100333231891</v>
+        <v>19791.327058368388</v>
       </c>
       <c r="DB40" s="14"/>
       <c r="DC40" s="14"/>
@@ -8025,86 +8006,86 @@
       <c r="FW40" s="14"/>
     </row>
     <row r="41" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="26"/>
-      <c r="S41" s="26"/>
-      <c r="T41" s="26"/>
-      <c r="U41" s="26"/>
-      <c r="V41" s="26"/>
-      <c r="W41" s="26"/>
-      <c r="X41" s="26"/>
-      <c r="Y41" s="26"/>
-      <c r="Z41" s="26"/>
-      <c r="AA41" s="26"/>
-      <c r="AB41" s="26"/>
-      <c r="AC41" s="26"/>
-      <c r="AD41" s="26"/>
-      <c r="AE41" s="26"/>
-      <c r="AF41" s="26"/>
-      <c r="AG41" s="26"/>
-      <c r="AH41" s="26"/>
-      <c r="AI41" s="26"/>
-      <c r="AJ41" s="26"/>
-      <c r="AK41" s="26"/>
-      <c r="AL41" s="26"/>
-      <c r="AM41" s="26"/>
-      <c r="AN41" s="26"/>
-      <c r="AO41" s="26"/>
-      <c r="AP41" s="26"/>
-      <c r="AQ41" s="26"/>
-      <c r="AR41" s="26"/>
-      <c r="AS41" s="26"/>
-      <c r="AT41" s="26"/>
-      <c r="AU41" s="26"/>
-      <c r="AV41" s="26"/>
-      <c r="AW41" s="26"/>
-      <c r="AX41" s="26"/>
-      <c r="AY41" s="26"/>
-      <c r="AZ41" s="26"/>
-      <c r="BA41" s="26"/>
-      <c r="BB41" s="26"/>
-      <c r="BC41" s="26"/>
-      <c r="BD41" s="26"/>
-      <c r="BE41" s="26"/>
-      <c r="BF41" s="26"/>
-      <c r="BG41" s="26"/>
-      <c r="BH41" s="26"/>
-      <c r="BI41" s="26"/>
-      <c r="BJ41" s="26"/>
-      <c r="BK41" s="26"/>
-      <c r="BL41" s="26"/>
-      <c r="BM41" s="26"/>
-      <c r="BN41" s="26"/>
-      <c r="BO41" s="26"/>
-      <c r="BP41" s="26"/>
-      <c r="BQ41" s="26"/>
-      <c r="BR41" s="26"/>
-      <c r="BS41" s="26"/>
-      <c r="BT41" s="26"/>
-      <c r="BU41" s="26"/>
-      <c r="BV41" s="26"/>
-      <c r="BW41" s="26"/>
-      <c r="BX41" s="26"/>
-      <c r="BY41" s="26"/>
-      <c r="BZ41" s="26"/>
-      <c r="CA41" s="26"/>
-      <c r="CB41" s="26"/>
-      <c r="CC41" s="26"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="25"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="25"/>
+      <c r="R41" s="25"/>
+      <c r="S41" s="25"/>
+      <c r="T41" s="25"/>
+      <c r="U41" s="25"/>
+      <c r="V41" s="25"/>
+      <c r="W41" s="25"/>
+      <c r="X41" s="25"/>
+      <c r="Y41" s="25"/>
+      <c r="Z41" s="25"/>
+      <c r="AA41" s="25"/>
+      <c r="AB41" s="25"/>
+      <c r="AC41" s="25"/>
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="25"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="25"/>
+      <c r="AH41" s="25"/>
+      <c r="AI41" s="25"/>
+      <c r="AJ41" s="25"/>
+      <c r="AK41" s="25"/>
+      <c r="AL41" s="25"/>
+      <c r="AM41" s="25"/>
+      <c r="AN41" s="25"/>
+      <c r="AO41" s="25"/>
+      <c r="AP41" s="25"/>
+      <c r="AQ41" s="25"/>
+      <c r="AR41" s="25"/>
+      <c r="AS41" s="25"/>
+      <c r="AT41" s="25"/>
+      <c r="AU41" s="25"/>
+      <c r="AV41" s="25"/>
+      <c r="AW41" s="25"/>
+      <c r="AX41" s="25"/>
+      <c r="AY41" s="25"/>
+      <c r="AZ41" s="25"/>
+      <c r="BA41" s="25"/>
+      <c r="BB41" s="25"/>
+      <c r="BC41" s="25"/>
+      <c r="BD41" s="25"/>
+      <c r="BE41" s="25"/>
+      <c r="BF41" s="25"/>
+      <c r="BG41" s="25"/>
+      <c r="BH41" s="25"/>
+      <c r="BI41" s="25"/>
+      <c r="BJ41" s="25"/>
+      <c r="BK41" s="25"/>
+      <c r="BL41" s="25"/>
+      <c r="BM41" s="25"/>
+      <c r="BN41" s="25"/>
+      <c r="BO41" s="25"/>
+      <c r="BP41" s="25"/>
+      <c r="BQ41" s="25"/>
+      <c r="BR41" s="25"/>
+      <c r="BS41" s="25"/>
+      <c r="BT41" s="25"/>
+      <c r="BU41" s="25"/>
+      <c r="BV41" s="25"/>
+      <c r="BW41" s="25"/>
+      <c r="BX41" s="25"/>
+      <c r="BY41" s="25"/>
+      <c r="BZ41" s="25"/>
+      <c r="CA41" s="25"/>
+      <c r="CB41" s="25"/>
+      <c r="CC41" s="25"/>
       <c r="CD41" s="16"/>
       <c r="CE41" s="16"/>
       <c r="CF41" s="16"/>
@@ -8208,244 +8189,244 @@
       <c r="A42" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="25">
         <v>14689.237691798957</v>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="25">
         <v>12780.107096915233</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="25">
         <v>13478.473825170244</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="25">
         <v>15504.034763046619</v>
       </c>
-      <c r="F42" s="26">
+      <c r="F42" s="25">
         <v>12863.496311206265</v>
       </c>
-      <c r="G42" s="26">
+      <c r="G42" s="25">
         <v>15745.206963155837</v>
       </c>
-      <c r="H42" s="26">
+      <c r="H42" s="25">
         <v>12793.115381337566</v>
       </c>
-      <c r="I42" s="26">
+      <c r="I42" s="25">
         <v>13018.983539112083</v>
       </c>
-      <c r="J42" s="26">
+      <c r="J42" s="25">
         <v>27879.747192050414</v>
       </c>
-      <c r="K42" s="26">
+      <c r="K42" s="25">
         <v>21193.287037931095</v>
       </c>
-      <c r="L42" s="26">
+      <c r="L42" s="25">
         <v>16619.916528380534</v>
       </c>
-      <c r="M42" s="26">
+      <c r="M42" s="25">
         <v>15432.067379178841</v>
       </c>
-      <c r="N42" s="26">
+      <c r="N42" s="25">
         <v>19638.096991627204</v>
       </c>
-      <c r="O42" s="26">
+      <c r="O42" s="25">
         <v>23441.704875460673</v>
       </c>
-      <c r="P42" s="26">
+      <c r="P42" s="25">
         <v>25066.78582625046</v>
       </c>
-      <c r="Q42" s="26">
+      <c r="Q42" s="25">
         <v>23532.422470706617</v>
       </c>
-      <c r="R42" s="26">
+      <c r="R42" s="25">
         <v>23378.897893980346</v>
       </c>
-      <c r="S42" s="26">
+      <c r="S42" s="25">
         <v>23824.470574551986</v>
       </c>
-      <c r="T42" s="26">
+      <c r="T42" s="25">
         <v>18895.622978983796</v>
       </c>
-      <c r="U42" s="26">
+      <c r="U42" s="25">
         <v>20833.73418258016</v>
       </c>
-      <c r="V42" s="26">
+      <c r="V42" s="25">
         <v>24530.300936673819</v>
       </c>
-      <c r="W42" s="26">
+      <c r="W42" s="25">
         <v>29236.445480524504</v>
       </c>
-      <c r="X42" s="26">
+      <c r="X42" s="25">
         <v>21268.372336264416</v>
       </c>
-      <c r="Y42" s="26">
+      <c r="Y42" s="25">
         <v>24308.177969138422</v>
       </c>
-      <c r="Z42" s="26">
+      <c r="Z42" s="25">
         <v>25198.156619366968</v>
       </c>
-      <c r="AA42" s="26">
+      <c r="AA42" s="25">
         <v>29560.362700742953</v>
       </c>
-      <c r="AB42" s="26">
+      <c r="AB42" s="25">
         <v>20099.279509799839</v>
       </c>
-      <c r="AC42" s="26">
+      <c r="AC42" s="25">
         <v>20685.20243101356</v>
       </c>
-      <c r="AD42" s="26">
+      <c r="AD42" s="25">
         <v>28533.001211817165</v>
       </c>
-      <c r="AE42" s="26">
+      <c r="AE42" s="25">
         <v>34022.81613170632</v>
       </c>
-      <c r="AF42" s="26">
+      <c r="AF42" s="25">
         <v>23854.768333393924</v>
       </c>
-      <c r="AG42" s="26">
+      <c r="AG42" s="25">
         <v>22635.435749119377</v>
       </c>
-      <c r="AH42" s="26">
+      <c r="AH42" s="25">
         <v>29255.986816566754</v>
       </c>
-      <c r="AI42" s="26">
+      <c r="AI42" s="25">
         <v>30590.2386270893</v>
       </c>
-      <c r="AJ42" s="26">
+      <c r="AJ42" s="25">
         <v>22386.39963299688</v>
       </c>
-      <c r="AK42" s="26">
+      <c r="AK42" s="25">
         <v>25051.458005276349</v>
       </c>
-      <c r="AL42" s="26">
+      <c r="AL42" s="25">
         <v>30394.177327650843</v>
       </c>
-      <c r="AM42" s="26">
+      <c r="AM42" s="25">
         <v>35595.138672997913</v>
       </c>
-      <c r="AN42" s="26">
+      <c r="AN42" s="25">
         <v>26291.219629175685</v>
       </c>
-      <c r="AO42" s="26">
+      <c r="AO42" s="25">
         <v>29840.503005279046</v>
       </c>
-      <c r="AP42" s="26">
+      <c r="AP42" s="25">
         <v>30028.327808639107</v>
       </c>
-      <c r="AQ42" s="26">
+      <c r="AQ42" s="25">
         <v>44334.717333960107</v>
       </c>
-      <c r="AR42" s="26">
+      <c r="AR42" s="25">
         <v>27288.51643301946</v>
       </c>
-      <c r="AS42" s="26">
+      <c r="AS42" s="25">
         <v>31747.549607047851</v>
       </c>
-      <c r="AT42" s="26">
+      <c r="AT42" s="25">
         <v>36142.157021573337</v>
       </c>
-      <c r="AU42" s="26">
+      <c r="AU42" s="25">
         <v>46292.311485991682</v>
       </c>
-      <c r="AV42" s="26">
+      <c r="AV42" s="25">
         <v>24182.516048577447</v>
       </c>
-      <c r="AW42" s="26">
+      <c r="AW42" s="25">
         <v>26771.067279914481</v>
       </c>
-      <c r="AX42" s="26">
+      <c r="AX42" s="25">
         <v>33678.767832686135</v>
       </c>
-      <c r="AY42" s="26">
+      <c r="AY42" s="25">
         <v>44704.922191080594</v>
       </c>
-      <c r="AZ42" s="26">
+      <c r="AZ42" s="25">
         <v>23659.569618300444</v>
       </c>
-      <c r="BA42" s="26">
+      <c r="BA42" s="25">
         <v>25967.311922243229</v>
       </c>
-      <c r="BB42" s="26">
+      <c r="BB42" s="25">
         <v>32896.63843762748</v>
       </c>
-      <c r="BC42" s="26">
+      <c r="BC42" s="25">
         <v>45121.351804934588</v>
       </c>
-      <c r="BD42" s="26">
+      <c r="BD42" s="25">
         <v>26041.824736643881</v>
       </c>
-      <c r="BE42" s="26">
+      <c r="BE42" s="25">
         <v>26850.666935763631</v>
       </c>
-      <c r="BF42" s="26">
+      <c r="BF42" s="25">
         <v>41827.410891983032</v>
       </c>
-      <c r="BG42" s="26">
+      <c r="BG42" s="25">
         <v>49512.767327502988</v>
       </c>
-      <c r="BH42" s="26">
+      <c r="BH42" s="25">
         <v>28580.060501402964</v>
       </c>
-      <c r="BI42" s="26">
+      <c r="BI42" s="25">
         <v>29590.330954814905</v>
       </c>
-      <c r="BJ42" s="26">
+      <c r="BJ42" s="25">
         <v>41764.586762748811</v>
       </c>
-      <c r="BK42" s="26">
+      <c r="BK42" s="25">
         <v>46477.695309697534</v>
       </c>
-      <c r="BL42" s="26">
+      <c r="BL42" s="25">
         <v>28287.194389674754</v>
       </c>
-      <c r="BM42" s="26">
+      <c r="BM42" s="25">
         <v>32059.230683040256</v>
       </c>
-      <c r="BN42" s="26">
+      <c r="BN42" s="25">
         <v>46383.173318465924</v>
       </c>
-      <c r="BO42" s="26">
+      <c r="BO42" s="25">
         <v>46543.873835961327</v>
       </c>
-      <c r="BP42" s="26">
+      <c r="BP42" s="25">
         <v>29322.772690243284</v>
       </c>
-      <c r="BQ42" s="26">
+      <c r="BQ42" s="25">
         <v>34556.716017512073</v>
       </c>
-      <c r="BR42" s="26">
+      <c r="BR42" s="25">
         <v>41621.494205789764</v>
       </c>
-      <c r="BS42" s="26">
+      <c r="BS42" s="25">
         <v>51011.944781831618</v>
       </c>
-      <c r="BT42" s="26">
+      <c r="BT42" s="25">
         <v>30440.296521687131</v>
       </c>
-      <c r="BU42" s="26">
+      <c r="BU42" s="25">
         <v>36991.750707884508</v>
       </c>
-      <c r="BV42" s="26">
+      <c r="BV42" s="25">
         <v>43913.473162055481</v>
       </c>
-      <c r="BW42" s="26">
+      <c r="BW42" s="25">
         <v>49764.057919797502</v>
       </c>
-      <c r="BX42" s="26">
+      <c r="BX42" s="25">
         <v>29963.557788390026</v>
       </c>
-      <c r="BY42" s="26">
+      <c r="BY42" s="25">
         <v>39681.399716053085</v>
       </c>
-      <c r="BZ42" s="26">
+      <c r="BZ42" s="25">
         <v>45590.119111540218</v>
       </c>
-      <c r="CA42" s="26">
+      <c r="CA42" s="25">
         <v>56863.457330680976</v>
       </c>
-      <c r="CB42" s="26">
+      <c r="CB42" s="25">
         <v>29033.80131277605</v>
       </c>
-      <c r="CC42" s="26">
+      <c r="CC42" s="25">
         <v>37369.637843153527</v>
       </c>
       <c r="CD42" s="16">
@@ -8497,28 +8478,28 @@
         <v>38884.103902952702</v>
       </c>
       <c r="CT42" s="16">
-        <v>43408.692713615004</v>
+        <v>43414.348216955084</v>
       </c>
       <c r="CU42" s="16">
-        <v>44833.381829186241</v>
+        <v>44831.737355391568</v>
       </c>
       <c r="CV42" s="16">
-        <v>31557.711001045427</v>
+        <v>31678.691740129572</v>
       </c>
       <c r="CW42" s="16">
-        <v>37293.706583945008</v>
+        <v>37347.520525451029</v>
       </c>
       <c r="CX42" s="16">
-        <v>44282.174571732874</v>
+        <v>44346.392024718021</v>
       </c>
       <c r="CY42" s="16">
-        <v>44263.971736186766</v>
+        <v>44256.940900622445</v>
       </c>
       <c r="CZ42" s="16">
-        <v>33155.948268038432</v>
+        <v>33249.868100998348</v>
       </c>
       <c r="DA42" s="16">
-        <v>39268.77292904981</v>
+        <v>39242.049728135236</v>
       </c>
       <c r="DB42" s="14"/>
       <c r="DC42" s="14"/>
@@ -9087,7 +9068,7 @@
     </row>
     <row r="49" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="CX49" s="4"/>
       <c r="CY49" s="4"/>
@@ -9111,7 +9092,7 @@
     </row>
     <row r="52" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="CX52" s="4"/>
       <c r="CY52" s="4"/>
@@ -9135,160 +9116,160 @@
     </row>
     <row r="55" spans="1:174" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22" t="s">
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="22" t="s">
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="22"/>
-      <c r="N55" s="22" t="s">
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="O55" s="22"/>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
-      <c r="R55" s="22" t="s">
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="S55" s="22"/>
-      <c r="T55" s="22"/>
-      <c r="U55" s="22"/>
-      <c r="V55" s="22" t="s">
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="W55" s="22"/>
-      <c r="X55" s="22"/>
-      <c r="Y55" s="22"/>
-      <c r="Z55" s="22" t="s">
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AA55" s="22"/>
-      <c r="AB55" s="22"/>
-      <c r="AC55" s="22"/>
-      <c r="AD55" s="22" t="s">
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="AE55" s="22"/>
-      <c r="AF55" s="22"/>
-      <c r="AG55" s="22"/>
-      <c r="AH55" s="22" t="s">
+      <c r="AE55" s="30"/>
+      <c r="AF55" s="30"/>
+      <c r="AG55" s="30"/>
+      <c r="AH55" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="AI55" s="22"/>
-      <c r="AJ55" s="22"/>
-      <c r="AK55" s="22"/>
-      <c r="AL55" s="22" t="s">
+      <c r="AI55" s="30"/>
+      <c r="AJ55" s="30"/>
+      <c r="AK55" s="30"/>
+      <c r="AL55" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="AM55" s="22"/>
-      <c r="AN55" s="22"/>
-      <c r="AO55" s="22"/>
-      <c r="AP55" s="22" t="s">
+      <c r="AM55" s="30"/>
+      <c r="AN55" s="30"/>
+      <c r="AO55" s="30"/>
+      <c r="AP55" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="AQ55" s="22"/>
-      <c r="AR55" s="22"/>
-      <c r="AS55" s="22"/>
-      <c r="AT55" s="22" t="s">
+      <c r="AQ55" s="30"/>
+      <c r="AR55" s="30"/>
+      <c r="AS55" s="30"/>
+      <c r="AT55" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="AU55" s="22"/>
-      <c r="AV55" s="22"/>
-      <c r="AW55" s="22"/>
-      <c r="AX55" s="22" t="s">
+      <c r="AU55" s="30"/>
+      <c r="AV55" s="30"/>
+      <c r="AW55" s="30"/>
+      <c r="AX55" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="AY55" s="22"/>
-      <c r="AZ55" s="22"/>
-      <c r="BA55" s="22"/>
-      <c r="BB55" s="22" t="s">
+      <c r="AY55" s="30"/>
+      <c r="AZ55" s="30"/>
+      <c r="BA55" s="30"/>
+      <c r="BB55" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="BC55" s="22"/>
-      <c r="BD55" s="22"/>
-      <c r="BE55" s="22"/>
-      <c r="BF55" s="22" t="s">
+      <c r="BC55" s="30"/>
+      <c r="BD55" s="30"/>
+      <c r="BE55" s="30"/>
+      <c r="BF55" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="BG55" s="22"/>
-      <c r="BH55" s="22"/>
-      <c r="BI55" s="22"/>
-      <c r="BJ55" s="22" t="s">
+      <c r="BG55" s="30"/>
+      <c r="BH55" s="30"/>
+      <c r="BI55" s="30"/>
+      <c r="BJ55" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="BK55" s="22"/>
-      <c r="BL55" s="22"/>
-      <c r="BM55" s="22"/>
-      <c r="BN55" s="22" t="s">
+      <c r="BK55" s="30"/>
+      <c r="BL55" s="30"/>
+      <c r="BM55" s="30"/>
+      <c r="BN55" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="BO55" s="22"/>
-      <c r="BP55" s="22"/>
-      <c r="BQ55" s="22"/>
-      <c r="BR55" s="22" t="s">
+      <c r="BO55" s="30"/>
+      <c r="BP55" s="30"/>
+      <c r="BQ55" s="30"/>
+      <c r="BR55" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="BS55" s="22"/>
-      <c r="BT55" s="22"/>
-      <c r="BU55" s="22"/>
-      <c r="BV55" s="22" t="s">
+      <c r="BS55" s="30"/>
+      <c r="BT55" s="30"/>
+      <c r="BU55" s="30"/>
+      <c r="BV55" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="BW55" s="22"/>
-      <c r="BX55" s="22"/>
-      <c r="BY55" s="22"/>
-      <c r="BZ55" s="22" t="s">
+      <c r="BW55" s="30"/>
+      <c r="BX55" s="30"/>
+      <c r="BY55" s="30"/>
+      <c r="BZ55" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="CA55" s="22"/>
-      <c r="CB55" s="22"/>
-      <c r="CC55" s="22"/>
-      <c r="CD55" s="22" t="s">
+      <c r="CA55" s="30"/>
+      <c r="CB55" s="30"/>
+      <c r="CC55" s="30"/>
+      <c r="CD55" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="CE55" s="22"/>
-      <c r="CF55" s="22"/>
-      <c r="CG55" s="22"/>
-      <c r="CH55" s="23" t="s">
+      <c r="CE55" s="30"/>
+      <c r="CF55" s="30"/>
+      <c r="CG55" s="30"/>
+      <c r="CH55" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="CI55" s="23"/>
-      <c r="CJ55" s="23"/>
-      <c r="CK55" s="23"/>
-      <c r="CL55" s="24" t="s">
+      <c r="CI55" s="22"/>
+      <c r="CJ55" s="22"/>
+      <c r="CK55" s="22"/>
+      <c r="CL55" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="CM55" s="24"/>
-      <c r="CN55" s="24"/>
-      <c r="CO55" s="24"/>
-      <c r="CP55" s="28" t="s">
+      <c r="CM55" s="23"/>
+      <c r="CN55" s="23"/>
+      <c r="CO55" s="23"/>
+      <c r="CP55" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="CQ55" s="28"/>
-      <c r="CR55" s="28"/>
-      <c r="CS55" s="28"/>
-      <c r="CT55" s="28" t="s">
+      <c r="CQ55" s="26"/>
+      <c r="CR55" s="26"/>
+      <c r="CS55" s="26"/>
+      <c r="CT55" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="CU55" s="28"/>
-      <c r="CV55" s="28"/>
-      <c r="CW55" s="28"/>
-      <c r="CX55" s="29"/>
-      <c r="CY55" s="29"/>
-      <c r="CZ55" s="29"/>
-      <c r="DA55" s="29"/>
+      <c r="CU55" s="26"/>
+      <c r="CV55" s="26"/>
+      <c r="CW55" s="26"/>
+      <c r="CX55" s="27"/>
+      <c r="CY55" s="27"/>
+      <c r="CZ55" s="27"/>
+      <c r="DA55" s="27"/>
     </row>
     <row r="56" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
@@ -9594,10 +9575,10 @@
       <c r="CW56" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX56" s="30"/>
-      <c r="CY56" s="30"/>
-      <c r="CZ56" s="30"/>
-      <c r="DA56" s="30"/>
+      <c r="CX56" s="28"/>
+      <c r="CY56" s="28"/>
+      <c r="CZ56" s="28"/>
+      <c r="DA56" s="28"/>
     </row>
     <row r="57" spans="1:174" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
@@ -9890,10 +9871,10 @@
         <v>-47.04872894284189</v>
       </c>
       <c r="CQ58" s="17">
-        <v>67.381560460660808</v>
+        <v>67.557864081165917</v>
       </c>
       <c r="CR58" s="17">
-        <v>21.147337368276993</v>
+        <v>21.125987573353271</v>
       </c>
       <c r="CS58" s="17">
         <v>-28.856659655013402</v>
@@ -9902,13 +9883,13 @@
         <v>4.5913203965616276</v>
       </c>
       <c r="CU58" s="17">
-        <v>-13.359199190295342</v>
+        <v>-12.971653530071904</v>
       </c>
       <c r="CV58" s="17">
-        <v>5.6616984200754388</v>
+        <v>6.3354690167391396</v>
       </c>
       <c r="CW58" s="17">
-        <v>30.282181600833354</v>
+        <v>33.612844800019445</v>
       </c>
       <c r="CX58" s="18"/>
       <c r="CY58" s="18"/>
@@ -9933,10 +9914,10 @@
         <v>39</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D59" s="18">
         <v>278.18996024535841</v>
@@ -9945,7 +9926,7 @@
         <v>-34.541677306791186</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G59" s="18">
         <v>593.6028170935565</v>
@@ -10212,25 +10193,25 @@
         <v>-2.6344447098315413</v>
       </c>
       <c r="CQ59" s="17">
-        <v>-3.7333348789425145</v>
+        <v>-3.7333348789425429</v>
       </c>
       <c r="CR59" s="17">
         <v>-31.826902392252293</v>
       </c>
       <c r="CS59" s="17">
-        <v>-24.202836747970053</v>
+        <v>-24.202836747970039</v>
       </c>
       <c r="CT59" s="17">
         <v>38.484665036958404</v>
       </c>
       <c r="CU59" s="17">
-        <v>-8.717078209869328</v>
+        <v>-8.7185118638445118</v>
       </c>
       <c r="CV59" s="17">
         <v>-3.2569113667349114</v>
       </c>
       <c r="CW59" s="17">
-        <v>-15.455140657915763</v>
+        <v>-13.906081026266392</v>
       </c>
       <c r="CX59" s="18"/>
       <c r="CY59" s="18"/>
@@ -10596,19 +10577,19 @@
         <v>33.423878949526284</v>
       </c>
       <c r="CS60" s="17">
-        <v>26.462090046372637</v>
+        <v>26.548984925824755</v>
       </c>
       <c r="CT60" s="17">
-        <v>53.824743410979238</v>
+        <v>54.265060241339057</v>
       </c>
       <c r="CU60" s="17">
-        <v>37.809097887290022</v>
+        <v>37.872883659031345</v>
       </c>
       <c r="CV60" s="17">
-        <v>30.768004754055397</v>
+        <v>30.934024592962004</v>
       </c>
       <c r="CW60" s="17">
-        <v>44.293699668450074</v>
+        <v>44.183769123410343</v>
       </c>
       <c r="CX60" s="18"/>
       <c r="CY60" s="18"/>
@@ -10758,7 +10739,7 @@
         <v>233.08189580134001</v>
       </c>
       <c r="Y61" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z61" s="18">
         <v>485.73457917091321</v>
@@ -10965,28 +10946,28 @@
         <v>-17.055116369346194</v>
       </c>
       <c r="CP61" s="17">
-        <v>-25.893784675017713</v>
+        <v>-25.301993051510095</v>
       </c>
       <c r="CQ61" s="17">
-        <v>-20.760144292809954</v>
+        <v>-20.374959049037102</v>
       </c>
       <c r="CR61" s="17">
-        <v>-12.034600527598741</v>
+        <v>-11.149850485337296</v>
       </c>
       <c r="CS61" s="17">
-        <v>-3.3556878671422936</v>
+        <v>-2.2785753375667355</v>
       </c>
       <c r="CT61" s="17">
-        <v>-10.011194762308833</v>
+        <v>-10.433650563952639</v>
       </c>
       <c r="CU61" s="17">
-        <v>3.7086129152414458</v>
+        <v>3.2456340677960043</v>
       </c>
       <c r="CV61" s="17">
-        <v>8.6050429390267595</v>
+        <v>8.7824269640835837</v>
       </c>
       <c r="CW61" s="17">
-        <v>11.885310511919897</v>
+        <v>14.45546225081948</v>
       </c>
       <c r="CX61" s="18"/>
       <c r="CY61" s="18"/>
@@ -11355,7 +11336,7 @@
         <v>15.448253723747825</v>
       </c>
       <c r="CT62" s="17">
-        <v>7.8357068120624973</v>
+        <v>7.8357068120624689</v>
       </c>
       <c r="CU62" s="17">
         <v>-19.012782432992509</v>
@@ -11364,7 +11345,7 @@
         <v>17.423046423374714</v>
       </c>
       <c r="CW62" s="17">
-        <v>2.8927467540575122</v>
+        <v>-0.23867834853777481</v>
       </c>
       <c r="CX62" s="18"/>
       <c r="CY62" s="18"/>
@@ -11721,28 +11702,28 @@
         <v>8.5405575936430012</v>
       </c>
       <c r="CP63" s="17">
-        <v>10.136501669190935</v>
+        <v>9.8551146260624733</v>
       </c>
       <c r="CQ63" s="17">
-        <v>4.048116908501413</v>
+        <v>3.440020610129352</v>
       </c>
       <c r="CR63" s="17">
-        <v>7.1935184300024275</v>
+        <v>7.7840313735523239</v>
       </c>
       <c r="CS63" s="17">
-        <v>6.4166380508385004</v>
+        <v>6.576381132940341</v>
       </c>
       <c r="CT63" s="17">
-        <v>4.7247854817657782</v>
+        <v>5.187752839284073</v>
       </c>
       <c r="CU63" s="17">
-        <v>3.0764754477112177</v>
+        <v>2.8395929633893218</v>
       </c>
       <c r="CV63" s="17">
-        <v>5.1470276632875596</v>
+        <v>4.3751508088909929</v>
       </c>
       <c r="CW63" s="17">
-        <v>2.4044428443638139</v>
+        <v>0.90107336555487905</v>
       </c>
       <c r="CX63" s="18"/>
       <c r="CY63" s="18"/>
@@ -12274,28 +12255,28 @@
         <v>-7.9447372843284683</v>
       </c>
       <c r="CP65" s="17">
-        <v>-13.528236534688943</v>
+        <v>-13.463571241545154</v>
       </c>
       <c r="CQ65" s="17">
-        <v>7.9100366788023848</v>
+        <v>7.9185920633249651</v>
       </c>
       <c r="CR65" s="17">
-        <v>8.4142322758499262</v>
+        <v>8.7213672982808816</v>
       </c>
       <c r="CS65" s="17">
-        <v>3.2409260699431286</v>
+        <v>3.3832143721173225</v>
       </c>
       <c r="CT65" s="17">
-        <v>15.96975724339849</v>
+        <v>16.094282495696916</v>
       </c>
       <c r="CU65" s="17">
-        <v>7.4570130192003461</v>
+        <v>7.4104713197486092</v>
       </c>
       <c r="CV65" s="17">
-        <v>13.651531905058562</v>
+        <v>13.613395249633612</v>
       </c>
       <c r="CW65" s="17">
-        <v>16.445987289713202</v>
+        <v>16.144426974359675</v>
       </c>
       <c r="CX65" s="18"/>
       <c r="CY65" s="18"/>
@@ -12473,10 +12454,10 @@
       <c r="CU66" s="8"/>
       <c r="CV66" s="8"/>
       <c r="CW66" s="8"/>
-      <c r="CX66" s="31"/>
-      <c r="CY66" s="31"/>
-      <c r="CZ66" s="31"/>
-      <c r="DA66" s="31"/>
+      <c r="CX66" s="29"/>
+      <c r="CY66" s="29"/>
+      <c r="CZ66" s="29"/>
+      <c r="DA66" s="29"/>
     </row>
     <row r="67" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
@@ -12857,7 +12838,7 @@
     </row>
     <row r="72" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="CX72" s="4"/>
       <c r="CY72" s="4"/>
@@ -12881,7 +12862,7 @@
     </row>
     <row r="75" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="CX75" s="4"/>
       <c r="CY75" s="4"/>
@@ -12905,160 +12886,160 @@
     </row>
     <row r="78" spans="1:174" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="22" t="s">
+      <c r="B78" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="22" t="s">
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+      <c r="F78" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-      <c r="J78" s="22" t="s">
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="K78" s="27"/>
-      <c r="L78" s="27"/>
-      <c r="M78" s="27"/>
-      <c r="N78" s="22" t="s">
+      <c r="K78" s="31"/>
+      <c r="L78" s="31"/>
+      <c r="M78" s="31"/>
+      <c r="N78" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="O78" s="27"/>
-      <c r="P78" s="27"/>
-      <c r="Q78" s="27"/>
-      <c r="R78" s="22" t="s">
+      <c r="O78" s="31"/>
+      <c r="P78" s="31"/>
+      <c r="Q78" s="31"/>
+      <c r="R78" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="S78" s="27"/>
-      <c r="T78" s="27"/>
-      <c r="U78" s="27"/>
-      <c r="V78" s="22" t="s">
+      <c r="S78" s="31"/>
+      <c r="T78" s="31"/>
+      <c r="U78" s="31"/>
+      <c r="V78" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="W78" s="27"/>
-      <c r="X78" s="27"/>
-      <c r="Y78" s="27"/>
-      <c r="Z78" s="22" t="s">
+      <c r="W78" s="31"/>
+      <c r="X78" s="31"/>
+      <c r="Y78" s="31"/>
+      <c r="Z78" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AA78" s="27"/>
-      <c r="AB78" s="27"/>
-      <c r="AC78" s="27"/>
-      <c r="AD78" s="22" t="s">
+      <c r="AA78" s="31"/>
+      <c r="AB78" s="31"/>
+      <c r="AC78" s="31"/>
+      <c r="AD78" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="AE78" s="27"/>
-      <c r="AF78" s="27"/>
-      <c r="AG78" s="27"/>
-      <c r="AH78" s="22" t="s">
+      <c r="AE78" s="31"/>
+      <c r="AF78" s="31"/>
+      <c r="AG78" s="31"/>
+      <c r="AH78" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="AI78" s="27"/>
-      <c r="AJ78" s="27"/>
-      <c r="AK78" s="27"/>
-      <c r="AL78" s="22" t="s">
+      <c r="AI78" s="31"/>
+      <c r="AJ78" s="31"/>
+      <c r="AK78" s="31"/>
+      <c r="AL78" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="AM78" s="27"/>
-      <c r="AN78" s="27"/>
-      <c r="AO78" s="27"/>
-      <c r="AP78" s="22" t="s">
+      <c r="AM78" s="31"/>
+      <c r="AN78" s="31"/>
+      <c r="AO78" s="31"/>
+      <c r="AP78" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="AQ78" s="27"/>
-      <c r="AR78" s="27"/>
-      <c r="AS78" s="27"/>
-      <c r="AT78" s="22" t="s">
+      <c r="AQ78" s="31"/>
+      <c r="AR78" s="31"/>
+      <c r="AS78" s="31"/>
+      <c r="AT78" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="AU78" s="27"/>
-      <c r="AV78" s="27"/>
-      <c r="AW78" s="27"/>
-      <c r="AX78" s="22" t="s">
+      <c r="AU78" s="31"/>
+      <c r="AV78" s="31"/>
+      <c r="AW78" s="31"/>
+      <c r="AX78" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="AY78" s="27"/>
-      <c r="AZ78" s="27"/>
-      <c r="BA78" s="27"/>
-      <c r="BB78" s="22" t="s">
+      <c r="AY78" s="31"/>
+      <c r="AZ78" s="31"/>
+      <c r="BA78" s="31"/>
+      <c r="BB78" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="BC78" s="27"/>
-      <c r="BD78" s="27"/>
-      <c r="BE78" s="27"/>
-      <c r="BF78" s="22" t="s">
+      <c r="BC78" s="31"/>
+      <c r="BD78" s="31"/>
+      <c r="BE78" s="31"/>
+      <c r="BF78" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="BG78" s="27"/>
-      <c r="BH78" s="27"/>
-      <c r="BI78" s="27"/>
-      <c r="BJ78" s="22" t="s">
+      <c r="BG78" s="31"/>
+      <c r="BH78" s="31"/>
+      <c r="BI78" s="31"/>
+      <c r="BJ78" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="BK78" s="27"/>
-      <c r="BL78" s="27"/>
-      <c r="BM78" s="27"/>
-      <c r="BN78" s="22" t="s">
+      <c r="BK78" s="31"/>
+      <c r="BL78" s="31"/>
+      <c r="BM78" s="31"/>
+      <c r="BN78" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="BO78" s="27"/>
-      <c r="BP78" s="27"/>
-      <c r="BQ78" s="27"/>
-      <c r="BR78" s="22" t="s">
+      <c r="BO78" s="31"/>
+      <c r="BP78" s="31"/>
+      <c r="BQ78" s="31"/>
+      <c r="BR78" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="BS78" s="27"/>
-      <c r="BT78" s="27"/>
-      <c r="BU78" s="27"/>
-      <c r="BV78" s="22" t="s">
+      <c r="BS78" s="31"/>
+      <c r="BT78" s="31"/>
+      <c r="BU78" s="31"/>
+      <c r="BV78" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="BW78" s="27"/>
-      <c r="BX78" s="27"/>
-      <c r="BY78" s="27"/>
-      <c r="BZ78" s="22" t="s">
+      <c r="BW78" s="31"/>
+      <c r="BX78" s="31"/>
+      <c r="BY78" s="31"/>
+      <c r="BZ78" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="CA78" s="27"/>
-      <c r="CB78" s="27"/>
-      <c r="CC78" s="27"/>
-      <c r="CD78" s="22" t="s">
+      <c r="CA78" s="31"/>
+      <c r="CB78" s="31"/>
+      <c r="CC78" s="31"/>
+      <c r="CD78" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="CE78" s="22"/>
-      <c r="CF78" s="22"/>
-      <c r="CG78" s="22"/>
-      <c r="CH78" s="23" t="s">
+      <c r="CE78" s="30"/>
+      <c r="CF78" s="30"/>
+      <c r="CG78" s="30"/>
+      <c r="CH78" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="CI78" s="23"/>
-      <c r="CJ78" s="23"/>
-      <c r="CK78" s="23"/>
-      <c r="CL78" s="24" t="s">
+      <c r="CI78" s="22"/>
+      <c r="CJ78" s="22"/>
+      <c r="CK78" s="22"/>
+      <c r="CL78" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="CM78" s="24"/>
-      <c r="CN78" s="24"/>
-      <c r="CO78" s="24"/>
-      <c r="CP78" s="28" t="s">
+      <c r="CM78" s="23"/>
+      <c r="CN78" s="23"/>
+      <c r="CO78" s="23"/>
+      <c r="CP78" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="CQ78" s="28"/>
-      <c r="CR78" s="28"/>
-      <c r="CS78" s="28"/>
-      <c r="CT78" s="28" t="s">
+      <c r="CQ78" s="26"/>
+      <c r="CR78" s="26"/>
+      <c r="CS78" s="26"/>
+      <c r="CT78" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="CU78" s="28"/>
-      <c r="CV78" s="28"/>
-      <c r="CW78" s="28"/>
-      <c r="CX78" s="29"/>
-      <c r="CY78" s="29"/>
-      <c r="CZ78" s="29"/>
-      <c r="DA78" s="29"/>
+      <c r="CU78" s="26"/>
+      <c r="CV78" s="26"/>
+      <c r="CW78" s="26"/>
+      <c r="CX78" s="27"/>
+      <c r="CY78" s="27"/>
+      <c r="CZ78" s="27"/>
+      <c r="DA78" s="27"/>
     </row>
     <row r="79" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
@@ -13364,10 +13345,10 @@
       <c r="CW79" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX79" s="30"/>
-      <c r="CY79" s="30"/>
-      <c r="CZ79" s="30"/>
-      <c r="DA79" s="30"/>
+      <c r="CX79" s="28"/>
+      <c r="CY79" s="28"/>
+      <c r="CZ79" s="28"/>
+      <c r="DA79" s="28"/>
     </row>
     <row r="80" spans="1:174" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
@@ -13660,25 +13641,25 @@
         <v>-13.207767698087409</v>
       </c>
       <c r="CQ81" s="17">
-        <v>83.591863199592069</v>
+        <v>83.785241192295018</v>
       </c>
       <c r="CR81" s="17">
-        <v>21.370908964858629</v>
+        <v>21.349519769913016</v>
       </c>
       <c r="CS81" s="17">
         <v>-29.801380981949634</v>
       </c>
       <c r="CT81" s="17">
-        <v>11.521492375779758</v>
+        <v>11.521492375779772</v>
       </c>
       <c r="CU81" s="17">
-        <v>5.8649011437991021</v>
+        <v>6.3384365061784678</v>
       </c>
       <c r="CV81" s="17">
-        <v>28.078351955192034</v>
+        <v>28.895066326689999</v>
       </c>
       <c r="CW81" s="17">
-        <v>59.699481670495459</v>
+        <v>63.78219797132229</v>
       </c>
       <c r="CX81" s="18"/>
       <c r="CY81" s="18"/>
@@ -13759,10 +13740,10 @@
         <v>39</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D82" s="18">
         <v>176.59409765019387</v>
@@ -13771,7 +13752,7 @@
         <v>-28.111023918922697</v>
       </c>
       <c r="F82" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G82" s="18">
         <v>557.75453877962764</v>
@@ -14038,7 +14019,7 @@
         <v>3.0761252136109647</v>
       </c>
       <c r="CQ82" s="17">
-        <v>-10.365276130208201</v>
+        <v>-10.36527613020823</v>
       </c>
       <c r="CR82" s="17">
         <v>-22.660135797957466</v>
@@ -14050,13 +14031,13 @@
         <v>-14.917725399995888</v>
       </c>
       <c r="CU82" s="17">
-        <v>-18.680082642090824</v>
+        <v>-18.681359821003326</v>
       </c>
       <c r="CV82" s="17">
         <v>-2.9894248775022163</v>
       </c>
       <c r="CW82" s="17">
-        <v>-10.053966933703947</v>
+        <v>-8.4059451623714807</v>
       </c>
       <c r="CX82" s="18"/>
       <c r="CY82" s="18"/>
@@ -14422,19 +14403,19 @@
         <v>1.5249936232408174</v>
       </c>
       <c r="CS83" s="17">
-        <v>-6.1942467330116813</v>
+        <v>-6.1297907397645304</v>
       </c>
       <c r="CT83" s="17">
-        <v>7.4584652963757776</v>
+        <v>7.7665003264771855</v>
       </c>
       <c r="CU83" s="17">
-        <v>0.81542498168987265</v>
+        <v>0.86208800890995008</v>
       </c>
       <c r="CV83" s="17">
-        <v>-5.8896963334616856</v>
+        <v>-5.7702162092251825</v>
       </c>
       <c r="CW83" s="17">
-        <v>-7.441408999363702</v>
+        <v>-7.5119250120530268</v>
       </c>
       <c r="CX83" s="18"/>
       <c r="CY83" s="18"/>
@@ -14584,7 +14565,7 @@
         <v>310.82743387501478</v>
       </c>
       <c r="Y84" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z84" s="18">
         <v>264.68039104028156</v>
@@ -14791,28 +14772,28 @@
         <v>6.9120335398334021</v>
       </c>
       <c r="CP84" s="17">
-        <v>6.7385453033738543</v>
+        <v>7.5909296376555915</v>
       </c>
       <c r="CQ84" s="17">
-        <v>-7.3747771832174891</v>
+        <v>-6.9245256183731954</v>
       </c>
       <c r="CR84" s="17">
-        <v>-4.1679267923236978</v>
+        <v>-3.2040542773458895</v>
       </c>
       <c r="CS84" s="17">
-        <v>0.61106125816603196</v>
+        <v>1.7323836857713957</v>
       </c>
       <c r="CT84" s="17">
-        <v>-7.3381510112274952</v>
+        <v>-7.7731555164318422</v>
       </c>
       <c r="CU84" s="17">
-        <v>4.4268530654486966</v>
+        <v>3.960667830533751</v>
       </c>
       <c r="CV84" s="17">
-        <v>9.2632845601800398</v>
+        <v>9.4417436876912149</v>
       </c>
       <c r="CW84" s="17">
-        <v>10.16415889062381</v>
+        <v>12.69477352843171</v>
       </c>
       <c r="CX84" s="18"/>
       <c r="CY84" s="18"/>
@@ -15181,7 +15162,7 @@
         <v>-0.84368431371547103</v>
       </c>
       <c r="CT85" s="17">
-        <v>-6.05508539184423</v>
+        <v>-6.0550853918442584</v>
       </c>
       <c r="CU85" s="17">
         <v>-17.006660775415725</v>
@@ -15190,7 +15171,7 @@
         <v>10.42813482787291</v>
       </c>
       <c r="CW85" s="17">
-        <v>-8.8596862262749596</v>
+        <v>-11.633439240096564</v>
       </c>
       <c r="CX85" s="18"/>
       <c r="CY85" s="18"/>
@@ -15547,28 +15528,28 @@
         <v>7.6755011240014426</v>
       </c>
       <c r="CP86" s="17">
-        <v>8.7124622705884462</v>
+        <v>8.4347134966041182</v>
       </c>
       <c r="CQ86" s="17">
-        <v>4.1400592798491544</v>
+        <v>3.531425635705304</v>
       </c>
       <c r="CR86" s="17">
-        <v>7.5078689239320084</v>
+        <v>8.1001135769938912</v>
       </c>
       <c r="CS86" s="17">
-        <v>6.791344522848533</v>
+        <v>6.9516500805915769</v>
       </c>
       <c r="CT86" s="17">
-        <v>4.5711399631599363</v>
+        <v>5.0334280845315789</v>
       </c>
       <c r="CU86" s="17">
-        <v>2.4067594149992431</v>
+        <v>2.1714160209201481</v>
       </c>
       <c r="CV86" s="17">
-        <v>3.9810485666904185</v>
+        <v>3.2177310819438958</v>
       </c>
       <c r="CW86" s="17">
-        <v>1.7232524217138092</v>
+        <v>0.2298832989659445</v>
       </c>
       <c r="CX86" s="18"/>
       <c r="CY86" s="18"/>
@@ -16100,28 +16081,28 @@
         <v>10.502654729296637</v>
       </c>
       <c r="CP88" s="17">
-        <v>0.5468690472596478</v>
+        <v>0.55996880028568796</v>
       </c>
       <c r="CQ88" s="17">
-        <v>6.6256131446331921</v>
+        <v>6.6217021519865682</v>
       </c>
       <c r="CR88" s="17">
-        <v>1.3189902868091252</v>
+        <v>1.7074102938163378</v>
       </c>
       <c r="CS88" s="17">
-        <v>-4.0900963616829671</v>
+        <v>-3.9517006263965584</v>
       </c>
       <c r="CT88" s="17">
-        <v>2.0122279744303455</v>
+        <v>2.1468566177827313</v>
       </c>
       <c r="CU88" s="17">
-        <v>-1.2700583131759089</v>
+        <v>-1.2821195177259739</v>
       </c>
       <c r="CV88" s="17">
-        <v>5.0644904725189406</v>
+        <v>4.9597261583831767</v>
       </c>
       <c r="CW88" s="17">
-        <v>5.295977595198508</v>
+        <v>5.0727040939522396</v>
       </c>
       <c r="CX88" s="18"/>
       <c r="CY88" s="18"/>
@@ -16299,10 +16280,10 @@
       <c r="CU89" s="8"/>
       <c r="CV89" s="8"/>
       <c r="CW89" s="8"/>
-      <c r="CX89" s="31"/>
-      <c r="CY89" s="31"/>
-      <c r="CZ89" s="31"/>
-      <c r="DA89" s="31"/>
+      <c r="CX89" s="29"/>
+      <c r="CY89" s="29"/>
+      <c r="CZ89" s="29"/>
+      <c r="DA89" s="29"/>
     </row>
     <row r="90" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9" t="s">
@@ -16679,7 +16660,7 @@
     </row>
     <row r="94" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="CX94" s="4"/>
       <c r="CY94" s="4"/>
@@ -16699,7 +16680,7 @@
     </row>
     <row r="97" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -16710,162 +16691,162 @@
     <row r="99" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="100" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="11"/>
-      <c r="B100" s="22">
+      <c r="B100" s="30">
         <v>2000</v>
       </c>
-      <c r="C100" s="22"/>
-      <c r="D100" s="22"/>
-      <c r="E100" s="22"/>
-      <c r="F100" s="22">
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30">
         <v>2001</v>
       </c>
-      <c r="G100" s="22"/>
-      <c r="H100" s="22"/>
-      <c r="I100" s="22"/>
-      <c r="J100" s="22">
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="30">
         <v>2002</v>
       </c>
-      <c r="K100" s="22"/>
-      <c r="L100" s="22"/>
-      <c r="M100" s="22"/>
-      <c r="N100" s="22">
+      <c r="K100" s="30"/>
+      <c r="L100" s="30"/>
+      <c r="M100" s="30"/>
+      <c r="N100" s="30">
         <v>2003</v>
       </c>
-      <c r="O100" s="22"/>
-      <c r="P100" s="22"/>
-      <c r="Q100" s="22"/>
-      <c r="R100" s="22">
+      <c r="O100" s="30"/>
+      <c r="P100" s="30"/>
+      <c r="Q100" s="30"/>
+      <c r="R100" s="30">
         <v>2004</v>
       </c>
-      <c r="S100" s="22"/>
-      <c r="T100" s="22"/>
-      <c r="U100" s="22"/>
-      <c r="V100" s="22">
+      <c r="S100" s="30"/>
+      <c r="T100" s="30"/>
+      <c r="U100" s="30"/>
+      <c r="V100" s="30">
         <v>2005</v>
       </c>
-      <c r="W100" s="22"/>
-      <c r="X100" s="22"/>
-      <c r="Y100" s="22"/>
-      <c r="Z100" s="22">
+      <c r="W100" s="30"/>
+      <c r="X100" s="30"/>
+      <c r="Y100" s="30"/>
+      <c r="Z100" s="30">
         <v>2006</v>
       </c>
-      <c r="AA100" s="22"/>
-      <c r="AB100" s="22"/>
-      <c r="AC100" s="22"/>
-      <c r="AD100" s="22">
+      <c r="AA100" s="30"/>
+      <c r="AB100" s="30"/>
+      <c r="AC100" s="30"/>
+      <c r="AD100" s="30">
         <v>2007</v>
       </c>
-      <c r="AE100" s="22"/>
-      <c r="AF100" s="22"/>
-      <c r="AG100" s="22"/>
-      <c r="AH100" s="22">
+      <c r="AE100" s="30"/>
+      <c r="AF100" s="30"/>
+      <c r="AG100" s="30"/>
+      <c r="AH100" s="30">
         <v>2008</v>
       </c>
-      <c r="AI100" s="22"/>
-      <c r="AJ100" s="22"/>
-      <c r="AK100" s="22"/>
-      <c r="AL100" s="22">
+      <c r="AI100" s="30"/>
+      <c r="AJ100" s="30"/>
+      <c r="AK100" s="30"/>
+      <c r="AL100" s="30">
         <v>2009</v>
       </c>
-      <c r="AM100" s="22"/>
-      <c r="AN100" s="22"/>
-      <c r="AO100" s="22"/>
-      <c r="AP100" s="22">
+      <c r="AM100" s="30"/>
+      <c r="AN100" s="30"/>
+      <c r="AO100" s="30"/>
+      <c r="AP100" s="30">
         <v>2010</v>
       </c>
-      <c r="AQ100" s="22"/>
-      <c r="AR100" s="22"/>
-      <c r="AS100" s="22"/>
-      <c r="AT100" s="22">
+      <c r="AQ100" s="30"/>
+      <c r="AR100" s="30"/>
+      <c r="AS100" s="30"/>
+      <c r="AT100" s="30">
         <v>2011</v>
       </c>
-      <c r="AU100" s="22"/>
-      <c r="AV100" s="22"/>
-      <c r="AW100" s="22"/>
-      <c r="AX100" s="22">
+      <c r="AU100" s="30"/>
+      <c r="AV100" s="30"/>
+      <c r="AW100" s="30"/>
+      <c r="AX100" s="30">
         <v>2012</v>
       </c>
-      <c r="AY100" s="22"/>
-      <c r="AZ100" s="22"/>
-      <c r="BA100" s="22"/>
-      <c r="BB100" s="22">
+      <c r="AY100" s="30"/>
+      <c r="AZ100" s="30"/>
+      <c r="BA100" s="30"/>
+      <c r="BB100" s="30">
         <v>2013</v>
       </c>
-      <c r="BC100" s="22"/>
-      <c r="BD100" s="22"/>
-      <c r="BE100" s="22"/>
-      <c r="BF100" s="22">
+      <c r="BC100" s="30"/>
+      <c r="BD100" s="30"/>
+      <c r="BE100" s="30"/>
+      <c r="BF100" s="30">
         <v>2014</v>
       </c>
-      <c r="BG100" s="22"/>
-      <c r="BH100" s="22"/>
-      <c r="BI100" s="22"/>
-      <c r="BJ100" s="22">
+      <c r="BG100" s="30"/>
+      <c r="BH100" s="30"/>
+      <c r="BI100" s="30"/>
+      <c r="BJ100" s="30">
         <v>2015</v>
       </c>
-      <c r="BK100" s="22"/>
-      <c r="BL100" s="22"/>
-      <c r="BM100" s="22"/>
-      <c r="BN100" s="22">
+      <c r="BK100" s="30"/>
+      <c r="BL100" s="30"/>
+      <c r="BM100" s="30"/>
+      <c r="BN100" s="30">
         <v>2016</v>
       </c>
-      <c r="BO100" s="22"/>
-      <c r="BP100" s="22"/>
-      <c r="BQ100" s="22"/>
-      <c r="BR100" s="22">
+      <c r="BO100" s="30"/>
+      <c r="BP100" s="30"/>
+      <c r="BQ100" s="30"/>
+      <c r="BR100" s="30">
         <v>2017</v>
       </c>
-      <c r="BS100" s="22"/>
-      <c r="BT100" s="22"/>
-      <c r="BU100" s="22"/>
-      <c r="BV100" s="22">
+      <c r="BS100" s="30"/>
+      <c r="BT100" s="30"/>
+      <c r="BU100" s="30"/>
+      <c r="BV100" s="30">
         <v>2018</v>
       </c>
-      <c r="BW100" s="22"/>
-      <c r="BX100" s="22"/>
-      <c r="BY100" s="22"/>
-      <c r="BZ100" s="22">
+      <c r="BW100" s="30"/>
+      <c r="BX100" s="30"/>
+      <c r="BY100" s="30"/>
+      <c r="BZ100" s="30">
         <v>2019</v>
       </c>
-      <c r="CA100" s="22"/>
-      <c r="CB100" s="22"/>
-      <c r="CC100" s="22"/>
-      <c r="CD100" s="22">
+      <c r="CA100" s="30"/>
+      <c r="CB100" s="30"/>
+      <c r="CC100" s="30"/>
+      <c r="CD100" s="30">
         <v>2020</v>
       </c>
-      <c r="CE100" s="22"/>
-      <c r="CF100" s="22"/>
-      <c r="CG100" s="22"/>
-      <c r="CH100" s="23">
+      <c r="CE100" s="30"/>
+      <c r="CF100" s="30"/>
+      <c r="CG100" s="30"/>
+      <c r="CH100" s="22">
         <v>2021</v>
       </c>
-      <c r="CI100" s="23"/>
-      <c r="CJ100" s="23"/>
-      <c r="CK100" s="23"/>
-      <c r="CL100" s="24">
+      <c r="CI100" s="22"/>
+      <c r="CJ100" s="22"/>
+      <c r="CK100" s="22"/>
+      <c r="CL100" s="23">
         <v>2022</v>
       </c>
-      <c r="CM100" s="24"/>
-      <c r="CN100" s="24"/>
-      <c r="CO100" s="24"/>
-      <c r="CP100" s="28">
+      <c r="CM100" s="23"/>
+      <c r="CN100" s="23"/>
+      <c r="CO100" s="23"/>
+      <c r="CP100" s="26">
         <v>2023</v>
       </c>
-      <c r="CQ100" s="28"/>
-      <c r="CR100" s="28"/>
-      <c r="CS100" s="28"/>
-      <c r="CT100" s="28">
+      <c r="CQ100" s="26"/>
+      <c r="CR100" s="26"/>
+      <c r="CS100" s="26"/>
+      <c r="CT100" s="26">
         <v>2024</v>
       </c>
-      <c r="CU100" s="28"/>
-      <c r="CV100" s="28"/>
-      <c r="CW100" s="28"/>
-      <c r="CX100" s="28">
+      <c r="CU100" s="26"/>
+      <c r="CV100" s="26"/>
+      <c r="CW100" s="26"/>
+      <c r="CX100" s="26">
         <v>2025</v>
       </c>
-      <c r="CY100" s="28"/>
-      <c r="CZ100" s="28"/>
-      <c r="DA100" s="28"/>
+      <c r="CY100" s="26"/>
+      <c r="CZ100" s="26"/>
+      <c r="DA100" s="26"/>
     </row>
     <row r="101" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
@@ -17498,10 +17479,10 @@
         <v>90.429441926744147</v>
       </c>
       <c r="CZ103" s="17">
-        <v>244.75710395560094</v>
+        <v>244.75710395560091</v>
       </c>
       <c r="DA103" s="17">
-        <v>89.62895497956886</v>
+        <v>89.628954979568903</v>
       </c>
       <c r="DB103" s="14"/>
       <c r="DC103" s="14"/>
@@ -17880,19 +17861,19 @@
         <v>163.31007477037613</v>
       </c>
       <c r="CW104" s="17">
-        <v>185.66089931724224</v>
+        <v>185.66089931724227</v>
       </c>
       <c r="CX104" s="17">
         <v>237.26605604252975</v>
       </c>
       <c r="CY104" s="17">
-        <v>67.010027261027687</v>
+        <v>67.010027261027702</v>
       </c>
       <c r="CZ104" s="17">
         <v>162.85978119669616</v>
       </c>
       <c r="DA104" s="17">
-        <v>174.51213892369935</v>
+        <v>174.51213892369941</v>
       </c>
       <c r="DB104" s="14"/>
       <c r="DC104" s="14"/>
@@ -18271,19 +18252,19 @@
         <v>250.87330937462249</v>
       </c>
       <c r="CW105" s="17">
-        <v>230.36970765684251</v>
+        <v>230.36970765684254</v>
       </c>
       <c r="CX105" s="17">
-        <v>286.83439246236696</v>
+        <v>286.83322211155149</v>
       </c>
       <c r="CY105" s="17">
-        <v>305.23457261606916</v>
+        <v>305.23457261606922</v>
       </c>
       <c r="CZ105" s="17">
         <v>348.59309591868583</v>
       </c>
       <c r="DA105" s="17">
-        <v>359.13357204321051</v>
+        <v>359.13357204321062</v>
       </c>
       <c r="DB105" s="14"/>
       <c r="DC105" s="14"/>
@@ -18656,22 +18637,22 @@
         <v>207.98423288635681</v>
       </c>
       <c r="CU106" s="17">
-        <v>146.85887079679839</v>
+        <v>146.85887079679836</v>
       </c>
       <c r="CV106" s="17">
-        <v>134.71759228386139</v>
+        <v>134.71759228386142</v>
       </c>
       <c r="CW106" s="17">
-        <v>186.42391805632516</v>
+        <v>186.42391805632514</v>
       </c>
       <c r="CX106" s="17">
-        <v>201.98445023462401</v>
+        <v>201.98445023462406</v>
       </c>
       <c r="CY106" s="17">
         <v>145.8487863757515</v>
       </c>
       <c r="CZ106" s="17">
-        <v>133.90600468881746</v>
+        <v>133.90600468881752</v>
       </c>
       <c r="DA106" s="17">
         <v>189.33651532972314</v>
@@ -19053,10 +19034,10 @@
         <v>237.10824960224457</v>
       </c>
       <c r="CW107" s="17">
-        <v>392.26894734547631</v>
+        <v>392.26894734547625</v>
       </c>
       <c r="CX107" s="17">
-        <v>59.812708381323034</v>
+        <v>59.812708381323041</v>
       </c>
       <c r="CY107" s="17">
         <v>299.7109169621134</v>
@@ -19065,7 +19046,7 @@
         <v>252.12753112064655</v>
       </c>
       <c r="DA107" s="17">
-        <v>442.85155259510105</v>
+        <v>442.85155259510088</v>
       </c>
       <c r="DB107" s="14"/>
       <c r="DC107" s="14"/>
@@ -19435,28 +19416,28 @@
         <v>92.353568620753364</v>
       </c>
       <c r="CT108" s="17">
-        <v>122.88974387348492</v>
+        <v>122.88974387348499</v>
       </c>
       <c r="CU108" s="17">
-        <v>125.29932760064848</v>
+        <v>125.29932760064852</v>
       </c>
       <c r="CV108" s="17">
-        <v>149.44388490174362</v>
+        <v>149.4438849017435</v>
       </c>
       <c r="CW108" s="17">
-        <v>92.029521011557705</v>
+        <v>92.029521011557719</v>
       </c>
       <c r="CX108" s="17">
-        <v>123.07030476662841</v>
+        <v>123.07030476662852</v>
       </c>
       <c r="CY108" s="17">
-        <v>126.11875562533699</v>
+        <v>126.11875562533696</v>
       </c>
       <c r="CZ108" s="17">
-        <v>151.11965609574102</v>
+        <v>151.11965609574091</v>
       </c>
       <c r="DA108" s="17">
-        <v>92.6457972986572</v>
+        <v>92.645797298657158</v>
       </c>
       <c r="DB108" s="14"/>
       <c r="DC108" s="14"/>
@@ -20006,28 +19987,28 @@
         <v>134.79017317114946</v>
       </c>
       <c r="CT110" s="17">
-        <v>134.70265521947721</v>
+        <v>134.7858279491594</v>
       </c>
       <c r="CU110" s="17">
-        <v>136.09011253257398</v>
+        <v>136.1058944255291</v>
       </c>
       <c r="CV110" s="17">
-        <v>191.00107940307896</v>
+        <v>190.81068258794323</v>
       </c>
       <c r="CW110" s="17">
-        <v>145.09306938515095</v>
+        <v>145.08368663565813</v>
       </c>
       <c r="CX110" s="17">
-        <v>153.1329580387121</v>
+        <v>153.18987293850779</v>
       </c>
       <c r="CY110" s="17">
-        <v>148.11957491664205</v>
+        <v>148.09068223731848</v>
       </c>
       <c r="CZ110" s="17">
-        <v>206.61181691408447</v>
+        <v>206.54255010158386</v>
       </c>
       <c r="DA110" s="17">
-        <v>160.45727576035341</v>
+        <v>160.37144749371657</v>
       </c>
       <c r="DB110" s="14"/>
       <c r="DC110" s="14"/>
@@ -20228,7 +20209,7 @@
     </row>
     <row r="117" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="118" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -20239,7 +20220,7 @@
     </row>
     <row r="120" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -20250,162 +20231,162 @@
     <row r="122" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="123" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="11"/>
-      <c r="B123" s="22">
+      <c r="B123" s="30">
         <v>2000</v>
       </c>
-      <c r="C123" s="22"/>
-      <c r="D123" s="22"/>
-      <c r="E123" s="22"/>
-      <c r="F123" s="22">
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30">
         <v>2001</v>
       </c>
-      <c r="G123" s="22"/>
-      <c r="H123" s="22"/>
-      <c r="I123" s="22"/>
-      <c r="J123" s="22">
+      <c r="G123" s="30"/>
+      <c r="H123" s="30"/>
+      <c r="I123" s="30"/>
+      <c r="J123" s="30">
         <v>2002</v>
       </c>
-      <c r="K123" s="22"/>
-      <c r="L123" s="22"/>
-      <c r="M123" s="22"/>
-      <c r="N123" s="22">
+      <c r="K123" s="30"/>
+      <c r="L123" s="30"/>
+      <c r="M123" s="30"/>
+      <c r="N123" s="30">
         <v>2003</v>
       </c>
-      <c r="O123" s="22"/>
-      <c r="P123" s="22"/>
-      <c r="Q123" s="22"/>
-      <c r="R123" s="22">
+      <c r="O123" s="30"/>
+      <c r="P123" s="30"/>
+      <c r="Q123" s="30"/>
+      <c r="R123" s="30">
         <v>2004</v>
       </c>
-      <c r="S123" s="22"/>
-      <c r="T123" s="22"/>
-      <c r="U123" s="22"/>
-      <c r="V123" s="22">
+      <c r="S123" s="30"/>
+      <c r="T123" s="30"/>
+      <c r="U123" s="30"/>
+      <c r="V123" s="30">
         <v>2005</v>
       </c>
-      <c r="W123" s="22"/>
-      <c r="X123" s="22"/>
-      <c r="Y123" s="22"/>
-      <c r="Z123" s="22">
+      <c r="W123" s="30"/>
+      <c r="X123" s="30"/>
+      <c r="Y123" s="30"/>
+      <c r="Z123" s="30">
         <v>2006</v>
       </c>
-      <c r="AA123" s="22"/>
-      <c r="AB123" s="22"/>
-      <c r="AC123" s="22"/>
-      <c r="AD123" s="22">
+      <c r="AA123" s="30"/>
+      <c r="AB123" s="30"/>
+      <c r="AC123" s="30"/>
+      <c r="AD123" s="30">
         <v>2007</v>
       </c>
-      <c r="AE123" s="22"/>
-      <c r="AF123" s="22"/>
-      <c r="AG123" s="22"/>
-      <c r="AH123" s="22">
+      <c r="AE123" s="30"/>
+      <c r="AF123" s="30"/>
+      <c r="AG123" s="30"/>
+      <c r="AH123" s="30">
         <v>2008</v>
       </c>
-      <c r="AI123" s="22"/>
-      <c r="AJ123" s="22"/>
-      <c r="AK123" s="22"/>
-      <c r="AL123" s="22">
+      <c r="AI123" s="30"/>
+      <c r="AJ123" s="30"/>
+      <c r="AK123" s="30"/>
+      <c r="AL123" s="30">
         <v>2009</v>
       </c>
-      <c r="AM123" s="22"/>
-      <c r="AN123" s="22"/>
-      <c r="AO123" s="22"/>
-      <c r="AP123" s="22">
+      <c r="AM123" s="30"/>
+      <c r="AN123" s="30"/>
+      <c r="AO123" s="30"/>
+      <c r="AP123" s="30">
         <v>2010</v>
       </c>
-      <c r="AQ123" s="22"/>
-      <c r="AR123" s="22"/>
-      <c r="AS123" s="22"/>
-      <c r="AT123" s="22">
+      <c r="AQ123" s="30"/>
+      <c r="AR123" s="30"/>
+      <c r="AS123" s="30"/>
+      <c r="AT123" s="30">
         <v>2011</v>
       </c>
-      <c r="AU123" s="22"/>
-      <c r="AV123" s="22"/>
-      <c r="AW123" s="22"/>
-      <c r="AX123" s="22">
+      <c r="AU123" s="30"/>
+      <c r="AV123" s="30"/>
+      <c r="AW123" s="30"/>
+      <c r="AX123" s="30">
         <v>2012</v>
       </c>
-      <c r="AY123" s="22"/>
-      <c r="AZ123" s="22"/>
-      <c r="BA123" s="22"/>
-      <c r="BB123" s="22">
+      <c r="AY123" s="30"/>
+      <c r="AZ123" s="30"/>
+      <c r="BA123" s="30"/>
+      <c r="BB123" s="30">
         <v>2013</v>
       </c>
-      <c r="BC123" s="22"/>
-      <c r="BD123" s="22"/>
-      <c r="BE123" s="22"/>
-      <c r="BF123" s="22">
+      <c r="BC123" s="30"/>
+      <c r="BD123" s="30"/>
+      <c r="BE123" s="30"/>
+      <c r="BF123" s="30">
         <v>2014</v>
       </c>
-      <c r="BG123" s="22"/>
-      <c r="BH123" s="22"/>
-      <c r="BI123" s="22"/>
-      <c r="BJ123" s="22">
+      <c r="BG123" s="30"/>
+      <c r="BH123" s="30"/>
+      <c r="BI123" s="30"/>
+      <c r="BJ123" s="30">
         <v>2015</v>
       </c>
-      <c r="BK123" s="22"/>
-      <c r="BL123" s="22"/>
-      <c r="BM123" s="22"/>
-      <c r="BN123" s="22">
+      <c r="BK123" s="30"/>
+      <c r="BL123" s="30"/>
+      <c r="BM123" s="30"/>
+      <c r="BN123" s="30">
         <v>2016</v>
       </c>
-      <c r="BO123" s="22"/>
-      <c r="BP123" s="22"/>
-      <c r="BQ123" s="22"/>
-      <c r="BR123" s="22">
+      <c r="BO123" s="30"/>
+      <c r="BP123" s="30"/>
+      <c r="BQ123" s="30"/>
+      <c r="BR123" s="30">
         <v>2017</v>
       </c>
-      <c r="BS123" s="22"/>
-      <c r="BT123" s="22"/>
-      <c r="BU123" s="22"/>
-      <c r="BV123" s="22">
+      <c r="BS123" s="30"/>
+      <c r="BT123" s="30"/>
+      <c r="BU123" s="30"/>
+      <c r="BV123" s="30">
         <v>2018</v>
       </c>
-      <c r="BW123" s="22"/>
-      <c r="BX123" s="22"/>
-      <c r="BY123" s="22"/>
-      <c r="BZ123" s="22">
+      <c r="BW123" s="30"/>
+      <c r="BX123" s="30"/>
+      <c r="BY123" s="30"/>
+      <c r="BZ123" s="30">
         <v>2019</v>
       </c>
-      <c r="CA123" s="22"/>
-      <c r="CB123" s="22"/>
-      <c r="CC123" s="22"/>
-      <c r="CD123" s="22">
+      <c r="CA123" s="30"/>
+      <c r="CB123" s="30"/>
+      <c r="CC123" s="30"/>
+      <c r="CD123" s="30">
         <v>2020</v>
       </c>
-      <c r="CE123" s="22"/>
-      <c r="CF123" s="22"/>
-      <c r="CG123" s="22"/>
-      <c r="CH123" s="23">
+      <c r="CE123" s="30"/>
+      <c r="CF123" s="30"/>
+      <c r="CG123" s="30"/>
+      <c r="CH123" s="22">
         <v>2021</v>
       </c>
-      <c r="CI123" s="23"/>
-      <c r="CJ123" s="23"/>
-      <c r="CK123" s="23"/>
-      <c r="CL123" s="24">
+      <c r="CI123" s="22"/>
+      <c r="CJ123" s="22"/>
+      <c r="CK123" s="22"/>
+      <c r="CL123" s="23">
         <v>2022</v>
       </c>
-      <c r="CM123" s="24"/>
-      <c r="CN123" s="24"/>
-      <c r="CO123" s="24"/>
-      <c r="CP123" s="28">
+      <c r="CM123" s="23"/>
+      <c r="CN123" s="23"/>
+      <c r="CO123" s="23"/>
+      <c r="CP123" s="26">
         <v>2023</v>
       </c>
-      <c r="CQ123" s="28"/>
-      <c r="CR123" s="28"/>
-      <c r="CS123" s="28"/>
-      <c r="CT123" s="28">
+      <c r="CQ123" s="26"/>
+      <c r="CR123" s="26"/>
+      <c r="CS123" s="26"/>
+      <c r="CT123" s="26">
         <v>2024</v>
       </c>
-      <c r="CU123" s="28"/>
-      <c r="CV123" s="28"/>
-      <c r="CW123" s="28"/>
-      <c r="CX123" s="28">
+      <c r="CU123" s="26"/>
+      <c r="CV123" s="26"/>
+      <c r="CW123" s="26"/>
+      <c r="CX123" s="26">
         <v>2025</v>
       </c>
-      <c r="CY123" s="28"/>
-      <c r="CZ123" s="28"/>
-      <c r="DA123" s="28"/>
+      <c r="CY123" s="26"/>
+      <c r="CZ123" s="26"/>
+      <c r="DA123" s="26"/>
     </row>
     <row r="124" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
@@ -21020,28 +21001,28 @@
         <v>12.0208609001163</v>
       </c>
       <c r="CT126" s="20">
-        <v>14.363343780639127</v>
+        <v>14.352610614856506</v>
       </c>
       <c r="CU126" s="20">
-        <v>18.628638671944518</v>
+        <v>18.646781921675721</v>
       </c>
       <c r="CV126" s="20">
-        <v>16.794576365336191</v>
+        <v>16.744180778790415</v>
       </c>
       <c r="CW126" s="20">
-        <v>8.2835773642454225</v>
+        <v>8.2721765177323263</v>
       </c>
       <c r="CX126" s="20">
-        <v>12.954076364700711</v>
+        <v>12.930511848429655</v>
       </c>
       <c r="CY126" s="20">
-        <v>15.019961258773471</v>
+        <v>15.10838354668328</v>
       </c>
       <c r="CZ126" s="20">
-        <v>15.613898319377562</v>
+        <v>15.671570350499575</v>
       </c>
       <c r="DA126" s="20">
-        <v>9.2678378670804662</v>
+        <v>9.5163329486841111</v>
       </c>
       <c r="DB126" s="14"/>
       <c r="DC126" s="14"/>
@@ -21411,28 +21392,28 @@
         <v>13.939509495201644</v>
       </c>
       <c r="CT127" s="20">
-        <v>10.043985963916009</v>
+        <v>10.036480485517982</v>
       </c>
       <c r="CU127" s="20">
-        <v>8.2290314054229281</v>
+        <v>8.2283790384250288</v>
       </c>
       <c r="CV127" s="20">
-        <v>6.6449266495977728</v>
+        <v>6.6261549054016475</v>
       </c>
       <c r="CW127" s="20">
-        <v>10.234073996442241</v>
+        <v>10.219988643978374</v>
       </c>
       <c r="CX127" s="20">
-        <v>11.993972091616142</v>
+        <v>11.972154082940687</v>
       </c>
       <c r="CY127" s="20">
-        <v>6.9904235106137884</v>
+        <v>6.9927882667961709</v>
       </c>
       <c r="CZ127" s="20">
-        <v>5.6563313934087809</v>
+        <v>5.6422457044129484</v>
       </c>
       <c r="DA127" s="20">
-        <v>7.4303835337237594</v>
+        <v>7.5757304689392972</v>
       </c>
       <c r="DB127" s="14"/>
       <c r="DC127" s="14"/>
@@ -21802,28 +21783,28 @@
         <v>25.222957767308539</v>
       </c>
       <c r="CT128" s="20">
-        <v>21.567162917969039</v>
+        <v>21.551046619522477</v>
       </c>
       <c r="CU128" s="20">
-        <v>28.339756995531403</v>
+        <v>28.337510325020439</v>
       </c>
       <c r="CV128" s="20">
-        <v>30.566395226243781</v>
+        <v>30.480045958232004</v>
       </c>
       <c r="CW128" s="20">
-        <v>30.896157927179509</v>
+        <v>30.874835162222585</v>
       </c>
       <c r="CX128" s="20">
-        <v>28.607141903353639</v>
+        <v>28.636840967148991</v>
       </c>
       <c r="CY128" s="20">
-        <v>36.344545936721417</v>
+        <v>36.374240017973015</v>
       </c>
       <c r="CZ128" s="20">
-        <v>35.169842845575175</v>
+        <v>35.126800658680537</v>
       </c>
       <c r="DA128" s="20">
-        <v>38.284882430184616</v>
+        <v>38.32857262911125</v>
       </c>
       <c r="DB128" s="14"/>
       <c r="DC128" s="14"/>
@@ -22193,28 +22174,28 @@
         <v>6.3505797045155994</v>
       </c>
       <c r="CT129" s="20">
-        <v>19.250321002402671</v>
+        <v>19.38954882390788</v>
       </c>
       <c r="CU129" s="20">
-        <v>19.52656281525147</v>
+        <v>19.619925994237423</v>
       </c>
       <c r="CV129" s="20">
-        <v>13.812599928226534</v>
+        <v>13.912113427863988</v>
       </c>
       <c r="CW129" s="20">
-        <v>5.9448072634683502</v>
+        <v>6.0027897171378015</v>
       </c>
       <c r="CX129" s="20">
-        <v>14.937630539421178</v>
+        <v>14.95897186352656</v>
       </c>
       <c r="CY129" s="20">
-        <v>18.845421882424958</v>
+        <v>18.859164053084587</v>
       </c>
       <c r="CZ129" s="20">
-        <v>13.199276623546078</v>
+        <v>13.320554847933225</v>
       </c>
       <c r="DA129" s="20">
-        <v>5.7119753294017643</v>
+        <v>5.9154975384324588</v>
       </c>
       <c r="DB129" s="14"/>
       <c r="DC129" s="14"/>
@@ -22584,28 +22565,28 @@
         <v>9.9338828839635376</v>
       </c>
       <c r="CT130" s="20">
-        <v>3.8753737068938072</v>
+        <v>3.8724777914927047</v>
       </c>
       <c r="CU130" s="20">
-        <v>7.0341895514194617</v>
+        <v>7.0336319070389495</v>
       </c>
       <c r="CV130" s="20">
-        <v>5.4370405574804952</v>
+        <v>5.4216810599403438</v>
       </c>
       <c r="CW130" s="20">
-        <v>11.108476796041687</v>
+        <v>11.093187986222318</v>
       </c>
       <c r="CX130" s="20">
-        <v>3.6035572788746641</v>
+        <v>3.5970021157166689</v>
       </c>
       <c r="CY130" s="20">
-        <v>5.3014635676369393</v>
+        <v>5.3033402660144144</v>
       </c>
       <c r="CZ130" s="20">
-        <v>5.6174681949745615</v>
+        <v>5.6034792851255757</v>
       </c>
       <c r="DA130" s="20">
-        <v>9.8155523981667674</v>
+        <v>9.5284046222723422</v>
       </c>
       <c r="DB130" s="14"/>
       <c r="DC130" s="14"/>
@@ -22975,28 +22956,28 @@
         <v>32.532209248894375</v>
       </c>
       <c r="CT131" s="20">
-        <v>30.899812628179351</v>
+        <v>30.797835664702443</v>
       </c>
       <c r="CU131" s="20">
-        <v>18.241820560430231</v>
+        <v>18.133770813602432</v>
       </c>
       <c r="CV131" s="20">
-        <v>26.744461273115217</v>
+        <v>26.815823869771609</v>
       </c>
       <c r="CW131" s="20">
-        <v>33.532906652622792</v>
+        <v>33.53702197270659</v>
       </c>
       <c r="CX131" s="20">
-        <v>27.90362182203366</v>
+        <v>27.904519122237431</v>
       </c>
       <c r="CY131" s="20">
-        <v>17.49818384382943</v>
+        <v>17.362083849448538</v>
       </c>
       <c r="CZ131" s="20">
-        <v>24.743182623117846</v>
+        <v>24.635349153348152</v>
       </c>
       <c r="DA131" s="20">
-        <v>29.489368441442625</v>
+        <v>29.135461792560541</v>
       </c>
       <c r="DB131" s="14"/>
       <c r="DC131" s="14"/>
@@ -24128,7 +24109,7 @@
     </row>
     <row r="140" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="141" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -24139,7 +24120,7 @@
     </row>
     <row r="143" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="144" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -24150,162 +24131,162 @@
     <row r="145" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="146" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="11"/>
-      <c r="B146" s="22">
+      <c r="B146" s="30">
         <v>2000</v>
       </c>
-      <c r="C146" s="22"/>
-      <c r="D146" s="22"/>
-      <c r="E146" s="22"/>
-      <c r="F146" s="22">
+      <c r="C146" s="30"/>
+      <c r="D146" s="30"/>
+      <c r="E146" s="30"/>
+      <c r="F146" s="30">
         <v>2001</v>
       </c>
-      <c r="G146" s="22"/>
-      <c r="H146" s="22"/>
-      <c r="I146" s="22"/>
-      <c r="J146" s="22">
+      <c r="G146" s="30"/>
+      <c r="H146" s="30"/>
+      <c r="I146" s="30"/>
+      <c r="J146" s="30">
         <v>2002</v>
       </c>
-      <c r="K146" s="22"/>
-      <c r="L146" s="22"/>
-      <c r="M146" s="22"/>
-      <c r="N146" s="22">
+      <c r="K146" s="30"/>
+      <c r="L146" s="30"/>
+      <c r="M146" s="30"/>
+      <c r="N146" s="30">
         <v>2003</v>
       </c>
-      <c r="O146" s="22"/>
-      <c r="P146" s="22"/>
-      <c r="Q146" s="22"/>
-      <c r="R146" s="22">
+      <c r="O146" s="30"/>
+      <c r="P146" s="30"/>
+      <c r="Q146" s="30"/>
+      <c r="R146" s="30">
         <v>2004</v>
       </c>
-      <c r="S146" s="22"/>
-      <c r="T146" s="22"/>
-      <c r="U146" s="22"/>
-      <c r="V146" s="22">
+      <c r="S146" s="30"/>
+      <c r="T146" s="30"/>
+      <c r="U146" s="30"/>
+      <c r="V146" s="30">
         <v>2005</v>
       </c>
-      <c r="W146" s="22"/>
-      <c r="X146" s="22"/>
-      <c r="Y146" s="22"/>
-      <c r="Z146" s="22">
+      <c r="W146" s="30"/>
+      <c r="X146" s="30"/>
+      <c r="Y146" s="30"/>
+      <c r="Z146" s="30">
         <v>2006</v>
       </c>
-      <c r="AA146" s="22"/>
-      <c r="AB146" s="22"/>
-      <c r="AC146" s="22"/>
-      <c r="AD146" s="22">
+      <c r="AA146" s="30"/>
+      <c r="AB146" s="30"/>
+      <c r="AC146" s="30"/>
+      <c r="AD146" s="30">
         <v>2007</v>
       </c>
-      <c r="AE146" s="22"/>
-      <c r="AF146" s="22"/>
-      <c r="AG146" s="22"/>
-      <c r="AH146" s="22">
+      <c r="AE146" s="30"/>
+      <c r="AF146" s="30"/>
+      <c r="AG146" s="30"/>
+      <c r="AH146" s="30">
         <v>2008</v>
       </c>
-      <c r="AI146" s="22"/>
-      <c r="AJ146" s="22"/>
-      <c r="AK146" s="22"/>
-      <c r="AL146" s="22">
+      <c r="AI146" s="30"/>
+      <c r="AJ146" s="30"/>
+      <c r="AK146" s="30"/>
+      <c r="AL146" s="30">
         <v>2009</v>
       </c>
-      <c r="AM146" s="22"/>
-      <c r="AN146" s="22"/>
-      <c r="AO146" s="22"/>
-      <c r="AP146" s="22">
+      <c r="AM146" s="30"/>
+      <c r="AN146" s="30"/>
+      <c r="AO146" s="30"/>
+      <c r="AP146" s="30">
         <v>2010</v>
       </c>
-      <c r="AQ146" s="22"/>
-      <c r="AR146" s="22"/>
-      <c r="AS146" s="22"/>
-      <c r="AT146" s="22">
+      <c r="AQ146" s="30"/>
+      <c r="AR146" s="30"/>
+      <c r="AS146" s="30"/>
+      <c r="AT146" s="30">
         <v>2011</v>
       </c>
-      <c r="AU146" s="22"/>
-      <c r="AV146" s="22"/>
-      <c r="AW146" s="22"/>
-      <c r="AX146" s="22">
+      <c r="AU146" s="30"/>
+      <c r="AV146" s="30"/>
+      <c r="AW146" s="30"/>
+      <c r="AX146" s="30">
         <v>2012</v>
       </c>
-      <c r="AY146" s="22"/>
-      <c r="AZ146" s="22"/>
-      <c r="BA146" s="22"/>
-      <c r="BB146" s="22">
+      <c r="AY146" s="30"/>
+      <c r="AZ146" s="30"/>
+      <c r="BA146" s="30"/>
+      <c r="BB146" s="30">
         <v>2013</v>
       </c>
-      <c r="BC146" s="22"/>
-      <c r="BD146" s="22"/>
-      <c r="BE146" s="22"/>
-      <c r="BF146" s="22">
+      <c r="BC146" s="30"/>
+      <c r="BD146" s="30"/>
+      <c r="BE146" s="30"/>
+      <c r="BF146" s="30">
         <v>2014</v>
       </c>
-      <c r="BG146" s="22"/>
-      <c r="BH146" s="22"/>
-      <c r="BI146" s="22"/>
-      <c r="BJ146" s="22">
+      <c r="BG146" s="30"/>
+      <c r="BH146" s="30"/>
+      <c r="BI146" s="30"/>
+      <c r="BJ146" s="30">
         <v>2015</v>
       </c>
-      <c r="BK146" s="22"/>
-      <c r="BL146" s="22"/>
-      <c r="BM146" s="22"/>
-      <c r="BN146" s="22">
+      <c r="BK146" s="30"/>
+      <c r="BL146" s="30"/>
+      <c r="BM146" s="30"/>
+      <c r="BN146" s="30">
         <v>2016</v>
       </c>
-      <c r="BO146" s="22"/>
-      <c r="BP146" s="22"/>
-      <c r="BQ146" s="22"/>
-      <c r="BR146" s="22">
+      <c r="BO146" s="30"/>
+      <c r="BP146" s="30"/>
+      <c r="BQ146" s="30"/>
+      <c r="BR146" s="30">
         <v>2017</v>
       </c>
-      <c r="BS146" s="22"/>
-      <c r="BT146" s="22"/>
-      <c r="BU146" s="22"/>
-      <c r="BV146" s="22">
+      <c r="BS146" s="30"/>
+      <c r="BT146" s="30"/>
+      <c r="BU146" s="30"/>
+      <c r="BV146" s="30">
         <v>2018</v>
       </c>
-      <c r="BW146" s="22"/>
-      <c r="BX146" s="22"/>
-      <c r="BY146" s="22"/>
-      <c r="BZ146" s="22">
+      <c r="BW146" s="30"/>
+      <c r="BX146" s="30"/>
+      <c r="BY146" s="30"/>
+      <c r="BZ146" s="30">
         <v>2019</v>
       </c>
-      <c r="CA146" s="22"/>
-      <c r="CB146" s="22"/>
-      <c r="CC146" s="22"/>
-      <c r="CD146" s="22">
+      <c r="CA146" s="30"/>
+      <c r="CB146" s="30"/>
+      <c r="CC146" s="30"/>
+      <c r="CD146" s="30">
         <v>2020</v>
       </c>
-      <c r="CE146" s="22"/>
-      <c r="CF146" s="22"/>
-      <c r="CG146" s="22"/>
-      <c r="CH146" s="23">
+      <c r="CE146" s="30"/>
+      <c r="CF146" s="30"/>
+      <c r="CG146" s="30"/>
+      <c r="CH146" s="22">
         <v>2021</v>
       </c>
-      <c r="CI146" s="23"/>
-      <c r="CJ146" s="23"/>
-      <c r="CK146" s="23"/>
-      <c r="CL146" s="24">
+      <c r="CI146" s="22"/>
+      <c r="CJ146" s="22"/>
+      <c r="CK146" s="22"/>
+      <c r="CL146" s="23">
         <v>2022</v>
       </c>
-      <c r="CM146" s="24"/>
-      <c r="CN146" s="24"/>
-      <c r="CO146" s="24"/>
-      <c r="CP146" s="28">
+      <c r="CM146" s="23"/>
+      <c r="CN146" s="23"/>
+      <c r="CO146" s="23"/>
+      <c r="CP146" s="26">
         <v>2023</v>
       </c>
-      <c r="CQ146" s="28"/>
-      <c r="CR146" s="28"/>
-      <c r="CS146" s="28"/>
-      <c r="CT146" s="28">
+      <c r="CQ146" s="26"/>
+      <c r="CR146" s="26"/>
+      <c r="CS146" s="26"/>
+      <c r="CT146" s="26">
         <v>2024</v>
       </c>
-      <c r="CU146" s="28"/>
-      <c r="CV146" s="28"/>
-      <c r="CW146" s="28"/>
-      <c r="CX146" s="28">
+      <c r="CU146" s="26"/>
+      <c r="CV146" s="26"/>
+      <c r="CW146" s="26"/>
+      <c r="CX146" s="26">
         <v>2025</v>
       </c>
-      <c r="CY146" s="28"/>
-      <c r="CZ146" s="28"/>
-      <c r="DA146" s="28"/>
+      <c r="CY146" s="26"/>
+      <c r="CZ146" s="26"/>
+      <c r="DA146" s="26"/>
     </row>
     <row r="147" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
@@ -24920,28 +24901,28 @@
         <v>14.946264713860232</v>
       </c>
       <c r="CT149" s="20">
-        <v>19.864355171057881</v>
+        <v>19.861767479853647</v>
       </c>
       <c r="CU149" s="20">
-        <v>22.943956100430583</v>
+        <v>22.96896554892226</v>
       </c>
       <c r="CV149" s="20">
-        <v>10.812134158147893</v>
+        <v>10.76894453525207</v>
       </c>
       <c r="CW149" s="20">
-        <v>10.939507835893963</v>
+        <v>10.923745128584269</v>
       </c>
       <c r="CX149" s="20">
-        <v>21.716048926156031</v>
+        <v>21.684602188613976</v>
       </c>
       <c r="CY149" s="20">
-        <v>24.602056913236321</v>
+        <v>24.742061647841478</v>
       </c>
       <c r="CZ149" s="20">
-        <v>13.180479131112655</v>
+        <v>13.224727911781963</v>
       </c>
       <c r="DA149" s="20">
-        <v>16.591647383140437</v>
+        <v>17.027400243152531</v>
       </c>
       <c r="DB149" s="14"/>
       <c r="DC149" s="14"/>
@@ -25311,28 +25292,28 @@
         <v>9.2922762573567486</v>
       </c>
       <c r="CT150" s="20">
-        <v>9.2813090776984257</v>
+        <v>9.2801000194804608</v>
       </c>
       <c r="CU150" s="20">
-        <v>18.759795606591261</v>
+        <v>18.760483735004037</v>
       </c>
       <c r="CV150" s="20">
-        <v>7.7716464487081707</v>
+        <v>7.7419665762254839</v>
       </c>
       <c r="CW150" s="20">
-        <v>7.9978779264733513</v>
+        <v>7.9863538057592525</v>
       </c>
       <c r="CX150" s="20">
-        <v>7.7409826574337997</v>
+        <v>7.7297730377293243</v>
       </c>
       <c r="CY150" s="20">
-        <v>15.451695831223802</v>
+        <v>15.453907832883914</v>
       </c>
       <c r="CZ150" s="20">
-        <v>7.1758963304076415</v>
+        <v>7.155626806852168</v>
       </c>
       <c r="DA150" s="20">
-        <v>6.8319551122869751</v>
+        <v>6.9618702092537079</v>
       </c>
       <c r="DB150" s="14"/>
       <c r="DC150" s="14"/>
@@ -25702,28 +25683,28 @@
         <v>19.895724233958489</v>
       </c>
       <c r="CT151" s="20">
-        <v>14.498514842552506</v>
+        <v>14.496626149010257</v>
       </c>
       <c r="CU151" s="20">
-        <v>17.271890540455082</v>
+        <v>17.272524090994359</v>
       </c>
       <c r="CV151" s="20">
-        <v>23.271564823803679</v>
+        <v>23.182690853403511</v>
       </c>
       <c r="CW151" s="20">
-        <v>19.459235467453126</v>
+        <v>19.444548309606937</v>
       </c>
       <c r="CX151" s="20">
-        <v>15.272562760299005</v>
+        <v>15.294162917473075</v>
       </c>
       <c r="CY151" s="20">
-        <v>17.636726562612647</v>
+        <v>17.647692965963881</v>
       </c>
       <c r="CZ151" s="20">
-        <v>20.845235364621551</v>
+        <v>20.812744342608106</v>
       </c>
       <c r="DA151" s="20">
-        <v>17.105301246561581</v>
+        <v>17.115661557140747</v>
       </c>
       <c r="DB151" s="14"/>
       <c r="DC151" s="14"/>
@@ -26093,28 +26074,28 @@
         <v>4.4106291196332981</v>
       </c>
       <c r="CT152" s="20">
-        <v>12.467624669740077</v>
+        <v>12.565550549300832</v>
       </c>
       <c r="CU152" s="20">
-        <v>18.094733511731995</v>
+        <v>18.183359040689218</v>
       </c>
       <c r="CV152" s="20">
-        <v>19.583348031452367</v>
+        <v>19.704775110723418</v>
       </c>
       <c r="CW152" s="20">
-        <v>4.6268222541013007</v>
+        <v>4.6716476691464059</v>
       </c>
       <c r="CX152" s="20">
-        <v>11.324849749244985</v>
+        <v>11.345244628497291</v>
       </c>
       <c r="CY152" s="20">
-        <v>19.138835143668061</v>
+        <v>19.149055267772489</v>
       </c>
       <c r="CZ152" s="20">
-        <v>20.365976353935682</v>
+        <v>20.546213543251966</v>
       </c>
       <c r="DA152" s="20">
-        <v>4.840735549453056</v>
+        <v>5.0105332361897652</v>
       </c>
       <c r="DB152" s="14"/>
       <c r="DC152" s="14"/>
@@ -26484,28 +26465,28 @@
         <v>3.9742970417373216</v>
       </c>
       <c r="CT153" s="20">
-        <v>10.01810524840297</v>
+        <v>10.016800209170077</v>
       </c>
       <c r="CU153" s="20">
-        <v>3.116817098040499</v>
+        <v>3.1169314260666448</v>
       </c>
       <c r="CV153" s="20">
-        <v>4.3797742886600179</v>
+        <v>4.3630479561835855</v>
       </c>
       <c r="CW153" s="20">
-        <v>4.1088212703003366</v>
+        <v>4.1029008808236647</v>
       </c>
       <c r="CX153" s="20">
-        <v>9.2258551821124435</v>
+        <v>9.2124953371655298</v>
       </c>
       <c r="CY153" s="20">
-        <v>2.6200264509340907</v>
+        <v>2.620442678869773</v>
       </c>
       <c r="CZ153" s="20">
-        <v>4.6033660229885669</v>
+        <v>4.5903630430483409</v>
       </c>
       <c r="DA153" s="20">
-        <v>3.5564441146553762</v>
+        <v>3.4505559089159656</v>
       </c>
       <c r="DB153" s="14"/>
       <c r="DC153" s="14"/>
@@ -26875,28 +26856,28 @@
         <v>47.480808633453897</v>
       </c>
       <c r="CT154" s="20">
-        <v>33.87009099054815</v>
+        <v>33.779155593184718</v>
       </c>
       <c r="CU154" s="20">
-        <v>19.812807142750568</v>
+        <v>19.69773615832348</v>
       </c>
       <c r="CV154" s="20">
-        <v>34.181532249227878</v>
+        <v>34.238574968211942</v>
       </c>
       <c r="CW154" s="20">
-        <v>52.867735245777915</v>
+        <v>52.87080420607947</v>
       </c>
       <c r="CX154" s="20">
-        <v>34.719700724753736</v>
+        <v>34.733721890520805</v>
       </c>
       <c r="CY154" s="20">
-        <v>20.550659098325077</v>
+        <v>20.386839606668481</v>
       </c>
       <c r="CZ154" s="20">
-        <v>33.829046796933895</v>
+        <v>33.670324352457463</v>
       </c>
       <c r="DA154" s="20">
-        <v>51.073916593902567</v>
+        <v>50.433978845347283</v>
       </c>
       <c r="DB154" s="14"/>
       <c r="DC154" s="14"/>
@@ -27945,41 +27926,94 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="CD146:CG146"/>
-    <mergeCell ref="BF146:BI146"/>
-    <mergeCell ref="BJ146:BM146"/>
-    <mergeCell ref="BN146:BQ146"/>
-    <mergeCell ref="BR146:BU146"/>
-    <mergeCell ref="BV146:BY146"/>
-    <mergeCell ref="BZ146:CC146"/>
-    <mergeCell ref="AH146:AK146"/>
-    <mergeCell ref="AL146:AO146"/>
-    <mergeCell ref="AP146:AS146"/>
-    <mergeCell ref="AT146:AW146"/>
-    <mergeCell ref="AX146:BA146"/>
-    <mergeCell ref="BB146:BE146"/>
-    <mergeCell ref="BZ123:CC123"/>
-    <mergeCell ref="CD123:CG123"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="F146:I146"/>
-    <mergeCell ref="J146:M146"/>
-    <mergeCell ref="N146:Q146"/>
-    <mergeCell ref="R146:U146"/>
-    <mergeCell ref="V146:Y146"/>
-    <mergeCell ref="Z146:AC146"/>
-    <mergeCell ref="AD146:AG146"/>
-    <mergeCell ref="BB123:BE123"/>
-    <mergeCell ref="BF123:BI123"/>
-    <mergeCell ref="BJ123:BM123"/>
-    <mergeCell ref="BN123:BQ123"/>
-    <mergeCell ref="BR123:BU123"/>
-    <mergeCell ref="BV123:BY123"/>
-    <mergeCell ref="AD123:AG123"/>
-    <mergeCell ref="AH123:AK123"/>
-    <mergeCell ref="AL123:AO123"/>
-    <mergeCell ref="AP123:AS123"/>
-    <mergeCell ref="AT123:AW123"/>
-    <mergeCell ref="AX123:BA123"/>
+    <mergeCell ref="AT9:AW9"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="AP32:AS32"/>
+    <mergeCell ref="AT32:AW32"/>
+    <mergeCell ref="AX32:BA32"/>
+    <mergeCell ref="BV9:BY9"/>
+    <mergeCell ref="BZ9:CC9"/>
+    <mergeCell ref="CD9:CG9"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="R32:U32"/>
+    <mergeCell ref="V32:Y32"/>
+    <mergeCell ref="Z32:AC32"/>
+    <mergeCell ref="AX9:BA9"/>
+    <mergeCell ref="BB9:BE9"/>
+    <mergeCell ref="BF9:BI9"/>
+    <mergeCell ref="BJ9:BM9"/>
+    <mergeCell ref="BN9:BQ9"/>
+    <mergeCell ref="BR9:BU9"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AH9:AK9"/>
+    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="AP9:AS9"/>
+    <mergeCell ref="AL55:AO55"/>
+    <mergeCell ref="AP55:AS55"/>
+    <mergeCell ref="AT55:AW55"/>
+    <mergeCell ref="AX55:BA55"/>
+    <mergeCell ref="BB55:BE55"/>
+    <mergeCell ref="BZ32:CC32"/>
+    <mergeCell ref="CD32:CG32"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="N55:Q55"/>
+    <mergeCell ref="R55:U55"/>
+    <mergeCell ref="V55:Y55"/>
+    <mergeCell ref="Z55:AC55"/>
+    <mergeCell ref="AD55:AG55"/>
+    <mergeCell ref="BB32:BE32"/>
+    <mergeCell ref="BF32:BI32"/>
+    <mergeCell ref="BJ32:BM32"/>
+    <mergeCell ref="BN32:BQ32"/>
+    <mergeCell ref="BR32:BU32"/>
+    <mergeCell ref="BV32:BY32"/>
+    <mergeCell ref="AD32:AG32"/>
+    <mergeCell ref="AH32:AK32"/>
+    <mergeCell ref="AL32:AO32"/>
+    <mergeCell ref="CD78:CG78"/>
+    <mergeCell ref="AL78:AO78"/>
+    <mergeCell ref="AP78:AS78"/>
+    <mergeCell ref="AT78:AW78"/>
+    <mergeCell ref="AX78:BA78"/>
+    <mergeCell ref="BB78:BE78"/>
+    <mergeCell ref="BF78:BI78"/>
+    <mergeCell ref="CD55:CG55"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="N78:Q78"/>
+    <mergeCell ref="R78:U78"/>
+    <mergeCell ref="V78:Y78"/>
+    <mergeCell ref="Z78:AC78"/>
+    <mergeCell ref="AD78:AG78"/>
+    <mergeCell ref="AH78:AK78"/>
+    <mergeCell ref="BF55:BI55"/>
+    <mergeCell ref="BJ55:BM55"/>
+    <mergeCell ref="BN55:BQ55"/>
+    <mergeCell ref="BR55:BU55"/>
+    <mergeCell ref="BV55:BY55"/>
+    <mergeCell ref="BZ55:CC55"/>
+    <mergeCell ref="AH55:AK55"/>
+    <mergeCell ref="J100:M100"/>
+    <mergeCell ref="N100:Q100"/>
+    <mergeCell ref="R100:U100"/>
+    <mergeCell ref="V100:Y100"/>
+    <mergeCell ref="BJ78:BM78"/>
+    <mergeCell ref="BN78:BQ78"/>
+    <mergeCell ref="BR78:BU78"/>
+    <mergeCell ref="BV78:BY78"/>
+    <mergeCell ref="BZ78:CC78"/>
     <mergeCell ref="BV100:BY100"/>
     <mergeCell ref="BZ100:CC100"/>
     <mergeCell ref="CD100:CG100"/>
@@ -28004,101 +28038,43 @@
     <mergeCell ref="AT100:AW100"/>
     <mergeCell ref="B100:E100"/>
     <mergeCell ref="F100:I100"/>
-    <mergeCell ref="J100:M100"/>
-    <mergeCell ref="N100:Q100"/>
-    <mergeCell ref="R100:U100"/>
-    <mergeCell ref="V100:Y100"/>
-    <mergeCell ref="BJ78:BM78"/>
-    <mergeCell ref="BN78:BQ78"/>
-    <mergeCell ref="BR78:BU78"/>
-    <mergeCell ref="BV78:BY78"/>
-    <mergeCell ref="BZ78:CC78"/>
-    <mergeCell ref="CD78:CG78"/>
-    <mergeCell ref="AL78:AO78"/>
-    <mergeCell ref="AP78:AS78"/>
-    <mergeCell ref="AT78:AW78"/>
-    <mergeCell ref="AX78:BA78"/>
-    <mergeCell ref="BB78:BE78"/>
-    <mergeCell ref="BF78:BI78"/>
-    <mergeCell ref="CD55:CG55"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="N78:Q78"/>
-    <mergeCell ref="R78:U78"/>
-    <mergeCell ref="V78:Y78"/>
-    <mergeCell ref="Z78:AC78"/>
-    <mergeCell ref="AD78:AG78"/>
-    <mergeCell ref="AH78:AK78"/>
-    <mergeCell ref="BF55:BI55"/>
-    <mergeCell ref="BJ55:BM55"/>
-    <mergeCell ref="BN55:BQ55"/>
-    <mergeCell ref="BR55:BU55"/>
-    <mergeCell ref="BV55:BY55"/>
-    <mergeCell ref="BZ55:CC55"/>
-    <mergeCell ref="AH55:AK55"/>
-    <mergeCell ref="AL55:AO55"/>
-    <mergeCell ref="AP55:AS55"/>
-    <mergeCell ref="AT55:AW55"/>
-    <mergeCell ref="AX55:BA55"/>
-    <mergeCell ref="BB55:BE55"/>
-    <mergeCell ref="BZ32:CC32"/>
-    <mergeCell ref="CD32:CG32"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="N55:Q55"/>
-    <mergeCell ref="R55:U55"/>
-    <mergeCell ref="V55:Y55"/>
-    <mergeCell ref="Z55:AC55"/>
-    <mergeCell ref="AD55:AG55"/>
-    <mergeCell ref="BB32:BE32"/>
-    <mergeCell ref="BF32:BI32"/>
-    <mergeCell ref="BJ32:BM32"/>
-    <mergeCell ref="BN32:BQ32"/>
-    <mergeCell ref="BR32:BU32"/>
-    <mergeCell ref="BV32:BY32"/>
-    <mergeCell ref="AD32:AG32"/>
-    <mergeCell ref="AH32:AK32"/>
-    <mergeCell ref="AL32:AO32"/>
-    <mergeCell ref="AP32:AS32"/>
-    <mergeCell ref="AT32:AW32"/>
-    <mergeCell ref="AX32:BA32"/>
-    <mergeCell ref="BV9:BY9"/>
-    <mergeCell ref="BZ9:CC9"/>
-    <mergeCell ref="CD9:CG9"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="R32:U32"/>
-    <mergeCell ref="V32:Y32"/>
-    <mergeCell ref="Z32:AC32"/>
-    <mergeCell ref="AX9:BA9"/>
-    <mergeCell ref="BB9:BE9"/>
-    <mergeCell ref="BF9:BI9"/>
-    <mergeCell ref="BJ9:BM9"/>
-    <mergeCell ref="BN9:BQ9"/>
-    <mergeCell ref="BR9:BU9"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AH9:AK9"/>
-    <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="AP9:AS9"/>
-    <mergeCell ref="AT9:AW9"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="BZ123:CC123"/>
+    <mergeCell ref="CD123:CG123"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="F146:I146"/>
+    <mergeCell ref="J146:M146"/>
+    <mergeCell ref="N146:Q146"/>
+    <mergeCell ref="R146:U146"/>
+    <mergeCell ref="V146:Y146"/>
+    <mergeCell ref="Z146:AC146"/>
+    <mergeCell ref="AD146:AG146"/>
+    <mergeCell ref="BB123:BE123"/>
+    <mergeCell ref="BF123:BI123"/>
+    <mergeCell ref="BJ123:BM123"/>
+    <mergeCell ref="BN123:BQ123"/>
+    <mergeCell ref="BR123:BU123"/>
+    <mergeCell ref="BV123:BY123"/>
+    <mergeCell ref="AD123:AG123"/>
+    <mergeCell ref="AH123:AK123"/>
+    <mergeCell ref="AL123:AO123"/>
+    <mergeCell ref="AP123:AS123"/>
+    <mergeCell ref="AT123:AW123"/>
+    <mergeCell ref="AX123:BA123"/>
+    <mergeCell ref="CD146:CG146"/>
+    <mergeCell ref="BF146:BI146"/>
+    <mergeCell ref="BJ146:BM146"/>
+    <mergeCell ref="BN146:BQ146"/>
+    <mergeCell ref="BR146:BU146"/>
+    <mergeCell ref="BV146:BY146"/>
+    <mergeCell ref="BZ146:CC146"/>
+    <mergeCell ref="AH146:AK146"/>
+    <mergeCell ref="AL146:AO146"/>
+    <mergeCell ref="AP146:AS146"/>
+    <mergeCell ref="AT146:AW146"/>
+    <mergeCell ref="AX146:BA146"/>
+    <mergeCell ref="BB146:BE146"/>
   </mergeCells>
-  <conditionalFormatting sqref="BR58:CO65 BR81:CO88 BR103:CO110">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CP58:DA65 CP81:DA88 CP103:DA110">
+  <conditionalFormatting sqref="BR58:DA65 BR81:DA88 BR103:DA110">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>

--- a/Data/National Accounts/PSA-09MAQ_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-09MAQ_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC0F0EF-7785-46E5-BF97-EFA74BD3F87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB402767-2C6F-4481-83CA-975EE309DBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="MAQ" sheetId="9" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">MAQ!$A$1:$DA$159</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">MAQ!$A$1:$DB$159</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="59">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -698,13 +698,16 @@
     <t>Table 10.7 Gross Value Added in Mining and Quarrying, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
-  </si>
-  <si>
     <t>*</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -897,7 +900,21 @@
     <cellStyle name="Normal 2 2" xfId="4" xr:uid="{97D21D1F-4EF8-4188-9D7F-BCC1E953CA47}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{B9946DC9-451A-4989-BE67-D129290ED45C}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1244,8 +1261,8 @@
     <col min="1" max="1" width="49.28515625" style="3" customWidth="1"/>
     <col min="2" max="85" width="12.28515625" style="15" customWidth="1"/>
     <col min="86" max="89" width="10.28515625" style="15" customWidth="1"/>
-    <col min="90" max="105" width="13" style="15" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="15"/>
+    <col min="90" max="106" width="13" style="15" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1260,7 +1277,7 @@
     </row>
     <row r="3" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -1271,7 +1288,7 @@
     </row>
     <row r="6" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1438,6 +1455,9 @@
       <c r="CY9" s="26"/>
       <c r="CZ9" s="26"/>
       <c r="DA9" s="26"/>
+      <c r="DB9" s="26">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1754,6 +1774,9 @@
       </c>
       <c r="DA10" s="10" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2075,7 +2098,9 @@
       <c r="DA12" s="12">
         <v>5988.9179232925389</v>
       </c>
-      <c r="DB12" s="14"/>
+      <c r="DB12" s="12">
+        <v>9270.4007819672115</v>
+      </c>
       <c r="DC12" s="14"/>
       <c r="DD12" s="14"/>
       <c r="DE12" s="14"/>
@@ -2466,7 +2491,9 @@
       <c r="DA13" s="12">
         <v>4767.6377268554515</v>
       </c>
-      <c r="DB13" s="14"/>
+      <c r="DB13" s="12">
+        <v>9211.44668924699</v>
+      </c>
       <c r="DC13" s="14"/>
       <c r="DD13" s="14"/>
       <c r="DE13" s="14"/>
@@ -2857,7 +2884,9 @@
       <c r="DA14" s="12">
         <v>24121.33716112205</v>
       </c>
-      <c r="DB14" s="14"/>
+      <c r="DB14" s="12">
+        <v>30822.082390590011</v>
+      </c>
       <c r="DC14" s="14"/>
       <c r="DD14" s="14"/>
       <c r="DE14" s="14"/>
@@ -3248,7 +3277,9 @@
       <c r="DA15" s="12">
         <v>3722.8026198904531</v>
       </c>
-      <c r="DB15" s="14"/>
+      <c r="DB15" s="12">
+        <v>18178.593271376951</v>
+      </c>
       <c r="DC15" s="14"/>
       <c r="DD15" s="14"/>
       <c r="DE15" s="14"/>
@@ -3639,7 +3670,9 @@
       <c r="DA16" s="12">
         <v>5996.5149948437911</v>
       </c>
-      <c r="DB16" s="14"/>
+      <c r="DB16" s="12">
+        <v>2793.9522461440733</v>
+      </c>
       <c r="DC16" s="14"/>
       <c r="DD16" s="14"/>
       <c r="DE16" s="14"/>
@@ -4030,7 +4063,9 @@
       <c r="DA17" s="12">
         <v>18335.832749210262</v>
       </c>
-      <c r="DB17" s="14"/>
+      <c r="DB17" s="12">
+        <v>19078.354755922042</v>
+      </c>
       <c r="DC17" s="14"/>
       <c r="DD17" s="14"/>
       <c r="DE17" s="14"/>
@@ -4601,7 +4636,9 @@
       <c r="DA19" s="16">
         <v>62933.043175214545</v>
       </c>
-      <c r="DB19" s="14"/>
+      <c r="DB19" s="16">
+        <v>89354.830135247277</v>
+      </c>
       <c r="DC19" s="14"/>
       <c r="DD19" s="14"/>
       <c r="DE19" s="14"/>
@@ -4782,6 +4819,7 @@
       <c r="CY20" s="8"/>
       <c r="CZ20" s="8"/>
       <c r="DA20" s="8"/>
+      <c r="DB20" s="8"/>
     </row>
     <row r="21" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
@@ -5160,7 +5198,7 @@
     </row>
     <row r="26" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -5171,7 +5209,7 @@
     </row>
     <row r="29" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -5338,6 +5376,9 @@
       <c r="CY32" s="26"/>
       <c r="CZ32" s="26"/>
       <c r="DA32" s="26"/>
+      <c r="DB32" s="26">
+        <v>2026</v>
+      </c>
     </row>
     <row r="33" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
@@ -5654,6 +5695,9 @@
       </c>
       <c r="DA33" s="10" t="s">
         <v>5</v>
+      </c>
+      <c r="DB33" s="10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5975,7 +6019,9 @@
       <c r="DA35" s="12">
         <v>6681.9008708265374</v>
       </c>
-      <c r="DB35" s="14"/>
+      <c r="DB35" s="12">
+        <v>9805.3269681692254</v>
+      </c>
       <c r="DC35" s="14"/>
       <c r="DD35" s="14"/>
       <c r="DE35" s="14"/>
@@ -6366,7 +6412,9 @@
       <c r="DA36" s="12">
         <v>2731.9805695235727</v>
       </c>
-      <c r="DB36" s="14"/>
+      <c r="DB36" s="12">
+        <v>3419.8338572974162</v>
+      </c>
       <c r="DC36" s="14"/>
       <c r="DD36" s="14"/>
       <c r="DE36" s="14"/>
@@ -6757,7 +6805,9 @@
       <c r="DA37" s="12">
         <v>6716.536419552498</v>
       </c>
-      <c r="DB37" s="14"/>
+      <c r="DB37" s="12">
+        <v>6093.698306316247</v>
+      </c>
       <c r="DC37" s="14"/>
       <c r="DD37" s="14"/>
       <c r="DE37" s="14"/>
@@ -7148,7 +7198,9 @@
       <c r="DA38" s="12">
         <v>1966.2359441903313</v>
       </c>
-      <c r="DB38" s="14"/>
+      <c r="DB38" s="12">
+        <v>7953.0743061500443</v>
+      </c>
       <c r="DC38" s="14"/>
       <c r="DD38" s="14"/>
       <c r="DE38" s="14"/>
@@ -7539,7 +7591,9 @@
       <c r="DA39" s="12">
         <v>1354.0688656739121</v>
       </c>
-      <c r="DB39" s="14"/>
+      <c r="DB39" s="12">
+        <v>3348.5078622013534</v>
+      </c>
       <c r="DC39" s="14"/>
       <c r="DD39" s="14"/>
       <c r="DE39" s="14"/>
@@ -7930,7 +7984,9 @@
       <c r="DA40" s="12">
         <v>19791.327058368388</v>
       </c>
-      <c r="DB40" s="14"/>
+      <c r="DB40" s="12">
+        <v>15416.050548811778</v>
+      </c>
       <c r="DC40" s="14"/>
       <c r="DD40" s="14"/>
       <c r="DE40" s="14"/>
@@ -8110,7 +8166,7 @@
       <c r="CY41" s="16"/>
       <c r="CZ41" s="16"/>
       <c r="DA41" s="16"/>
-      <c r="DB41" s="14"/>
+      <c r="DB41" s="16"/>
       <c r="DC41" s="14"/>
       <c r="DD41" s="14"/>
       <c r="DE41" s="14"/>
@@ -8501,7 +8557,9 @@
       <c r="DA42" s="16">
         <v>39242.049728135236</v>
       </c>
-      <c r="DB42" s="14"/>
+      <c r="DB42" s="16">
+        <v>46036.491848946069</v>
+      </c>
       <c r="DC42" s="14"/>
       <c r="DD42" s="14"/>
       <c r="DE42" s="14"/>
@@ -8682,6 +8740,7 @@
       <c r="CY43" s="8"/>
       <c r="CZ43" s="8"/>
       <c r="DA43" s="8"/>
+      <c r="DB43" s="8"/>
     </row>
     <row r="44" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
@@ -8793,7 +8852,7 @@
       <c r="CY45" s="13"/>
       <c r="CZ45" s="13"/>
       <c r="DA45" s="13"/>
-      <c r="DB45" s="14"/>
+      <c r="DB45" s="13"/>
       <c r="DC45" s="14"/>
       <c r="DD45" s="14"/>
       <c r="DE45" s="14"/>
@@ -8973,7 +9032,7 @@
       <c r="CY46" s="13"/>
       <c r="CZ46" s="13"/>
       <c r="DA46" s="13"/>
-      <c r="DB46" s="14"/>
+      <c r="DB46" s="13"/>
       <c r="DC46" s="14"/>
       <c r="DD46" s="14"/>
       <c r="DE46" s="14"/>
@@ -9056,6 +9115,7 @@
       <c r="CY47" s="4"/>
       <c r="CZ47" s="4"/>
       <c r="DA47" s="4"/>
+      <c r="DB47" s="4"/>
     </row>
     <row r="48" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
@@ -9065,21 +9125,24 @@
       <c r="CY48" s="4"/>
       <c r="CZ48" s="4"/>
       <c r="DA48" s="4"/>
+      <c r="DB48" s="4"/>
     </row>
     <row r="49" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CX49" s="4"/>
       <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
+      <c r="DB49" s="4"/>
     </row>
     <row r="50" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX50" s="4"/>
       <c r="CY50" s="4"/>
       <c r="CZ50" s="4"/>
       <c r="DA50" s="4"/>
+      <c r="DB50" s="4"/>
     </row>
     <row r="51" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
@@ -9089,15 +9152,17 @@
       <c r="CY51" s="4"/>
       <c r="CZ51" s="4"/>
       <c r="DA51" s="4"/>
+      <c r="DB51" s="4"/>
     </row>
     <row r="52" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="CX52" s="4"/>
       <c r="CY52" s="4"/>
       <c r="CZ52" s="4"/>
       <c r="DA52" s="4"/>
+      <c r="DB52" s="4"/>
     </row>
     <row r="53" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
@@ -9107,12 +9172,14 @@
       <c r="CY53" s="4"/>
       <c r="CZ53" s="4"/>
       <c r="DA53" s="4"/>
+      <c r="DB53" s="4"/>
     </row>
     <row r="54" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX54" s="4"/>
       <c r="CY54" s="4"/>
       <c r="CZ54" s="4"/>
       <c r="DA54" s="4"/>
+      <c r="DB54" s="4"/>
     </row>
     <row r="55" spans="1:174" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="11"/>
@@ -9266,10 +9333,13 @@
       <c r="CU55" s="26"/>
       <c r="CV55" s="26"/>
       <c r="CW55" s="26"/>
-      <c r="CX55" s="27"/>
+      <c r="CX55" s="26" t="s">
+        <v>58</v>
+      </c>
       <c r="CY55" s="27"/>
       <c r="CZ55" s="27"/>
       <c r="DA55" s="27"/>
+      <c r="DB55" s="27"/>
     </row>
     <row r="56" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
@@ -9575,17 +9645,20 @@
       <c r="CW56" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX56" s="28"/>
+      <c r="CX56" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY56" s="28"/>
       <c r="CZ56" s="28"/>
       <c r="DA56" s="28"/>
+      <c r="DB56" s="28"/>
     </row>
     <row r="57" spans="1:174" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
-      <c r="CX57" s="4"/>
       <c r="CY57" s="4"/>
       <c r="CZ57" s="4"/>
       <c r="DA57" s="4"/>
+      <c r="DB57" s="4"/>
     </row>
     <row r="58" spans="1:174" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
@@ -9891,11 +9964,13 @@
       <c r="CW58" s="17">
         <v>33.612844800019445</v>
       </c>
-      <c r="CX58" s="18"/>
+      <c r="CX58" s="17">
+        <v>5.5344972986675884</v>
+      </c>
       <c r="CY58" s="18"/>
       <c r="CZ58" s="18"/>
       <c r="DA58" s="18"/>
-      <c r="DB58" s="14"/>
+      <c r="DB58" s="18"/>
       <c r="DC58" s="14"/>
       <c r="DD58" s="14"/>
       <c r="DE58" s="14"/>
@@ -9914,10 +9989,10 @@
         <v>39</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D59" s="18">
         <v>278.18996024535841</v>
@@ -9926,7 +10001,7 @@
         <v>-34.541677306791186</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G59" s="18">
         <v>593.6028170935565</v>
@@ -10213,11 +10288,13 @@
       <c r="CW59" s="17">
         <v>-13.906081026266392</v>
       </c>
-      <c r="CX59" s="18"/>
+      <c r="CX59" s="17">
+        <v>13.257559092693995</v>
+      </c>
       <c r="CY59" s="18"/>
       <c r="CZ59" s="18"/>
       <c r="DA59" s="18"/>
-      <c r="DB59" s="14"/>
+      <c r="DB59" s="18"/>
       <c r="DC59" s="14"/>
       <c r="DD59" s="14"/>
       <c r="DE59" s="14"/>
@@ -10591,11 +10668,13 @@
       <c r="CW60" s="17">
         <v>44.183769123410343</v>
       </c>
-      <c r="CX60" s="18"/>
+      <c r="CX60" s="17">
+        <v>58.434049062855195</v>
+      </c>
       <c r="CY60" s="18"/>
       <c r="CZ60" s="18"/>
       <c r="DA60" s="18"/>
-      <c r="DB60" s="14"/>
+      <c r="DB60" s="18"/>
       <c r="DC60" s="14"/>
       <c r="DD60" s="14"/>
       <c r="DE60" s="14"/>
@@ -10739,7 +10818,7 @@
         <v>233.08189580134001</v>
       </c>
       <c r="Y61" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z61" s="18">
         <v>485.73457917091321</v>
@@ -10969,11 +11048,13 @@
       <c r="CW61" s="17">
         <v>14.45546225081948</v>
       </c>
-      <c r="CX61" s="18"/>
+      <c r="CX61" s="17">
+        <v>78.883457200782544</v>
+      </c>
       <c r="CY61" s="18"/>
       <c r="CZ61" s="18"/>
       <c r="DA61" s="18"/>
-      <c r="DB61" s="14"/>
+      <c r="DB61" s="18"/>
       <c r="DC61" s="14"/>
       <c r="DD61" s="14"/>
       <c r="DE61" s="14"/>
@@ -11347,11 +11428,13 @@
       <c r="CW62" s="17">
         <v>-0.23867834853777481</v>
       </c>
-      <c r="CX62" s="18"/>
+      <c r="CX62" s="17">
+        <v>14.337827975165823</v>
+      </c>
       <c r="CY62" s="18"/>
       <c r="CZ62" s="18"/>
       <c r="DA62" s="18"/>
-      <c r="DB62" s="14"/>
+      <c r="DB62" s="18"/>
       <c r="DC62" s="14"/>
       <c r="DD62" s="14"/>
       <c r="DE62" s="14"/>
@@ -11725,11 +11808,13 @@
       <c r="CW63" s="17">
         <v>0.90107336555487905</v>
       </c>
-      <c r="CX63" s="18"/>
+      <c r="CX63" s="17">
+        <v>0.64171516730726808</v>
+      </c>
       <c r="CY63" s="18"/>
       <c r="CZ63" s="18"/>
       <c r="DA63" s="18"/>
-      <c r="DB63" s="14"/>
+      <c r="DB63" s="18"/>
       <c r="DC63" s="14"/>
       <c r="DD63" s="14"/>
       <c r="DE63" s="14"/>
@@ -11900,11 +11985,11 @@
       <c r="CU64" s="14"/>
       <c r="CV64" s="14"/>
       <c r="CW64" s="14"/>
-      <c r="CX64" s="13"/>
+      <c r="CX64" s="14"/>
       <c r="CY64" s="13"/>
       <c r="CZ64" s="13"/>
       <c r="DA64" s="13"/>
-      <c r="DB64" s="14"/>
+      <c r="DB64" s="13"/>
       <c r="DC64" s="14"/>
       <c r="DD64" s="14"/>
       <c r="DE64" s="14"/>
@@ -12278,11 +12363,13 @@
       <c r="CW65" s="17">
         <v>16.144426974359675</v>
       </c>
-      <c r="CX65" s="18"/>
+      <c r="CX65" s="17">
+        <v>31.53147360679327</v>
+      </c>
       <c r="CY65" s="18"/>
       <c r="CZ65" s="18"/>
       <c r="DA65" s="18"/>
-      <c r="DB65" s="14"/>
+      <c r="DB65" s="18"/>
       <c r="DC65" s="14"/>
       <c r="DD65" s="14"/>
       <c r="DE65" s="14"/>
@@ -12454,19 +12541,20 @@
       <c r="CU66" s="8"/>
       <c r="CV66" s="8"/>
       <c r="CW66" s="8"/>
-      <c r="CX66" s="29"/>
+      <c r="CX66" s="8"/>
       <c r="CY66" s="29"/>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
+      <c r="DB66" s="29"/>
     </row>
     <row r="67" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CX67" s="4"/>
       <c r="CY67" s="4"/>
       <c r="CZ67" s="4"/>
       <c r="DA67" s="4"/>
+      <c r="DB67" s="4"/>
     </row>
     <row r="68" spans="1:174" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="14"/>
@@ -12569,11 +12657,11 @@
       <c r="CU68" s="14"/>
       <c r="CV68" s="14"/>
       <c r="CW68" s="14"/>
-      <c r="CX68" s="13"/>
+      <c r="CX68" s="14"/>
       <c r="CY68" s="13"/>
       <c r="CZ68" s="13"/>
       <c r="DA68" s="13"/>
-      <c r="DB68" s="14"/>
+      <c r="DB68" s="13"/>
       <c r="DC68" s="14"/>
       <c r="DD68" s="14"/>
       <c r="DE68" s="14"/>
@@ -12744,11 +12832,11 @@
       <c r="CU69" s="14"/>
       <c r="CV69" s="14"/>
       <c r="CW69" s="14"/>
-      <c r="CX69" s="13"/>
+      <c r="CX69" s="14"/>
       <c r="CY69" s="13"/>
       <c r="CZ69" s="13"/>
       <c r="DA69" s="13"/>
-      <c r="DB69" s="14"/>
+      <c r="DB69" s="13"/>
       <c r="DC69" s="14"/>
       <c r="DD69" s="14"/>
       <c r="DE69" s="14"/>
@@ -12822,67 +12910,67 @@
       <c r="A70" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CX70" s="4"/>
       <c r="CY70" s="4"/>
       <c r="CZ70" s="4"/>
       <c r="DA70" s="4"/>
+      <c r="DB70" s="4"/>
     </row>
     <row r="71" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CX71" s="4"/>
       <c r="CY71" s="4"/>
       <c r="CZ71" s="4"/>
       <c r="DA71" s="4"/>
+      <c r="DB71" s="4"/>
     </row>
     <row r="72" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="CX72" s="4"/>
+        <v>56</v>
+      </c>
       <c r="CY72" s="4"/>
       <c r="CZ72" s="4"/>
       <c r="DA72" s="4"/>
+      <c r="DB72" s="4"/>
     </row>
     <row r="73" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CX73" s="4"/>
       <c r="CY73" s="4"/>
       <c r="CZ73" s="4"/>
       <c r="DA73" s="4"/>
+      <c r="DB73" s="4"/>
     </row>
     <row r="74" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="CX74" s="4"/>
       <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
+      <c r="DB74" s="4"/>
     </row>
     <row r="75" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="CX75" s="4"/>
+        <v>57</v>
+      </c>
       <c r="CY75" s="4"/>
       <c r="CZ75" s="4"/>
       <c r="DA75" s="4"/>
+      <c r="DB75" s="4"/>
     </row>
     <row r="76" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CX76" s="4"/>
       <c r="CY76" s="4"/>
       <c r="CZ76" s="4"/>
       <c r="DA76" s="4"/>
+      <c r="DB76" s="4"/>
     </row>
     <row r="77" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CX77" s="4"/>
       <c r="CY77" s="4"/>
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
+      <c r="DB77" s="4"/>
     </row>
     <row r="78" spans="1:174" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
@@ -13036,10 +13124,13 @@
       <c r="CU78" s="26"/>
       <c r="CV78" s="26"/>
       <c r="CW78" s="26"/>
-      <c r="CX78" s="27"/>
+      <c r="CX78" s="26" t="s">
+        <v>58</v>
+      </c>
       <c r="CY78" s="27"/>
       <c r="CZ78" s="27"/>
       <c r="DA78" s="27"/>
+      <c r="DB78" s="27"/>
     </row>
     <row r="79" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
@@ -13345,17 +13436,20 @@
       <c r="CW79" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX79" s="28"/>
+      <c r="CX79" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY79" s="28"/>
       <c r="CZ79" s="28"/>
       <c r="DA79" s="28"/>
+      <c r="DB79" s="28"/>
     </row>
     <row r="80" spans="1:174" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
-      <c r="CX80" s="4"/>
       <c r="CY80" s="4"/>
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
+      <c r="DB80" s="4"/>
     </row>
     <row r="81" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
@@ -13661,11 +13755,13 @@
       <c r="CW81" s="17">
         <v>63.78219797132229</v>
       </c>
-      <c r="CX81" s="18"/>
+      <c r="CX81" s="17">
+        <v>1.9652830311923282</v>
+      </c>
       <c r="CY81" s="18"/>
       <c r="CZ81" s="18"/>
       <c r="DA81" s="18"/>
-      <c r="DB81" s="14"/>
+      <c r="DB81" s="18"/>
       <c r="DC81" s="14"/>
       <c r="DD81" s="14"/>
       <c r="DE81" s="14"/>
@@ -13740,10 +13836,10 @@
         <v>39</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D82" s="18">
         <v>176.59409765019387</v>
@@ -13752,7 +13848,7 @@
         <v>-28.111023918922697</v>
       </c>
       <c r="F82" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G82" s="18">
         <v>557.75453877962764</v>
@@ -14039,11 +14135,13 @@
       <c r="CW82" s="17">
         <v>-8.4059451623714807</v>
       </c>
-      <c r="CX82" s="18"/>
+      <c r="CX82" s="17">
+        <v>-0.23459418940556986</v>
+      </c>
       <c r="CY82" s="18"/>
       <c r="CZ82" s="18"/>
       <c r="DA82" s="18"/>
-      <c r="DB82" s="14"/>
+      <c r="DB82" s="18"/>
       <c r="DC82" s="14"/>
       <c r="DD82" s="14"/>
       <c r="DE82" s="14"/>
@@ -14417,11 +14515,13 @@
       <c r="CW83" s="17">
         <v>-7.5119250120530268</v>
       </c>
-      <c r="CX83" s="18"/>
+      <c r="CX83" s="17">
+        <v>-10.154372773027958</v>
+      </c>
       <c r="CY83" s="18"/>
       <c r="CZ83" s="18"/>
       <c r="DA83" s="18"/>
-      <c r="DB83" s="14"/>
+      <c r="DB83" s="18"/>
       <c r="DC83" s="14"/>
       <c r="DD83" s="14"/>
       <c r="DE83" s="14"/>
@@ -14565,7 +14665,7 @@
         <v>310.82743387501478</v>
       </c>
       <c r="Y84" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z84" s="18">
         <v>264.68039104028156</v>
@@ -14795,11 +14895,13 @@
       <c r="CW84" s="17">
         <v>12.69477352843171</v>
       </c>
-      <c r="CX84" s="18"/>
+      <c r="CX84" s="17">
+        <v>58.074888292232515</v>
+      </c>
       <c r="CY84" s="18"/>
       <c r="CZ84" s="18"/>
       <c r="DA84" s="18"/>
-      <c r="DB84" s="14"/>
+      <c r="DB84" s="18"/>
       <c r="DC84" s="14"/>
       <c r="DD84" s="14"/>
       <c r="DE84" s="14"/>
@@ -15173,11 +15275,13 @@
       <c r="CW85" s="17">
         <v>-11.633439240096564</v>
       </c>
-      <c r="CX85" s="18"/>
+      <c r="CX85" s="17">
+        <v>-18.037395561120178</v>
+      </c>
       <c r="CY85" s="18"/>
       <c r="CZ85" s="18"/>
       <c r="DA85" s="18"/>
-      <c r="DB85" s="14"/>
+      <c r="DB85" s="18"/>
       <c r="DC85" s="14"/>
       <c r="DD85" s="14"/>
       <c r="DE85" s="14"/>
@@ -15551,11 +15655,13 @@
       <c r="CW86" s="17">
         <v>0.2298832989659445</v>
       </c>
-      <c r="CX86" s="18"/>
+      <c r="CX86" s="17">
+        <v>8.3736588906731413E-2</v>
+      </c>
       <c r="CY86" s="18"/>
       <c r="CZ86" s="18"/>
       <c r="DA86" s="18"/>
-      <c r="DB86" s="14"/>
+      <c r="DB86" s="18"/>
       <c r="DC86" s="14"/>
       <c r="DD86" s="14"/>
       <c r="DE86" s="14"/>
@@ -15726,11 +15832,11 @@
       <c r="CU87" s="14"/>
       <c r="CV87" s="14"/>
       <c r="CW87" s="14"/>
-      <c r="CX87" s="13"/>
+      <c r="CX87" s="14"/>
       <c r="CY87" s="13"/>
       <c r="CZ87" s="13"/>
       <c r="DA87" s="13"/>
-      <c r="DB87" s="14"/>
+      <c r="DB87" s="13"/>
       <c r="DC87" s="14"/>
       <c r="DD87" s="14"/>
       <c r="DE87" s="14"/>
@@ -16104,11 +16210,13 @@
       <c r="CW88" s="17">
         <v>5.0727040939522396</v>
       </c>
-      <c r="CX88" s="18"/>
+      <c r="CX88" s="17">
+        <v>3.8111326470167057</v>
+      </c>
       <c r="CY88" s="18"/>
       <c r="CZ88" s="18"/>
       <c r="DA88" s="18"/>
-      <c r="DB88" s="14"/>
+      <c r="DB88" s="18"/>
       <c r="DC88" s="14"/>
       <c r="DD88" s="14"/>
       <c r="DE88" s="14"/>
@@ -16280,19 +16388,20 @@
       <c r="CU89" s="8"/>
       <c r="CV89" s="8"/>
       <c r="CW89" s="8"/>
-      <c r="CX89" s="29"/>
+      <c r="CX89" s="8"/>
       <c r="CY89" s="29"/>
       <c r="CZ89" s="29"/>
       <c r="DA89" s="29"/>
+      <c r="DB89" s="29"/>
     </row>
     <row r="90" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CX90" s="4"/>
       <c r="CY90" s="4"/>
       <c r="CZ90" s="4"/>
       <c r="DA90" s="4"/>
+      <c r="DB90" s="4"/>
     </row>
     <row r="91" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="14"/>
@@ -16399,7 +16508,7 @@
       <c r="CY91" s="13"/>
       <c r="CZ91" s="13"/>
       <c r="DA91" s="13"/>
-      <c r="DB91" s="14"/>
+      <c r="DB91" s="13"/>
       <c r="DC91" s="14"/>
       <c r="DD91" s="14"/>
       <c r="DE91" s="14"/>
@@ -16574,7 +16683,7 @@
       <c r="CY92" s="13"/>
       <c r="CZ92" s="13"/>
       <c r="DA92" s="13"/>
-      <c r="DB92" s="14"/>
+      <c r="DB92" s="13"/>
       <c r="DC92" s="14"/>
       <c r="DD92" s="14"/>
       <c r="DE92" s="14"/>
@@ -16657,21 +16766,24 @@
       <c r="CY93" s="4"/>
       <c r="CZ93" s="4"/>
       <c r="DA93" s="4"/>
+      <c r="DB93" s="4"/>
     </row>
     <row r="94" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CX94" s="4"/>
       <c r="CY94" s="4"/>
       <c r="CZ94" s="4"/>
       <c r="DA94" s="4"/>
+      <c r="DB94" s="4"/>
     </row>
     <row r="95" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX95" s="4"/>
       <c r="CY95" s="4"/>
       <c r="CZ95" s="4"/>
       <c r="DA95" s="4"/>
+      <c r="DB95" s="4"/>
     </row>
     <row r="96" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
@@ -16680,7 +16792,7 @@
     </row>
     <row r="97" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -16847,6 +16959,9 @@
       <c r="CY100" s="26"/>
       <c r="CZ100" s="26"/>
       <c r="DA100" s="26"/>
+      <c r="DB100" s="26">
+        <v>2026</v>
+      </c>
     </row>
     <row r="101" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
@@ -17163,6 +17278,9 @@
       </c>
       <c r="DA101" s="10" t="s">
         <v>5</v>
+      </c>
+      <c r="DB101" s="10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17484,7 +17602,9 @@
       <c r="DA103" s="17">
         <v>89.628954979568903</v>
       </c>
-      <c r="DB103" s="14"/>
+      <c r="DB103" s="17">
+        <v>94.544534945764369</v>
+      </c>
       <c r="DC103" s="14"/>
       <c r="DD103" s="14"/>
       <c r="DE103" s="14"/>
@@ -17875,7 +17995,9 @@
       <c r="DA104" s="17">
         <v>174.51213892369941</v>
       </c>
-      <c r="DB104" s="14"/>
+      <c r="DB104" s="17">
+        <v>269.35363159795418</v>
+      </c>
       <c r="DC104" s="14"/>
       <c r="DD104" s="14"/>
       <c r="DE104" s="14"/>
@@ -18266,7 +18388,9 @@
       <c r="DA105" s="17">
         <v>359.13357204321062</v>
       </c>
-      <c r="DB105" s="14"/>
+      <c r="DB105" s="17">
+        <v>505.8025658842065</v>
+      </c>
       <c r="DC105" s="14"/>
       <c r="DD105" s="14"/>
       <c r="DE105" s="14"/>
@@ -18657,7 +18781,9 @@
       <c r="DA106" s="17">
         <v>189.33651532972314</v>
       </c>
-      <c r="DB106" s="14"/>
+      <c r="DB106" s="17">
+        <v>228.57316015920537</v>
+      </c>
       <c r="DC106" s="14"/>
       <c r="DD106" s="14"/>
       <c r="DE106" s="14"/>
@@ -19048,7 +19174,9 @@
       <c r="DA107" s="17">
         <v>442.85155259510088</v>
       </c>
-      <c r="DB107" s="14"/>
+      <c r="DB107" s="17">
+        <v>83.438724384756028</v>
+      </c>
       <c r="DC107" s="14"/>
       <c r="DD107" s="14"/>
       <c r="DE107" s="14"/>
@@ -19439,7 +19567,9 @@
       <c r="DA108" s="17">
         <v>92.645797298657158</v>
       </c>
-      <c r="DB108" s="14"/>
+      <c r="DB108" s="17">
+        <v>123.75643616057386</v>
+      </c>
       <c r="DC108" s="14"/>
       <c r="DD108" s="14"/>
       <c r="DE108" s="14"/>
@@ -20010,7 +20140,9 @@
       <c r="DA110" s="17">
         <v>160.37144749371657</v>
       </c>
-      <c r="DB110" s="14"/>
+      <c r="DB110" s="17">
+        <v>194.095654439605</v>
+      </c>
       <c r="DC110" s="14"/>
       <c r="DD110" s="14"/>
       <c r="DE110" s="14"/>
@@ -20191,6 +20323,7 @@
       <c r="CY111" s="8"/>
       <c r="CZ111" s="8"/>
       <c r="DA111" s="8"/>
+      <c r="DB111" s="8"/>
     </row>
     <row r="112" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9" t="s">
@@ -20209,7 +20342,7 @@
     </row>
     <row r="117" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -20220,7 +20353,7 @@
     </row>
     <row r="120" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="121" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -20387,6 +20520,9 @@
       <c r="CY123" s="26"/>
       <c r="CZ123" s="26"/>
       <c r="DA123" s="26"/>
+      <c r="DB123" s="26">
+        <v>2026</v>
+      </c>
     </row>
     <row r="124" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
@@ -20703,6 +20839,9 @@
       </c>
       <c r="DA124" s="10" t="s">
         <v>5</v>
+      </c>
+      <c r="DB124" s="10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -21024,7 +21163,9 @@
       <c r="DA126" s="20">
         <v>9.5163329486841111</v>
       </c>
-      <c r="DB126" s="14"/>
+      <c r="DB126" s="20">
+        <v>10.374817755162818</v>
+      </c>
       <c r="DC126" s="14"/>
       <c r="DD126" s="14"/>
       <c r="DE126" s="14"/>
@@ -21415,7 +21556,9 @@
       <c r="DA127" s="20">
         <v>7.5757304689392972</v>
       </c>
-      <c r="DB127" s="14"/>
+      <c r="DB127" s="20">
+        <v>10.308840244343328</v>
+      </c>
       <c r="DC127" s="14"/>
       <c r="DD127" s="14"/>
       <c r="DE127" s="14"/>
@@ -21806,7 +21949,9 @@
       <c r="DA128" s="20">
         <v>38.32857262911125</v>
       </c>
-      <c r="DB128" s="14"/>
+      <c r="DB128" s="20">
+        <v>34.494030534149942</v>
+      </c>
       <c r="DC128" s="14"/>
       <c r="DD128" s="14"/>
       <c r="DE128" s="14"/>
@@ -22197,7 +22342,9 @@
       <c r="DA129" s="20">
         <v>5.9154975384324588</v>
       </c>
-      <c r="DB129" s="14"/>
+      <c r="DB129" s="20">
+        <v>20.344276010442716</v>
+      </c>
       <c r="DC129" s="14"/>
       <c r="DD129" s="14"/>
       <c r="DE129" s="14"/>
@@ -22588,7 +22735,9 @@
       <c r="DA130" s="20">
         <v>9.5284046222723422</v>
       </c>
-      <c r="DB130" s="14"/>
+      <c r="DB130" s="20">
+        <v>3.1268060628789214</v>
+      </c>
       <c r="DC130" s="14"/>
       <c r="DD130" s="14"/>
       <c r="DE130" s="14"/>
@@ -22979,7 +23128,9 @@
       <c r="DA131" s="20">
         <v>29.135461792560541</v>
       </c>
-      <c r="DB131" s="14"/>
+      <c r="DB131" s="20">
+        <v>21.351229393022276</v>
+      </c>
       <c r="DC131" s="14"/>
       <c r="DD131" s="14"/>
       <c r="DE131" s="14"/>
@@ -23550,7 +23701,9 @@
       <c r="DA133" s="20">
         <v>100</v>
       </c>
-      <c r="DB133" s="14"/>
+      <c r="DB133" s="20">
+        <v>100</v>
+      </c>
       <c r="DC133" s="14"/>
       <c r="DD133" s="14"/>
       <c r="DE133" s="14"/>
@@ -23731,6 +23884,7 @@
       <c r="CY134" s="8"/>
       <c r="CZ134" s="8"/>
       <c r="DA134" s="8"/>
+      <c r="DB134" s="8"/>
     </row>
     <row r="135" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9" t="s">
@@ -24109,7 +24263,7 @@
     </row>
     <row r="140" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="141" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -24120,7 +24274,7 @@
     </row>
     <row r="143" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="144" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -24287,6 +24441,9 @@
       <c r="CY146" s="26"/>
       <c r="CZ146" s="26"/>
       <c r="DA146" s="26"/>
+      <c r="DB146" s="26">
+        <v>2026</v>
+      </c>
     </row>
     <row r="147" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
@@ -24603,6 +24760,9 @@
       </c>
       <c r="DA147" s="10" t="s">
         <v>5</v>
+      </c>
+      <c r="DB147" s="10" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -24924,7 +25084,9 @@
       <c r="DA149" s="20">
         <v>17.027400243152531</v>
       </c>
-      <c r="DB149" s="14"/>
+      <c r="DB149" s="20">
+        <v>21.299031647203375</v>
+      </c>
       <c r="DC149" s="14"/>
       <c r="DD149" s="14"/>
       <c r="DE149" s="14"/>
@@ -25315,7 +25477,9 @@
       <c r="DA150" s="20">
         <v>6.9618702092537079</v>
       </c>
-      <c r="DB150" s="14"/>
+      <c r="DB150" s="20">
+        <v>7.4285283694476556</v>
+      </c>
       <c r="DC150" s="14"/>
       <c r="DD150" s="14"/>
       <c r="DE150" s="14"/>
@@ -25706,7 +25870,9 @@
       <c r="DA151" s="20">
         <v>17.115661557140747</v>
       </c>
-      <c r="DB151" s="14"/>
+      <c r="DB151" s="20">
+        <v>13.236669567070308</v>
+      </c>
       <c r="DC151" s="14"/>
       <c r="DD151" s="14"/>
       <c r="DE151" s="14"/>
@@ -26097,7 +26263,9 @@
       <c r="DA152" s="20">
         <v>5.0105332361897652</v>
       </c>
-      <c r="DB152" s="14"/>
+      <c r="DB152" s="20">
+        <v>17.275587228161299</v>
+      </c>
       <c r="DC152" s="14"/>
       <c r="DD152" s="14"/>
       <c r="DE152" s="14"/>
@@ -26488,7 +26656,9 @@
       <c r="DA153" s="20">
         <v>3.4505559089159656</v>
       </c>
-      <c r="DB153" s="14"/>
+      <c r="DB153" s="20">
+        <v>7.2735947673606498</v>
+      </c>
       <c r="DC153" s="14"/>
       <c r="DD153" s="14"/>
       <c r="DE153" s="14"/>
@@ -26879,7 +27049,9 @@
       <c r="DA154" s="20">
         <v>50.433978845347283</v>
       </c>
-      <c r="DB154" s="14"/>
+      <c r="DB154" s="20">
+        <v>33.486588420756703</v>
+      </c>
       <c r="DC154" s="14"/>
       <c r="DD154" s="14"/>
       <c r="DE154" s="14"/>
@@ -27450,7 +27622,9 @@
       <c r="DA156" s="20">
         <v>100</v>
       </c>
-      <c r="DB156" s="14"/>
+      <c r="DB156" s="20">
+        <v>100</v>
+      </c>
       <c r="DC156" s="14"/>
       <c r="DD156" s="14"/>
       <c r="DE156" s="14"/>
@@ -27631,6 +27805,7 @@
       <c r="CY157" s="8"/>
       <c r="CZ157" s="8"/>
       <c r="DA157" s="8"/>
+      <c r="DB157" s="8"/>
     </row>
     <row r="158" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="9" t="s">
@@ -27873,8 +28048,9 @@
       <c r="CY160" s="21"/>
       <c r="CZ160" s="21"/>
       <c r="DA160" s="21"/>
+      <c r="DB160" s="21"/>
     </row>
-    <row r="161" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="161" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT161" s="21"/>
       <c r="CU161" s="21"/>
       <c r="CV161" s="21"/>
@@ -27883,8 +28059,9 @@
       <c r="CY161" s="21"/>
       <c r="CZ161" s="21"/>
       <c r="DA161" s="21"/>
+      <c r="DB161" s="21"/>
     </row>
-    <row r="162" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="162" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT162" s="21"/>
       <c r="CU162" s="21"/>
       <c r="CV162" s="21"/>
@@ -27894,7 +28071,7 @@
       <c r="CZ162" s="21"/>
       <c r="DA162" s="21"/>
     </row>
-    <row r="163" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="163" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT163" s="21"/>
       <c r="CU163" s="21"/>
       <c r="CV163" s="21"/>
@@ -27904,7 +28081,7 @@
       <c r="CZ163" s="21"/>
       <c r="DA163" s="21"/>
     </row>
-    <row r="164" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="164" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT164" s="21"/>
       <c r="CU164" s="21"/>
       <c r="CV164" s="21"/>
@@ -27914,7 +28091,7 @@
       <c r="CZ164" s="21"/>
       <c r="DA164" s="21"/>
     </row>
-    <row r="165" spans="98:105" x14ac:dyDescent="0.2">
+    <row r="165" spans="98:106" x14ac:dyDescent="0.2">
       <c r="CT165" s="21"/>
       <c r="CU165" s="21"/>
       <c r="CV165" s="21"/>
@@ -27926,37 +28103,98 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="AT9:AW9"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="AP32:AS32"/>
-    <mergeCell ref="AT32:AW32"/>
-    <mergeCell ref="AX32:BA32"/>
-    <mergeCell ref="BV9:BY9"/>
-    <mergeCell ref="BZ9:CC9"/>
-    <mergeCell ref="CD9:CG9"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="R32:U32"/>
-    <mergeCell ref="V32:Y32"/>
-    <mergeCell ref="Z32:AC32"/>
-    <mergeCell ref="AX9:BA9"/>
-    <mergeCell ref="BB9:BE9"/>
-    <mergeCell ref="BF9:BI9"/>
-    <mergeCell ref="BJ9:BM9"/>
-    <mergeCell ref="BN9:BQ9"/>
-    <mergeCell ref="BR9:BU9"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AH9:AK9"/>
-    <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="AP9:AS9"/>
+    <mergeCell ref="CD146:CG146"/>
+    <mergeCell ref="BF146:BI146"/>
+    <mergeCell ref="BJ146:BM146"/>
+    <mergeCell ref="BN146:BQ146"/>
+    <mergeCell ref="BR146:BU146"/>
+    <mergeCell ref="BV146:BY146"/>
+    <mergeCell ref="BZ146:CC146"/>
+    <mergeCell ref="AH146:AK146"/>
+    <mergeCell ref="AL146:AO146"/>
+    <mergeCell ref="AP146:AS146"/>
+    <mergeCell ref="AT146:AW146"/>
+    <mergeCell ref="AX146:BA146"/>
+    <mergeCell ref="BB146:BE146"/>
+    <mergeCell ref="BF123:BI123"/>
+    <mergeCell ref="BJ123:BM123"/>
+    <mergeCell ref="BN123:BQ123"/>
+    <mergeCell ref="BR123:BU123"/>
+    <mergeCell ref="BV123:BY123"/>
+    <mergeCell ref="AD123:AG123"/>
+    <mergeCell ref="AH123:AK123"/>
+    <mergeCell ref="AL123:AO123"/>
+    <mergeCell ref="AP123:AS123"/>
+    <mergeCell ref="AT123:AW123"/>
+    <mergeCell ref="AX123:BA123"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="F146:I146"/>
+    <mergeCell ref="J146:M146"/>
+    <mergeCell ref="N146:Q146"/>
+    <mergeCell ref="R146:U146"/>
+    <mergeCell ref="V146:Y146"/>
+    <mergeCell ref="Z146:AC146"/>
+    <mergeCell ref="AD146:AG146"/>
+    <mergeCell ref="BB123:BE123"/>
+    <mergeCell ref="CD100:CG100"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="F123:I123"/>
+    <mergeCell ref="J123:M123"/>
+    <mergeCell ref="N123:Q123"/>
+    <mergeCell ref="R123:U123"/>
+    <mergeCell ref="V123:Y123"/>
+    <mergeCell ref="Z123:AC123"/>
+    <mergeCell ref="AX100:BA100"/>
+    <mergeCell ref="BB100:BE100"/>
+    <mergeCell ref="BF100:BI100"/>
+    <mergeCell ref="BJ100:BM100"/>
+    <mergeCell ref="BN100:BQ100"/>
+    <mergeCell ref="BR100:BU100"/>
+    <mergeCell ref="Z100:AC100"/>
+    <mergeCell ref="AD100:AG100"/>
+    <mergeCell ref="AH100:AK100"/>
+    <mergeCell ref="AL100:AO100"/>
+    <mergeCell ref="AP100:AS100"/>
+    <mergeCell ref="AT100:AW100"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="F100:I100"/>
+    <mergeCell ref="BZ123:CC123"/>
+    <mergeCell ref="CD123:CG123"/>
+    <mergeCell ref="J100:M100"/>
+    <mergeCell ref="N100:Q100"/>
+    <mergeCell ref="R100:U100"/>
+    <mergeCell ref="V100:Y100"/>
+    <mergeCell ref="BJ78:BM78"/>
+    <mergeCell ref="BN78:BQ78"/>
+    <mergeCell ref="BR78:BU78"/>
+    <mergeCell ref="BV78:BY78"/>
+    <mergeCell ref="BZ78:CC78"/>
+    <mergeCell ref="BV100:BY100"/>
+    <mergeCell ref="BZ100:CC100"/>
+    <mergeCell ref="CD78:CG78"/>
+    <mergeCell ref="AL78:AO78"/>
+    <mergeCell ref="AP78:AS78"/>
+    <mergeCell ref="AT78:AW78"/>
+    <mergeCell ref="AX78:BA78"/>
+    <mergeCell ref="BB78:BE78"/>
+    <mergeCell ref="BF78:BI78"/>
+    <mergeCell ref="CD55:CG55"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="N78:Q78"/>
+    <mergeCell ref="R78:U78"/>
+    <mergeCell ref="V78:Y78"/>
+    <mergeCell ref="Z78:AC78"/>
+    <mergeCell ref="AD78:AG78"/>
+    <mergeCell ref="AH78:AK78"/>
+    <mergeCell ref="BF55:BI55"/>
+    <mergeCell ref="BJ55:BM55"/>
+    <mergeCell ref="BN55:BQ55"/>
+    <mergeCell ref="BR55:BU55"/>
+    <mergeCell ref="BV55:BY55"/>
+    <mergeCell ref="BZ55:CC55"/>
+    <mergeCell ref="AH55:AK55"/>
     <mergeCell ref="AL55:AO55"/>
     <mergeCell ref="AP55:AS55"/>
     <mergeCell ref="AT55:AW55"/>
@@ -27981,100 +28219,49 @@
     <mergeCell ref="AD32:AG32"/>
     <mergeCell ref="AH32:AK32"/>
     <mergeCell ref="AL32:AO32"/>
-    <mergeCell ref="CD78:CG78"/>
-    <mergeCell ref="AL78:AO78"/>
-    <mergeCell ref="AP78:AS78"/>
-    <mergeCell ref="AT78:AW78"/>
-    <mergeCell ref="AX78:BA78"/>
-    <mergeCell ref="BB78:BE78"/>
-    <mergeCell ref="BF78:BI78"/>
-    <mergeCell ref="CD55:CG55"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="N78:Q78"/>
-    <mergeCell ref="R78:U78"/>
-    <mergeCell ref="V78:Y78"/>
-    <mergeCell ref="Z78:AC78"/>
-    <mergeCell ref="AD78:AG78"/>
-    <mergeCell ref="AH78:AK78"/>
-    <mergeCell ref="BF55:BI55"/>
-    <mergeCell ref="BJ55:BM55"/>
-    <mergeCell ref="BN55:BQ55"/>
-    <mergeCell ref="BR55:BU55"/>
-    <mergeCell ref="BV55:BY55"/>
-    <mergeCell ref="BZ55:CC55"/>
-    <mergeCell ref="AH55:AK55"/>
-    <mergeCell ref="J100:M100"/>
-    <mergeCell ref="N100:Q100"/>
-    <mergeCell ref="R100:U100"/>
-    <mergeCell ref="V100:Y100"/>
-    <mergeCell ref="BJ78:BM78"/>
-    <mergeCell ref="BN78:BQ78"/>
-    <mergeCell ref="BR78:BU78"/>
-    <mergeCell ref="BV78:BY78"/>
-    <mergeCell ref="BZ78:CC78"/>
-    <mergeCell ref="BV100:BY100"/>
-    <mergeCell ref="BZ100:CC100"/>
-    <mergeCell ref="CD100:CG100"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="F123:I123"/>
-    <mergeCell ref="J123:M123"/>
-    <mergeCell ref="N123:Q123"/>
-    <mergeCell ref="R123:U123"/>
-    <mergeCell ref="V123:Y123"/>
-    <mergeCell ref="Z123:AC123"/>
-    <mergeCell ref="AX100:BA100"/>
-    <mergeCell ref="BB100:BE100"/>
-    <mergeCell ref="BF100:BI100"/>
-    <mergeCell ref="BJ100:BM100"/>
-    <mergeCell ref="BN100:BQ100"/>
-    <mergeCell ref="BR100:BU100"/>
-    <mergeCell ref="Z100:AC100"/>
-    <mergeCell ref="AD100:AG100"/>
-    <mergeCell ref="AH100:AK100"/>
-    <mergeCell ref="AL100:AO100"/>
-    <mergeCell ref="AP100:AS100"/>
-    <mergeCell ref="AT100:AW100"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="F100:I100"/>
-    <mergeCell ref="BZ123:CC123"/>
-    <mergeCell ref="CD123:CG123"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="F146:I146"/>
-    <mergeCell ref="J146:M146"/>
-    <mergeCell ref="N146:Q146"/>
-    <mergeCell ref="R146:U146"/>
-    <mergeCell ref="V146:Y146"/>
-    <mergeCell ref="Z146:AC146"/>
-    <mergeCell ref="AD146:AG146"/>
-    <mergeCell ref="BB123:BE123"/>
-    <mergeCell ref="BF123:BI123"/>
-    <mergeCell ref="BJ123:BM123"/>
-    <mergeCell ref="BN123:BQ123"/>
-    <mergeCell ref="BR123:BU123"/>
-    <mergeCell ref="BV123:BY123"/>
-    <mergeCell ref="AD123:AG123"/>
-    <mergeCell ref="AH123:AK123"/>
-    <mergeCell ref="AL123:AO123"/>
-    <mergeCell ref="AP123:AS123"/>
-    <mergeCell ref="AT123:AW123"/>
-    <mergeCell ref="AX123:BA123"/>
-    <mergeCell ref="CD146:CG146"/>
-    <mergeCell ref="BF146:BI146"/>
-    <mergeCell ref="BJ146:BM146"/>
-    <mergeCell ref="BN146:BQ146"/>
-    <mergeCell ref="BR146:BU146"/>
-    <mergeCell ref="BV146:BY146"/>
-    <mergeCell ref="BZ146:CC146"/>
-    <mergeCell ref="AH146:AK146"/>
-    <mergeCell ref="AL146:AO146"/>
-    <mergeCell ref="AP146:AS146"/>
-    <mergeCell ref="AT146:AW146"/>
-    <mergeCell ref="AX146:BA146"/>
-    <mergeCell ref="BB146:BE146"/>
+    <mergeCell ref="AX32:BA32"/>
+    <mergeCell ref="BV9:BY9"/>
+    <mergeCell ref="BZ9:CC9"/>
+    <mergeCell ref="CD9:CG9"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="R32:U32"/>
+    <mergeCell ref="V32:Y32"/>
+    <mergeCell ref="Z32:AC32"/>
+    <mergeCell ref="AX9:BA9"/>
+    <mergeCell ref="BB9:BE9"/>
+    <mergeCell ref="BF9:BI9"/>
+    <mergeCell ref="BJ9:BM9"/>
+    <mergeCell ref="BN9:BQ9"/>
+    <mergeCell ref="BR9:BU9"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AH9:AK9"/>
+    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="AP9:AS9"/>
+    <mergeCell ref="AT9:AW9"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="AP32:AS32"/>
+    <mergeCell ref="AT32:AW32"/>
   </mergeCells>
-  <conditionalFormatting sqref="BR58:DA65 BR81:DA88 BR103:DA110">
+  <conditionalFormatting sqref="BR58:CW65 BR81:CW88 BR103:DA110 CY81:DA88 CY58:DA65">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="DB58:DB65 DB81:DB88 DB103:DB110">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
+      <formula>1000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CX58:CX65 CX81:CX88">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
@@ -28084,13 +28271,13 @@
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="46" max="81" man="1"/>
-    <brk id="92" max="81" man="1"/>
-    <brk id="114" max="81" man="1"/>
+    <brk id="46" max="105" man="1"/>
+    <brk id="92" max="105" man="1"/>
+    <brk id="114" max="105" man="1"/>
   </rowBreaks>
   <colBreaks count="2" manualBreakCount="2">
-    <brk id="56" max="180" man="1"/>
-    <brk id="86" max="180" man="1"/>
+    <brk id="56" max="158" man="1"/>
+    <brk id="86" max="158" man="1"/>
   </colBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-09MAQ_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-09MAQ_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB402767-2C6F-4481-83CA-975EE309DBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6C6613-F719-4A7E-8798-DA77C36281DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">MAQ!$A$1:$DB$159</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">MAQ!$A$1:$DC$159</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="59">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -701,13 +701,13 @@
     <t>*</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1261,8 +1261,8 @@
     <col min="1" max="1" width="49.28515625" style="3" customWidth="1"/>
     <col min="2" max="85" width="12.28515625" style="15" customWidth="1"/>
     <col min="86" max="89" width="10.28515625" style="15" customWidth="1"/>
-    <col min="90" max="106" width="13" style="15" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="15"/>
+    <col min="90" max="107" width="13" style="15" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="3" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="6" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1458,6 +1458,7 @@
       <c r="DB9" s="26">
         <v>2026</v>
       </c>
+      <c r="DC9" s="26"/>
     </row>
     <row r="10" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1777,6 +1778,9 @@
       </c>
       <c r="DB10" s="10" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2099,9 +2103,11 @@
         <v>5988.9179232925389</v>
       </c>
       <c r="DB12" s="12">
-        <v>9270.4007819672115</v>
-      </c>
-      <c r="DC12" s="14"/>
+        <v>9272.3976074582642</v>
+      </c>
+      <c r="DC12" s="12">
+        <v>5466.9711702890709</v>
+      </c>
       <c r="DD12" s="14"/>
       <c r="DE12" s="14"/>
       <c r="DF12" s="14"/>
@@ -2494,7 +2500,9 @@
       <c r="DB13" s="12">
         <v>9211.44668924699</v>
       </c>
-      <c r="DC13" s="14"/>
+      <c r="DC13" s="12">
+        <v>5453.9009281228955</v>
+      </c>
       <c r="DD13" s="14"/>
       <c r="DE13" s="14"/>
       <c r="DF13" s="14"/>
@@ -2885,9 +2893,11 @@
         <v>24121.33716112205</v>
       </c>
       <c r="DB14" s="12">
-        <v>30822.082390590011</v>
-      </c>
-      <c r="DC14" s="14"/>
+        <v>30727.306851206518</v>
+      </c>
+      <c r="DC14" s="12">
+        <v>37129.96297422611</v>
+      </c>
       <c r="DD14" s="14"/>
       <c r="DE14" s="14"/>
       <c r="DF14" s="14"/>
@@ -3278,9 +3288,11 @@
         <v>3722.8026198904531</v>
       </c>
       <c r="DB15" s="12">
-        <v>18178.593271376951</v>
-      </c>
-      <c r="DC15" s="14"/>
+        <v>19053.911182804168</v>
+      </c>
+      <c r="DC15" s="12">
+        <v>19768.953231027073</v>
+      </c>
       <c r="DD15" s="14"/>
       <c r="DE15" s="14"/>
       <c r="DF15" s="14"/>
@@ -3671,9 +3683,11 @@
         <v>5996.5149948437911</v>
       </c>
       <c r="DB16" s="12">
-        <v>2793.9522461440733</v>
-      </c>
-      <c r="DC16" s="14"/>
+        <v>2745.0513208158368</v>
+      </c>
+      <c r="DC16" s="12">
+        <v>6754.8112943033848</v>
+      </c>
       <c r="DD16" s="14"/>
       <c r="DE16" s="14"/>
       <c r="DF16" s="14"/>
@@ -4064,9 +4078,11 @@
         <v>18335.832749210262</v>
       </c>
       <c r="DB17" s="12">
-        <v>19078.354755922042</v>
-      </c>
-      <c r="DC17" s="14"/>
+        <v>19121.824200900362</v>
+      </c>
+      <c r="DC17" s="12">
+        <v>11840.519260448769</v>
+      </c>
       <c r="DD17" s="14"/>
       <c r="DE17" s="14"/>
       <c r="DF17" s="14"/>
@@ -4637,9 +4653,11 @@
         <v>62933.043175214545</v>
       </c>
       <c r="DB19" s="16">
-        <v>89354.830135247277</v>
-      </c>
-      <c r="DC19" s="14"/>
+        <v>90131.937852432136</v>
+      </c>
+      <c r="DC19" s="16">
+        <v>86415.118858417307</v>
+      </c>
       <c r="DD19" s="14"/>
       <c r="DE19" s="14"/>
       <c r="DF19" s="14"/>
@@ -4820,6 +4838,7 @@
       <c r="CZ20" s="8"/>
       <c r="DA20" s="8"/>
       <c r="DB20" s="8"/>
+      <c r="DC20" s="8"/>
     </row>
     <row r="21" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
@@ -5198,7 +5217,7 @@
     </row>
     <row r="26" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -5209,7 +5228,7 @@
     </row>
     <row r="29" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -5379,6 +5398,7 @@
       <c r="DB32" s="26">
         <v>2026</v>
       </c>
+      <c r="DC32" s="26"/>
     </row>
     <row r="33" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
@@ -5698,6 +5718,9 @@
       </c>
       <c r="DB33" s="10" t="s">
         <v>2</v>
+      </c>
+      <c r="DC33" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -6020,9 +6043,11 @@
         <v>6681.9008708265374</v>
       </c>
       <c r="DB35" s="12">
-        <v>9805.3269681692254</v>
-      </c>
-      <c r="DC35" s="14"/>
+        <v>9807.4390156738209</v>
+      </c>
+      <c r="DC35" s="12">
+        <v>4794.8318989163117</v>
+      </c>
       <c r="DD35" s="14"/>
       <c r="DE35" s="14"/>
       <c r="DF35" s="14"/>
@@ -6415,7 +6440,9 @@
       <c r="DB36" s="12">
         <v>3419.8338572974162</v>
       </c>
-      <c r="DC36" s="14"/>
+      <c r="DC36" s="12">
+        <v>6014.1893916778854</v>
+      </c>
       <c r="DD36" s="14"/>
       <c r="DE36" s="14"/>
       <c r="DF36" s="14"/>
@@ -6806,9 +6833,11 @@
         <v>6716.536419552498</v>
       </c>
       <c r="DB37" s="12">
-        <v>6093.698306316247</v>
-      </c>
-      <c r="DC37" s="14"/>
+        <v>6074.9614047580353</v>
+      </c>
+      <c r="DC37" s="12">
+        <v>8063.648143543106</v>
+      </c>
       <c r="DD37" s="14"/>
       <c r="DE37" s="14"/>
       <c r="DF37" s="14"/>
@@ -7199,9 +7228,11 @@
         <v>1966.2359441903313</v>
       </c>
       <c r="DB38" s="12">
-        <v>7953.0743061500443</v>
-      </c>
-      <c r="DC38" s="14"/>
+        <v>8336.0229912964314</v>
+      </c>
+      <c r="DC38" s="12">
+        <v>10459.886305802815</v>
+      </c>
       <c r="DD38" s="14"/>
       <c r="DE38" s="14"/>
       <c r="DF38" s="14"/>
@@ -7592,9 +7623,11 @@
         <v>1354.0688656739121</v>
       </c>
       <c r="DB39" s="12">
-        <v>3348.5078622013534</v>
-      </c>
-      <c r="DC39" s="14"/>
+        <v>3289.9008716357466</v>
+      </c>
+      <c r="DC39" s="12">
+        <v>1482.074468801291</v>
+      </c>
       <c r="DD39" s="14"/>
       <c r="DE39" s="14"/>
       <c r="DF39" s="14"/>
@@ -7985,9 +8018,11 @@
         <v>19791.327058368388</v>
       </c>
       <c r="DB40" s="12">
-        <v>15416.050548811778</v>
-      </c>
-      <c r="DC40" s="14"/>
+        <v>15451.1755462074</v>
+      </c>
+      <c r="DC40" s="12">
+        <v>9100.2542072986416</v>
+      </c>
       <c r="DD40" s="14"/>
       <c r="DE40" s="14"/>
       <c r="DF40" s="14"/>
@@ -8167,7 +8202,7 @@
       <c r="CZ41" s="16"/>
       <c r="DA41" s="16"/>
       <c r="DB41" s="16"/>
-      <c r="DC41" s="14"/>
+      <c r="DC41" s="16"/>
       <c r="DD41" s="14"/>
       <c r="DE41" s="14"/>
       <c r="DF41" s="14"/>
@@ -8558,9 +8593,11 @@
         <v>39242.049728135236</v>
       </c>
       <c r="DB42" s="16">
-        <v>46036.491848946069</v>
-      </c>
-      <c r="DC42" s="14"/>
+        <v>46379.333686868849</v>
+      </c>
+      <c r="DC42" s="16">
+        <v>39914.884416040048</v>
+      </c>
       <c r="DD42" s="14"/>
       <c r="DE42" s="14"/>
       <c r="DF42" s="14"/>
@@ -8741,6 +8778,7 @@
       <c r="CZ43" s="8"/>
       <c r="DA43" s="8"/>
       <c r="DB43" s="8"/>
+      <c r="DC43" s="8"/>
     </row>
     <row r="44" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
@@ -8853,7 +8891,7 @@
       <c r="CZ45" s="13"/>
       <c r="DA45" s="13"/>
       <c r="DB45" s="13"/>
-      <c r="DC45" s="14"/>
+      <c r="DC45" s="13"/>
       <c r="DD45" s="14"/>
       <c r="DE45" s="14"/>
       <c r="DF45" s="14"/>
@@ -9033,7 +9071,7 @@
       <c r="CZ46" s="13"/>
       <c r="DA46" s="13"/>
       <c r="DB46" s="13"/>
-      <c r="DC46" s="14"/>
+      <c r="DC46" s="13"/>
       <c r="DD46" s="14"/>
       <c r="DE46" s="14"/>
       <c r="DF46" s="14"/>
@@ -9116,6 +9154,7 @@
       <c r="CZ47" s="4"/>
       <c r="DA47" s="4"/>
       <c r="DB47" s="4"/>
+      <c r="DC47" s="4"/>
     </row>
     <row r="48" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
@@ -9126,16 +9165,18 @@
       <c r="CZ48" s="4"/>
       <c r="DA48" s="4"/>
       <c r="DB48" s="4"/>
+      <c r="DC48" s="4"/>
     </row>
     <row r="49" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="CX49" s="4"/>
       <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
       <c r="DB49" s="4"/>
+      <c r="DC49" s="4"/>
     </row>
     <row r="50" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX50" s="4"/>
@@ -9143,6 +9184,7 @@
       <c r="CZ50" s="4"/>
       <c r="DA50" s="4"/>
       <c r="DB50" s="4"/>
+      <c r="DC50" s="4"/>
     </row>
     <row r="51" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
@@ -9153,16 +9195,18 @@
       <c r="CZ51" s="4"/>
       <c r="DA51" s="4"/>
       <c r="DB51" s="4"/>
+      <c r="DC51" s="4"/>
     </row>
     <row r="52" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="CX52" s="4"/>
       <c r="CY52" s="4"/>
       <c r="CZ52" s="4"/>
       <c r="DA52" s="4"/>
       <c r="DB52" s="4"/>
+      <c r="DC52" s="4"/>
     </row>
     <row r="53" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
@@ -9173,13 +9217,13 @@
       <c r="CZ53" s="4"/>
       <c r="DA53" s="4"/>
       <c r="DB53" s="4"/>
+      <c r="DC53" s="4"/>
     </row>
     <row r="54" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CX54" s="4"/>
-      <c r="CY54" s="4"/>
       <c r="CZ54" s="4"/>
       <c r="DA54" s="4"/>
       <c r="DB54" s="4"/>
+      <c r="DC54" s="4"/>
     </row>
     <row r="55" spans="1:174" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="11"/>
@@ -9334,12 +9378,13 @@
       <c r="CV55" s="26"/>
       <c r="CW55" s="26"/>
       <c r="CX55" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="CY55" s="27"/>
+        <v>56</v>
+      </c>
+      <c r="CY55" s="26"/>
       <c r="CZ55" s="27"/>
       <c r="DA55" s="27"/>
       <c r="DB55" s="27"/>
+      <c r="DC55" s="27"/>
     </row>
     <row r="56" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
@@ -9648,17 +9693,20 @@
       <c r="CX56" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY56" s="28"/>
+      <c r="CY56" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ56" s="28"/>
       <c r="DA56" s="28"/>
       <c r="DB56" s="28"/>
+      <c r="DC56" s="28"/>
     </row>
     <row r="57" spans="1:174" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6"/>
-      <c r="CY57" s="4"/>
       <c r="CZ57" s="4"/>
       <c r="DA57" s="4"/>
       <c r="DB57" s="4"/>
+      <c r="DC57" s="4"/>
     </row>
     <row r="58" spans="1:174" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
@@ -9965,13 +10013,15 @@
         <v>33.612844800019445</v>
       </c>
       <c r="CX58" s="17">
-        <v>5.5344972986675884</v>
-      </c>
-      <c r="CY58" s="18"/>
+        <v>5.5572292149404348</v>
+      </c>
+      <c r="CY58" s="17">
+        <v>-44.789757239588091</v>
+      </c>
       <c r="CZ58" s="18"/>
       <c r="DA58" s="18"/>
       <c r="DB58" s="18"/>
-      <c r="DC58" s="14"/>
+      <c r="DC58" s="18"/>
       <c r="DD58" s="14"/>
       <c r="DE58" s="14"/>
       <c r="DF58" s="14"/>
@@ -10291,11 +10341,13 @@
       <c r="CX59" s="17">
         <v>13.257559092693995</v>
       </c>
-      <c r="CY59" s="18"/>
+      <c r="CY59" s="17">
+        <v>19.00021350033721</v>
+      </c>
       <c r="CZ59" s="18"/>
       <c r="DA59" s="18"/>
       <c r="DB59" s="18"/>
-      <c r="DC59" s="14"/>
+      <c r="DC59" s="18"/>
       <c r="DD59" s="14"/>
       <c r="DE59" s="14"/>
       <c r="DF59" s="14"/>
@@ -10669,13 +10721,15 @@
         <v>44.183769123410343</v>
       </c>
       <c r="CX60" s="17">
-        <v>58.434049062855195</v>
-      </c>
-      <c r="CY60" s="18"/>
+        <v>57.946876513435654</v>
+      </c>
+      <c r="CY60" s="17">
+        <v>55.747635636717376</v>
+      </c>
       <c r="CZ60" s="18"/>
       <c r="DA60" s="18"/>
       <c r="DB60" s="18"/>
-      <c r="DC60" s="14"/>
+      <c r="DC60" s="18"/>
       <c r="DD60" s="14"/>
       <c r="DE60" s="14"/>
       <c r="DF60" s="14"/>
@@ -11049,13 +11103,15 @@
         <v>14.45546225081948</v>
       </c>
       <c r="CX61" s="17">
-        <v>78.883457200782544</v>
-      </c>
-      <c r="CY61" s="18"/>
+        <v>87.496879142094741</v>
+      </c>
+      <c r="CY61" s="17">
+        <v>59.938165413048239</v>
+      </c>
       <c r="CZ61" s="18"/>
       <c r="DA61" s="18"/>
       <c r="DB61" s="18"/>
-      <c r="DC61" s="14"/>
+      <c r="DC61" s="18"/>
       <c r="DD61" s="14"/>
       <c r="DE61" s="14"/>
       <c r="DF61" s="14"/>
@@ -11429,13 +11485,15 @@
         <v>-0.23867834853777481</v>
       </c>
       <c r="CX62" s="17">
-        <v>14.337827975165823</v>
-      </c>
-      <c r="CY62" s="18"/>
+        <v>12.336639302122919</v>
+      </c>
+      <c r="CY62" s="17">
+        <v>94.336601089888035</v>
+      </c>
       <c r="CZ62" s="18"/>
       <c r="DA62" s="18"/>
       <c r="DB62" s="18"/>
-      <c r="DC62" s="14"/>
+      <c r="DC62" s="18"/>
       <c r="DD62" s="14"/>
       <c r="DE62" s="14"/>
       <c r="DF62" s="14"/>
@@ -11809,13 +11867,15 @@
         <v>0.90107336555487905</v>
       </c>
       <c r="CX63" s="17">
-        <v>0.64171516730726808</v>
-      </c>
-      <c r="CY63" s="18"/>
+        <v>0.87102422230482546</v>
+      </c>
+      <c r="CY63" s="17">
+        <v>4.0542381492888495</v>
+      </c>
       <c r="CZ63" s="18"/>
       <c r="DA63" s="18"/>
       <c r="DB63" s="18"/>
-      <c r="DC63" s="14"/>
+      <c r="DC63" s="18"/>
       <c r="DD63" s="14"/>
       <c r="DE63" s="14"/>
       <c r="DF63" s="14"/>
@@ -11986,11 +12046,11 @@
       <c r="CV64" s="14"/>
       <c r="CW64" s="14"/>
       <c r="CX64" s="14"/>
-      <c r="CY64" s="13"/>
+      <c r="CY64" s="14"/>
       <c r="CZ64" s="13"/>
       <c r="DA64" s="13"/>
       <c r="DB64" s="13"/>
-      <c r="DC64" s="14"/>
+      <c r="DC64" s="13"/>
       <c r="DD64" s="14"/>
       <c r="DE64" s="14"/>
       <c r="DF64" s="14"/>
@@ -12364,13 +12424,15 @@
         <v>16.144426974359675</v>
       </c>
       <c r="CX65" s="17">
-        <v>31.53147360679327</v>
-      </c>
-      <c r="CY65" s="18"/>
+        <v>32.675386286587127</v>
+      </c>
+      <c r="CY65" s="17">
+        <v>31.850143301558404</v>
+      </c>
       <c r="CZ65" s="18"/>
       <c r="DA65" s="18"/>
       <c r="DB65" s="18"/>
-      <c r="DC65" s="14"/>
+      <c r="DC65" s="18"/>
       <c r="DD65" s="14"/>
       <c r="DE65" s="14"/>
       <c r="DF65" s="14"/>
@@ -12542,19 +12604,20 @@
       <c r="CV66" s="8"/>
       <c r="CW66" s="8"/>
       <c r="CX66" s="8"/>
-      <c r="CY66" s="29"/>
+      <c r="CY66" s="8"/>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
       <c r="DB66" s="29"/>
+      <c r="DC66" s="29"/>
     </row>
     <row r="67" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CY67" s="4"/>
       <c r="CZ67" s="4"/>
       <c r="DA67" s="4"/>
       <c r="DB67" s="4"/>
+      <c r="DC67" s="4"/>
     </row>
     <row r="68" spans="1:174" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="14"/>
@@ -12658,11 +12721,11 @@
       <c r="CV68" s="14"/>
       <c r="CW68" s="14"/>
       <c r="CX68" s="14"/>
-      <c r="CY68" s="13"/>
+      <c r="CY68" s="14"/>
       <c r="CZ68" s="13"/>
       <c r="DA68" s="13"/>
       <c r="DB68" s="13"/>
-      <c r="DC68" s="14"/>
+      <c r="DC68" s="13"/>
       <c r="DD68" s="14"/>
       <c r="DE68" s="14"/>
       <c r="DF68" s="14"/>
@@ -12833,11 +12896,11 @@
       <c r="CV69" s="14"/>
       <c r="CW69" s="14"/>
       <c r="CX69" s="14"/>
-      <c r="CY69" s="13"/>
+      <c r="CY69" s="14"/>
       <c r="CZ69" s="13"/>
       <c r="DA69" s="13"/>
       <c r="DB69" s="13"/>
-      <c r="DC69" s="14"/>
+      <c r="DC69" s="13"/>
       <c r="DD69" s="14"/>
       <c r="DE69" s="14"/>
       <c r="DF69" s="14"/>
@@ -12910,67 +12973,67 @@
       <c r="A70" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CY70" s="4"/>
       <c r="CZ70" s="4"/>
       <c r="DA70" s="4"/>
       <c r="DB70" s="4"/>
+      <c r="DC70" s="4"/>
     </row>
     <row r="71" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CY71" s="4"/>
       <c r="CZ71" s="4"/>
       <c r="DA71" s="4"/>
       <c r="DB71" s="4"/>
+      <c r="DC71" s="4"/>
     </row>
     <row r="72" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="CY72" s="4"/>
+        <v>57</v>
+      </c>
       <c r="CZ72" s="4"/>
       <c r="DA72" s="4"/>
       <c r="DB72" s="4"/>
+      <c r="DC72" s="4"/>
     </row>
     <row r="73" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CY73" s="4"/>
       <c r="CZ73" s="4"/>
       <c r="DA73" s="4"/>
       <c r="DB73" s="4"/>
+      <c r="DC73" s="4"/>
     </row>
     <row r="74" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
       <c r="DB74" s="4"/>
+      <c r="DC74" s="4"/>
     </row>
     <row r="75" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="CY75" s="4"/>
+        <v>58</v>
+      </c>
       <c r="CZ75" s="4"/>
       <c r="DA75" s="4"/>
       <c r="DB75" s="4"/>
+      <c r="DC75" s="4"/>
     </row>
     <row r="76" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CY76" s="4"/>
       <c r="CZ76" s="4"/>
       <c r="DA76" s="4"/>
       <c r="DB76" s="4"/>
+      <c r="DC76" s="4"/>
     </row>
     <row r="77" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CY77" s="4"/>
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
       <c r="DB77" s="4"/>
+      <c r="DC77" s="4"/>
     </row>
     <row r="78" spans="1:174" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
@@ -13125,12 +13188,13 @@
       <c r="CV78" s="26"/>
       <c r="CW78" s="26"/>
       <c r="CX78" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="CY78" s="27"/>
+        <v>56</v>
+      </c>
+      <c r="CY78" s="26"/>
       <c r="CZ78" s="27"/>
       <c r="DA78" s="27"/>
       <c r="DB78" s="27"/>
+      <c r="DC78" s="27"/>
     </row>
     <row r="79" spans="1:174" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
@@ -13439,17 +13503,20 @@
       <c r="CX79" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY79" s="28"/>
+      <c r="CY79" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ79" s="28"/>
       <c r="DA79" s="28"/>
       <c r="DB79" s="28"/>
+      <c r="DC79" s="28"/>
     </row>
     <row r="80" spans="1:174" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6"/>
-      <c r="CY80" s="4"/>
       <c r="CZ80" s="4"/>
       <c r="DA80" s="4"/>
       <c r="DB80" s="4"/>
+      <c r="DC80" s="4"/>
     </row>
     <row r="81" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
@@ -13756,13 +13823,15 @@
         <v>63.78219797132229</v>
       </c>
       <c r="CX81" s="17">
-        <v>1.9652830311923282</v>
-      </c>
-      <c r="CY81" s="18"/>
+        <v>1.9872461459645763</v>
+      </c>
+      <c r="CY81" s="17">
+        <v>-56.211899149636665</v>
+      </c>
       <c r="CZ81" s="18"/>
       <c r="DA81" s="18"/>
       <c r="DB81" s="18"/>
-      <c r="DC81" s="14"/>
+      <c r="DC81" s="18"/>
       <c r="DD81" s="14"/>
       <c r="DE81" s="14"/>
       <c r="DF81" s="14"/>
@@ -14138,11 +14207,13 @@
       <c r="CX82" s="17">
         <v>-0.23459418940556986</v>
       </c>
-      <c r="CY82" s="18"/>
+      <c r="CY82" s="17">
+        <v>-12.065886251589035</v>
+      </c>
       <c r="CZ82" s="18"/>
       <c r="DA82" s="18"/>
       <c r="DB82" s="18"/>
-      <c r="DC82" s="14"/>
+      <c r="DC82" s="18"/>
       <c r="DD82" s="14"/>
       <c r="DE82" s="14"/>
       <c r="DF82" s="14"/>
@@ -14516,13 +14587,15 @@
         <v>-7.5119250120530268</v>
       </c>
       <c r="CX83" s="17">
-        <v>-10.154372773027958</v>
-      </c>
-      <c r="CY83" s="18"/>
+        <v>-10.430630078225136</v>
+      </c>
+      <c r="CY83" s="17">
+        <v>3.243385723859447</v>
+      </c>
       <c r="CZ83" s="18"/>
       <c r="DA83" s="18"/>
       <c r="DB83" s="18"/>
-      <c r="DC83" s="14"/>
+      <c r="DC83" s="18"/>
       <c r="DD83" s="14"/>
       <c r="DE83" s="14"/>
       <c r="DF83" s="14"/>
@@ -14896,13 +14969,15 @@
         <v>12.69477352843171</v>
       </c>
       <c r="CX84" s="17">
-        <v>58.074888292232515</v>
-      </c>
-      <c r="CY84" s="18"/>
+        <v>65.686356297675616</v>
+      </c>
+      <c r="CY84" s="17">
+        <v>23.423602859644859</v>
+      </c>
       <c r="CZ84" s="18"/>
       <c r="DA84" s="18"/>
       <c r="DB84" s="18"/>
-      <c r="DC84" s="14"/>
+      <c r="DC84" s="18"/>
       <c r="DD84" s="14"/>
       <c r="DE84" s="14"/>
       <c r="DF84" s="14"/>
@@ -15276,13 +15351,15 @@
         <v>-11.633439240096564</v>
       </c>
       <c r="CX85" s="17">
-        <v>-18.037395561120178</v>
-      </c>
-      <c r="CY85" s="18"/>
+        <v>-19.471939478220037</v>
+      </c>
+      <c r="CY85" s="17">
+        <v>27.795031735107585</v>
+      </c>
       <c r="CZ85" s="18"/>
       <c r="DA85" s="18"/>
       <c r="DB85" s="18"/>
-      <c r="DC85" s="14"/>
+      <c r="DC85" s="18"/>
       <c r="DD85" s="14"/>
       <c r="DE85" s="14"/>
       <c r="DF85" s="14"/>
@@ -15656,13 +15733,15 @@
         <v>0.2298832989659445</v>
       </c>
       <c r="CX86" s="17">
-        <v>8.3736588906731413E-2</v>
-      </c>
-      <c r="CY86" s="18"/>
+        <v>0.31177430686170737</v>
+      </c>
+      <c r="CY86" s="17">
+        <v>0.86075769457916351</v>
+      </c>
       <c r="CZ86" s="18"/>
       <c r="DA86" s="18"/>
       <c r="DB86" s="18"/>
-      <c r="DC86" s="14"/>
+      <c r="DC86" s="18"/>
       <c r="DD86" s="14"/>
       <c r="DE86" s="14"/>
       <c r="DF86" s="14"/>
@@ -15833,11 +15912,11 @@
       <c r="CV87" s="14"/>
       <c r="CW87" s="14"/>
       <c r="CX87" s="14"/>
-      <c r="CY87" s="13"/>
+      <c r="CY87" s="14"/>
       <c r="CZ87" s="13"/>
       <c r="DA87" s="13"/>
       <c r="DB87" s="13"/>
-      <c r="DC87" s="14"/>
+      <c r="DC87" s="13"/>
       <c r="DD87" s="14"/>
       <c r="DE87" s="14"/>
       <c r="DF87" s="14"/>
@@ -16211,13 +16290,15 @@
         <v>5.0727040939522396</v>
       </c>
       <c r="CX88" s="17">
-        <v>3.8111326470167057</v>
-      </c>
-      <c r="CY88" s="18"/>
+        <v>4.5842323790799071</v>
+      </c>
+      <c r="CY88" s="17">
+        <v>-9.8110181052331313</v>
+      </c>
       <c r="CZ88" s="18"/>
       <c r="DA88" s="18"/>
       <c r="DB88" s="18"/>
-      <c r="DC88" s="14"/>
+      <c r="DC88" s="18"/>
       <c r="DD88" s="14"/>
       <c r="DE88" s="14"/>
       <c r="DF88" s="14"/>
@@ -16389,19 +16470,20 @@
       <c r="CV89" s="8"/>
       <c r="CW89" s="8"/>
       <c r="CX89" s="8"/>
-      <c r="CY89" s="29"/>
+      <c r="CY89" s="8"/>
       <c r="CZ89" s="29"/>
       <c r="DA89" s="29"/>
       <c r="DB89" s="29"/>
+      <c r="DC89" s="29"/>
     </row>
     <row r="90" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CY90" s="4"/>
       <c r="CZ90" s="4"/>
       <c r="DA90" s="4"/>
       <c r="DB90" s="4"/>
+      <c r="DC90" s="4"/>
     </row>
     <row r="91" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B91" s="14"/>
@@ -16504,12 +16586,12 @@
       <c r="CU91" s="14"/>
       <c r="CV91" s="14"/>
       <c r="CW91" s="14"/>
-      <c r="CX91" s="13"/>
-      <c r="CY91" s="13"/>
+      <c r="CX91" s="14"/>
+      <c r="CY91" s="14"/>
       <c r="CZ91" s="13"/>
       <c r="DA91" s="13"/>
       <c r="DB91" s="13"/>
-      <c r="DC91" s="14"/>
+      <c r="DC91" s="13"/>
       <c r="DD91" s="14"/>
       <c r="DE91" s="14"/>
       <c r="DF91" s="14"/>
@@ -16680,11 +16762,11 @@
       <c r="CV92" s="14"/>
       <c r="CW92" s="14"/>
       <c r="CX92" s="13"/>
-      <c r="CY92" s="13"/>
+      <c r="CY92" s="14"/>
       <c r="CZ92" s="13"/>
       <c r="DA92" s="13"/>
       <c r="DB92" s="13"/>
-      <c r="DC92" s="14"/>
+      <c r="DC92" s="13"/>
       <c r="DD92" s="14"/>
       <c r="DE92" s="14"/>
       <c r="DF92" s="14"/>
@@ -16767,16 +16849,18 @@
       <c r="CZ93" s="4"/>
       <c r="DA93" s="4"/>
       <c r="DB93" s="4"/>
+      <c r="DC93" s="4"/>
     </row>
     <row r="94" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="CX94" s="4"/>
       <c r="CY94" s="4"/>
       <c r="CZ94" s="4"/>
       <c r="DA94" s="4"/>
       <c r="DB94" s="4"/>
+      <c r="DC94" s="4"/>
     </row>
     <row r="95" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX95" s="4"/>
@@ -16784,6 +16868,7 @@
       <c r="CZ95" s="4"/>
       <c r="DA95" s="4"/>
       <c r="DB95" s="4"/>
+      <c r="DC95" s="4"/>
     </row>
     <row r="96" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
@@ -16792,7 +16877,7 @@
     </row>
     <row r="97" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -16962,6 +17047,7 @@
       <c r="DB100" s="26">
         <v>2026</v>
       </c>
+      <c r="DC100" s="26"/>
     </row>
     <row r="101" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
@@ -17281,6 +17367,9 @@
       </c>
       <c r="DB101" s="10" t="s">
         <v>2</v>
+      </c>
+      <c r="DC101" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -17605,7 +17694,9 @@
       <c r="DB103" s="17">
         <v>94.544534945764369</v>
       </c>
-      <c r="DC103" s="14"/>
+      <c r="DC103" s="17">
+        <v>114.01799448953926</v>
+      </c>
       <c r="DD103" s="14"/>
       <c r="DE103" s="14"/>
       <c r="DF103" s="14"/>
@@ -17998,7 +18089,9 @@
       <c r="DB104" s="17">
         <v>269.35363159795418</v>
       </c>
-      <c r="DC104" s="14"/>
+      <c r="DC104" s="17">
+        <v>90.683890594960531</v>
+      </c>
       <c r="DD104" s="14"/>
       <c r="DE104" s="14"/>
       <c r="DF104" s="14"/>
@@ -18389,9 +18482,11 @@
         <v>359.13357204321062</v>
       </c>
       <c r="DB105" s="17">
-        <v>505.8025658842065</v>
-      </c>
-      <c r="DC105" s="14"/>
+        <v>505.80250315895432</v>
+      </c>
+      <c r="DC105" s="17">
+        <v>460.46110040103372</v>
+      </c>
       <c r="DD105" s="14"/>
       <c r="DE105" s="14"/>
       <c r="DF105" s="14"/>
@@ -18782,9 +18877,11 @@
         <v>189.33651532972314</v>
       </c>
       <c r="DB106" s="17">
-        <v>228.57316015920537</v>
-      </c>
-      <c r="DC106" s="14"/>
+        <v>228.57316015920529</v>
+      </c>
+      <c r="DC106" s="17">
+        <v>188.99778308354922</v>
+      </c>
       <c r="DD106" s="14"/>
       <c r="DE106" s="14"/>
       <c r="DF106" s="14"/>
@@ -19177,7 +19274,9 @@
       <c r="DB107" s="17">
         <v>83.438724384756028</v>
       </c>
-      <c r="DC107" s="14"/>
+      <c r="DC107" s="17">
+        <v>455.76733399683411</v>
+      </c>
       <c r="DD107" s="14"/>
       <c r="DE107" s="14"/>
       <c r="DF107" s="14"/>
@@ -19568,9 +19667,11 @@
         <v>92.645797298657158</v>
       </c>
       <c r="DB108" s="17">
-        <v>123.75643616057386</v>
-      </c>
-      <c r="DC108" s="14"/>
+        <v>123.75643616057388</v>
+      </c>
+      <c r="DC108" s="17">
+        <v>130.1119616081973</v>
+      </c>
       <c r="DD108" s="14"/>
       <c r="DE108" s="14"/>
       <c r="DF108" s="14"/>
@@ -20141,9 +20242,11 @@
         <v>160.37144749371657</v>
       </c>
       <c r="DB110" s="17">
-        <v>194.095654439605</v>
-      </c>
-      <c r="DC110" s="14"/>
+        <v>194.33642246988717</v>
+      </c>
+      <c r="DC110" s="17">
+        <v>216.49848201412016</v>
+      </c>
       <c r="DD110" s="14"/>
       <c r="DE110" s="14"/>
       <c r="DF110" s="14"/>
@@ -20324,6 +20427,7 @@
       <c r="CZ111" s="8"/>
       <c r="DA111" s="8"/>
       <c r="DB111" s="8"/>
+      <c r="DC111" s="8"/>
     </row>
     <row r="112" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9" t="s">
@@ -20342,7 +20446,7 @@
     </row>
     <row r="117" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="118" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -20353,7 +20457,7 @@
     </row>
     <row r="120" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="121" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -20523,6 +20627,7 @@
       <c r="DB123" s="26">
         <v>2026</v>
       </c>
+      <c r="DC123" s="26"/>
     </row>
     <row r="124" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
@@ -20842,6 +20947,9 @@
       </c>
       <c r="DB124" s="10" t="s">
         <v>2</v>
+      </c>
+      <c r="DC124" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -21164,9 +21272,11 @@
         <v>9.5163329486841111</v>
       </c>
       <c r="DB126" s="20">
-        <v>10.374817755162818</v>
-      </c>
-      <c r="DC126" s="14"/>
+        <v>10.287582657591841</v>
+      </c>
+      <c r="DC126" s="20">
+        <v>6.326405891133664</v>
+      </c>
       <c r="DD126" s="14"/>
       <c r="DE126" s="14"/>
       <c r="DF126" s="14"/>
@@ -21557,9 +21667,11 @@
         <v>7.5757304689392972</v>
       </c>
       <c r="DB127" s="20">
-        <v>10.308840244343328</v>
-      </c>
-      <c r="DC127" s="14"/>
+        <v>10.219958550462284</v>
+      </c>
+      <c r="DC127" s="20">
+        <v>6.3112809427000576</v>
+      </c>
       <c r="DD127" s="14"/>
       <c r="DE127" s="14"/>
       <c r="DF127" s="14"/>
@@ -21950,9 +22062,11 @@
         <v>38.32857262911125</v>
       </c>
       <c r="DB128" s="20">
-        <v>34.494030534149942</v>
-      </c>
-      <c r="DC128" s="14"/>
+        <v>34.091474768371874</v>
+      </c>
+      <c r="DC128" s="20">
+        <v>42.966975530126753</v>
+      </c>
       <c r="DD128" s="14"/>
       <c r="DE128" s="14"/>
       <c r="DF128" s="14"/>
@@ -22343,9 +22457,11 @@
         <v>5.9154975384324588</v>
       </c>
       <c r="DB129" s="20">
-        <v>20.344276010442716</v>
-      </c>
-      <c r="DC129" s="14"/>
+        <v>21.140021658027642</v>
+      </c>
+      <c r="DC129" s="20">
+        <v>22.876729780834491</v>
+      </c>
       <c r="DD129" s="14"/>
       <c r="DE129" s="14"/>
       <c r="DF129" s="14"/>
@@ -22736,9 +22852,11 @@
         <v>9.5284046222723422</v>
       </c>
       <c r="DB130" s="20">
-        <v>3.1268060628789214</v>
-      </c>
-      <c r="DC130" s="14"/>
+        <v>3.0455922575526468</v>
+      </c>
+      <c r="DC130" s="20">
+        <v>7.8167008083047138</v>
+      </c>
       <c r="DD130" s="14"/>
       <c r="DE130" s="14"/>
       <c r="DF130" s="14"/>
@@ -23129,9 +23247,11 @@
         <v>29.135461792560541</v>
       </c>
       <c r="DB131" s="20">
-        <v>21.351229393022276</v>
-      </c>
-      <c r="DC131" s="14"/>
+        <v>21.215370107993717</v>
+      </c>
+      <c r="DC131" s="20">
+        <v>13.701907046900322</v>
+      </c>
       <c r="DD131" s="14"/>
       <c r="DE131" s="14"/>
       <c r="DF131" s="14"/>
@@ -23704,7 +23824,9 @@
       <c r="DB133" s="20">
         <v>100</v>
       </c>
-      <c r="DC133" s="14"/>
+      <c r="DC133" s="20">
+        <v>100</v>
+      </c>
       <c r="DD133" s="14"/>
       <c r="DE133" s="14"/>
       <c r="DF133" s="14"/>
@@ -23885,6 +24007,7 @@
       <c r="CZ134" s="8"/>
       <c r="DA134" s="8"/>
       <c r="DB134" s="8"/>
+      <c r="DC134" s="8"/>
     </row>
     <row r="135" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9" t="s">
@@ -24263,7 +24386,7 @@
     </row>
     <row r="140" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="141" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -24274,7 +24397,7 @@
     </row>
     <row r="143" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="144" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -24444,6 +24567,7 @@
       <c r="DB146" s="26">
         <v>2026</v>
       </c>
+      <c r="DC146" s="26"/>
     </row>
     <row r="147" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
@@ -24763,6 +24887,9 @@
       </c>
       <c r="DB147" s="10" t="s">
         <v>2</v>
+      </c>
+      <c r="DC147" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -25085,9 +25212,11 @@
         <v>17.027400243152531</v>
       </c>
       <c r="DB149" s="20">
-        <v>21.299031647203375</v>
-      </c>
-      <c r="DC149" s="14"/>
+        <v>21.146140394963357</v>
+      </c>
+      <c r="DC149" s="20">
+        <v>12.012641321815973</v>
+      </c>
       <c r="DD149" s="14"/>
       <c r="DE149" s="14"/>
       <c r="DF149" s="14"/>
@@ -25478,9 +25607,11 @@
         <v>6.9618702092537079</v>
       </c>
       <c r="DB150" s="20">
-        <v>7.4285283694476556</v>
-      </c>
-      <c r="DC150" s="14"/>
+        <v>7.3736157582308186</v>
+      </c>
+      <c r="DC150" s="20">
+        <v>15.067535531334386</v>
+      </c>
       <c r="DD150" s="14"/>
       <c r="DE150" s="14"/>
       <c r="DF150" s="14"/>
@@ -25871,9 +26002,11 @@
         <v>17.115661557140747</v>
       </c>
       <c r="DB151" s="20">
-        <v>13.236669567070308</v>
-      </c>
-      <c r="DC151" s="14"/>
+        <v>13.09842320239717</v>
+      </c>
+      <c r="DC151" s="20">
+        <v>20.2021082148059</v>
+      </c>
       <c r="DD151" s="14"/>
       <c r="DE151" s="14"/>
       <c r="DF151" s="14"/>
@@ -26264,9 +26397,11 @@
         <v>5.0105332361897652</v>
       </c>
       <c r="DB152" s="20">
-        <v>17.275587228161299</v>
-      </c>
-      <c r="DC152" s="14"/>
+        <v>17.973572124984123</v>
+      </c>
+      <c r="DC152" s="20">
+        <v>26.205478128854214</v>
+      </c>
       <c r="DD152" s="14"/>
       <c r="DE152" s="14"/>
       <c r="DF152" s="14"/>
@@ -26657,9 +26792,11 @@
         <v>3.4505559089159656</v>
       </c>
       <c r="DB153" s="20">
-        <v>7.2735947673606498</v>
-      </c>
-      <c r="DC153" s="14"/>
+        <v>7.0934629933400704</v>
+      </c>
+      <c r="DC153" s="20">
+        <v>3.7130872116610965</v>
+      </c>
       <c r="DD153" s="14"/>
       <c r="DE153" s="14"/>
       <c r="DF153" s="14"/>
@@ -27050,9 +27187,11 @@
         <v>50.433978845347283</v>
       </c>
       <c r="DB154" s="20">
-        <v>33.486588420756703</v>
-      </c>
-      <c r="DC154" s="14"/>
+        <v>33.314785526084464</v>
+      </c>
+      <c r="DC154" s="20">
+        <v>22.799149591528437</v>
+      </c>
       <c r="DD154" s="14"/>
       <c r="DE154" s="14"/>
       <c r="DF154" s="14"/>
@@ -27625,7 +27764,9 @@
       <c r="DB156" s="20">
         <v>100</v>
       </c>
-      <c r="DC156" s="14"/>
+      <c r="DC156" s="20">
+        <v>100</v>
+      </c>
       <c r="DD156" s="14"/>
       <c r="DE156" s="14"/>
       <c r="DF156" s="14"/>
@@ -27806,6 +27947,7 @@
       <c r="CZ157" s="8"/>
       <c r="DA157" s="8"/>
       <c r="DB157" s="8"/>
+      <c r="DC157" s="8"/>
     </row>
     <row r="158" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="9" t="s">
@@ -28049,8 +28191,9 @@
       <c r="CZ160" s="21"/>
       <c r="DA160" s="21"/>
       <c r="DB160" s="21"/>
+      <c r="DC160" s="21"/>
     </row>
-    <row r="161" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="161" spans="98:107" x14ac:dyDescent="0.2">
       <c r="CT161" s="21"/>
       <c r="CU161" s="21"/>
       <c r="CV161" s="21"/>
@@ -28060,8 +28203,9 @@
       <c r="CZ161" s="21"/>
       <c r="DA161" s="21"/>
       <c r="DB161" s="21"/>
+      <c r="DC161" s="21"/>
     </row>
-    <row r="162" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="162" spans="98:107" x14ac:dyDescent="0.2">
       <c r="CT162" s="21"/>
       <c r="CU162" s="21"/>
       <c r="CV162" s="21"/>
@@ -28070,8 +28214,10 @@
       <c r="CY162" s="21"/>
       <c r="CZ162" s="21"/>
       <c r="DA162" s="21"/>
+      <c r="DB162" s="21"/>
+      <c r="DC162" s="21"/>
     </row>
-    <row r="163" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="163" spans="98:107" x14ac:dyDescent="0.2">
       <c r="CT163" s="21"/>
       <c r="CU163" s="21"/>
       <c r="CV163" s="21"/>
@@ -28080,62 +28226,113 @@
       <c r="CY163" s="21"/>
       <c r="CZ163" s="21"/>
       <c r="DA163" s="21"/>
+      <c r="DB163" s="21"/>
+      <c r="DC163" s="21"/>
     </row>
-    <row r="164" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="164" spans="98:107" x14ac:dyDescent="0.2">
       <c r="CT164" s="21"/>
       <c r="CU164" s="21"/>
       <c r="CV164" s="21"/>
       <c r="CW164" s="21"/>
-      <c r="CX164" s="21"/>
-      <c r="CY164" s="21"/>
-      <c r="CZ164" s="21"/>
-      <c r="DA164" s="21"/>
     </row>
-    <row r="165" spans="98:106" x14ac:dyDescent="0.2">
+    <row r="165" spans="98:107" x14ac:dyDescent="0.2">
       <c r="CT165" s="21"/>
       <c r="CU165" s="21"/>
       <c r="CV165" s="21"/>
       <c r="CW165" s="21"/>
-      <c r="CX165" s="21"/>
-      <c r="CY165" s="21"/>
-      <c r="CZ165" s="21"/>
-      <c r="DA165" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="CD146:CG146"/>
-    <mergeCell ref="BF146:BI146"/>
-    <mergeCell ref="BJ146:BM146"/>
-    <mergeCell ref="BN146:BQ146"/>
-    <mergeCell ref="BR146:BU146"/>
-    <mergeCell ref="BV146:BY146"/>
-    <mergeCell ref="BZ146:CC146"/>
-    <mergeCell ref="AH146:AK146"/>
-    <mergeCell ref="AL146:AO146"/>
-    <mergeCell ref="AP146:AS146"/>
-    <mergeCell ref="AT146:AW146"/>
-    <mergeCell ref="AX146:BA146"/>
-    <mergeCell ref="BB146:BE146"/>
-    <mergeCell ref="BF123:BI123"/>
-    <mergeCell ref="BJ123:BM123"/>
-    <mergeCell ref="BN123:BQ123"/>
-    <mergeCell ref="BR123:BU123"/>
-    <mergeCell ref="BV123:BY123"/>
-    <mergeCell ref="AD123:AG123"/>
-    <mergeCell ref="AH123:AK123"/>
-    <mergeCell ref="AL123:AO123"/>
-    <mergeCell ref="AP123:AS123"/>
-    <mergeCell ref="AT123:AW123"/>
-    <mergeCell ref="AX123:BA123"/>
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="F146:I146"/>
-    <mergeCell ref="J146:M146"/>
-    <mergeCell ref="N146:Q146"/>
-    <mergeCell ref="R146:U146"/>
-    <mergeCell ref="V146:Y146"/>
-    <mergeCell ref="Z146:AC146"/>
-    <mergeCell ref="AD146:AG146"/>
-    <mergeCell ref="BB123:BE123"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="AP32:AS32"/>
+    <mergeCell ref="AT32:AW32"/>
+    <mergeCell ref="AX32:BA32"/>
+    <mergeCell ref="BV9:BY9"/>
+    <mergeCell ref="BZ9:CC9"/>
+    <mergeCell ref="CD9:CG9"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="R32:U32"/>
+    <mergeCell ref="V32:Y32"/>
+    <mergeCell ref="Z32:AC32"/>
+    <mergeCell ref="AX9:BA9"/>
+    <mergeCell ref="BB9:BE9"/>
+    <mergeCell ref="BF9:BI9"/>
+    <mergeCell ref="BJ9:BM9"/>
+    <mergeCell ref="BN9:BQ9"/>
+    <mergeCell ref="BR9:BU9"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="AD9:AG9"/>
+    <mergeCell ref="AH9:AK9"/>
+    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="AP9:AS9"/>
+    <mergeCell ref="AT9:AW9"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="AL55:AO55"/>
+    <mergeCell ref="AP55:AS55"/>
+    <mergeCell ref="AT55:AW55"/>
+    <mergeCell ref="AX55:BA55"/>
+    <mergeCell ref="BB55:BE55"/>
+    <mergeCell ref="BZ32:CC32"/>
+    <mergeCell ref="CD32:CG32"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="N55:Q55"/>
+    <mergeCell ref="R55:U55"/>
+    <mergeCell ref="V55:Y55"/>
+    <mergeCell ref="Z55:AC55"/>
+    <mergeCell ref="AD55:AG55"/>
+    <mergeCell ref="BB32:BE32"/>
+    <mergeCell ref="BF32:BI32"/>
+    <mergeCell ref="BJ32:BM32"/>
+    <mergeCell ref="BN32:BQ32"/>
+    <mergeCell ref="BR32:BU32"/>
+    <mergeCell ref="BV32:BY32"/>
+    <mergeCell ref="AD32:AG32"/>
+    <mergeCell ref="AH32:AK32"/>
+    <mergeCell ref="AL32:AO32"/>
+    <mergeCell ref="CD78:CG78"/>
+    <mergeCell ref="AL78:AO78"/>
+    <mergeCell ref="AP78:AS78"/>
+    <mergeCell ref="AT78:AW78"/>
+    <mergeCell ref="AX78:BA78"/>
+    <mergeCell ref="BB78:BE78"/>
+    <mergeCell ref="BF78:BI78"/>
+    <mergeCell ref="CD55:CG55"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="N78:Q78"/>
+    <mergeCell ref="R78:U78"/>
+    <mergeCell ref="V78:Y78"/>
+    <mergeCell ref="Z78:AC78"/>
+    <mergeCell ref="AD78:AG78"/>
+    <mergeCell ref="AH78:AK78"/>
+    <mergeCell ref="BF55:BI55"/>
+    <mergeCell ref="BJ55:BM55"/>
+    <mergeCell ref="BN55:BQ55"/>
+    <mergeCell ref="BR55:BU55"/>
+    <mergeCell ref="BV55:BY55"/>
+    <mergeCell ref="BZ55:CC55"/>
+    <mergeCell ref="AH55:AK55"/>
+    <mergeCell ref="J100:M100"/>
+    <mergeCell ref="N100:Q100"/>
+    <mergeCell ref="R100:U100"/>
+    <mergeCell ref="V100:Y100"/>
+    <mergeCell ref="BJ78:BM78"/>
+    <mergeCell ref="BN78:BQ78"/>
+    <mergeCell ref="BR78:BU78"/>
+    <mergeCell ref="BV78:BY78"/>
+    <mergeCell ref="BZ78:CC78"/>
+    <mergeCell ref="BV100:BY100"/>
+    <mergeCell ref="BZ100:CC100"/>
     <mergeCell ref="CD100:CG100"/>
     <mergeCell ref="B123:E123"/>
     <mergeCell ref="F123:I123"/>
@@ -28160,108 +28357,51 @@
     <mergeCell ref="F100:I100"/>
     <mergeCell ref="BZ123:CC123"/>
     <mergeCell ref="CD123:CG123"/>
-    <mergeCell ref="J100:M100"/>
-    <mergeCell ref="N100:Q100"/>
-    <mergeCell ref="R100:U100"/>
-    <mergeCell ref="V100:Y100"/>
-    <mergeCell ref="BJ78:BM78"/>
-    <mergeCell ref="BN78:BQ78"/>
-    <mergeCell ref="BR78:BU78"/>
-    <mergeCell ref="BV78:BY78"/>
-    <mergeCell ref="BZ78:CC78"/>
-    <mergeCell ref="BV100:BY100"/>
-    <mergeCell ref="BZ100:CC100"/>
-    <mergeCell ref="CD78:CG78"/>
-    <mergeCell ref="AL78:AO78"/>
-    <mergeCell ref="AP78:AS78"/>
-    <mergeCell ref="AT78:AW78"/>
-    <mergeCell ref="AX78:BA78"/>
-    <mergeCell ref="BB78:BE78"/>
-    <mergeCell ref="BF78:BI78"/>
-    <mergeCell ref="CD55:CG55"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="N78:Q78"/>
-    <mergeCell ref="R78:U78"/>
-    <mergeCell ref="V78:Y78"/>
-    <mergeCell ref="Z78:AC78"/>
-    <mergeCell ref="AD78:AG78"/>
-    <mergeCell ref="AH78:AK78"/>
-    <mergeCell ref="BF55:BI55"/>
-    <mergeCell ref="BJ55:BM55"/>
-    <mergeCell ref="BN55:BQ55"/>
-    <mergeCell ref="BR55:BU55"/>
-    <mergeCell ref="BV55:BY55"/>
-    <mergeCell ref="BZ55:CC55"/>
-    <mergeCell ref="AH55:AK55"/>
-    <mergeCell ref="AL55:AO55"/>
-    <mergeCell ref="AP55:AS55"/>
-    <mergeCell ref="AT55:AW55"/>
-    <mergeCell ref="AX55:BA55"/>
-    <mergeCell ref="BB55:BE55"/>
-    <mergeCell ref="BZ32:CC32"/>
-    <mergeCell ref="CD32:CG32"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="N55:Q55"/>
-    <mergeCell ref="R55:U55"/>
-    <mergeCell ref="V55:Y55"/>
-    <mergeCell ref="Z55:AC55"/>
-    <mergeCell ref="AD55:AG55"/>
-    <mergeCell ref="BB32:BE32"/>
-    <mergeCell ref="BF32:BI32"/>
-    <mergeCell ref="BJ32:BM32"/>
-    <mergeCell ref="BN32:BQ32"/>
-    <mergeCell ref="BR32:BU32"/>
-    <mergeCell ref="BV32:BY32"/>
-    <mergeCell ref="AD32:AG32"/>
-    <mergeCell ref="AH32:AK32"/>
-    <mergeCell ref="AL32:AO32"/>
-    <mergeCell ref="AX32:BA32"/>
-    <mergeCell ref="BV9:BY9"/>
-    <mergeCell ref="BZ9:CC9"/>
-    <mergeCell ref="CD9:CG9"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="R32:U32"/>
-    <mergeCell ref="V32:Y32"/>
-    <mergeCell ref="Z32:AC32"/>
-    <mergeCell ref="AX9:BA9"/>
-    <mergeCell ref="BB9:BE9"/>
-    <mergeCell ref="BF9:BI9"/>
-    <mergeCell ref="BJ9:BM9"/>
-    <mergeCell ref="BN9:BQ9"/>
-    <mergeCell ref="BR9:BU9"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="AD9:AG9"/>
-    <mergeCell ref="AH9:AK9"/>
-    <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="AP9:AS9"/>
-    <mergeCell ref="AT9:AW9"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="AP32:AS32"/>
-    <mergeCell ref="AT32:AW32"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="F146:I146"/>
+    <mergeCell ref="J146:M146"/>
+    <mergeCell ref="N146:Q146"/>
+    <mergeCell ref="R146:U146"/>
+    <mergeCell ref="V146:Y146"/>
+    <mergeCell ref="Z146:AC146"/>
+    <mergeCell ref="AD146:AG146"/>
+    <mergeCell ref="BB123:BE123"/>
+    <mergeCell ref="BF123:BI123"/>
+    <mergeCell ref="BJ123:BM123"/>
+    <mergeCell ref="BN123:BQ123"/>
+    <mergeCell ref="BR123:BU123"/>
+    <mergeCell ref="BV123:BY123"/>
+    <mergeCell ref="AD123:AG123"/>
+    <mergeCell ref="AH123:AK123"/>
+    <mergeCell ref="AL123:AO123"/>
+    <mergeCell ref="AP123:AS123"/>
+    <mergeCell ref="AT123:AW123"/>
+    <mergeCell ref="AX123:BA123"/>
+    <mergeCell ref="CD146:CG146"/>
+    <mergeCell ref="BF146:BI146"/>
+    <mergeCell ref="BJ146:BM146"/>
+    <mergeCell ref="BN146:BQ146"/>
+    <mergeCell ref="BR146:BU146"/>
+    <mergeCell ref="BV146:BY146"/>
+    <mergeCell ref="BZ146:CC146"/>
+    <mergeCell ref="AH146:AK146"/>
+    <mergeCell ref="AL146:AO146"/>
+    <mergeCell ref="AP146:AS146"/>
+    <mergeCell ref="AT146:AW146"/>
+    <mergeCell ref="AX146:BA146"/>
+    <mergeCell ref="BB146:BE146"/>
   </mergeCells>
-  <conditionalFormatting sqref="BR58:CW65 BR81:CW88 BR103:DA110 CY81:DA88 CY58:DA65">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="BR58:CW65 BR81:CW88">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DB58:DB65 DB81:DB88 DB103:DB110">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
+  <conditionalFormatting sqref="BR103:CW110">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="CX58:CX65 CX81:CX88">
+  <conditionalFormatting sqref="CX58:DC65 CX81:DC88 CX103:DC110">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>1000</formula>
     </cfRule>
@@ -28271,9 +28411,9 @@
   <pageSetup paperSize="9" scale="46" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="46" max="105" man="1"/>
-    <brk id="92" max="105" man="1"/>
-    <brk id="114" max="105" man="1"/>
+    <brk id="46" max="106" man="1"/>
+    <brk id="92" max="106" man="1"/>
+    <brk id="114" max="106" man="1"/>
   </rowBreaks>
   <colBreaks count="2" manualBreakCount="2">
     <brk id="56" max="158" man="1"/>
